--- a/output/latest/all_candidates_latest.xlsx
+++ b/output/latest/all_candidates_latest.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="all_candidates" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="true_breakout" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="range_rebound" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="revenue_pullback" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="pullback_rebound" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="all_candidates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="true_breakout" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="range_rebound" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="revenue_pullback" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pullback_rebound" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/output/latest/all_candidates_latest.xlsx
+++ b/output/latest/all_candidates_latest.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV311"/>
+  <dimension ref="A1:CG311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,61 @@
       <c r="BV1" t="inlineStr">
         <is>
           <t>warrant_note</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>warrant_flow_signal_warrant</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>warrant_flow_score_warrant</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>warrant_flow_warning_warrant</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>call_turnover_warrant</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>put_turnover_warrant</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>call_put_turnover_ratio_warrant</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>call_turnover_change_1d_warrant</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>call_turnover_change_5d_warrant</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>low_float_call_spike_count_warrant</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>top_issuer_warrant</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>warrant_note_warrant</t>
         </is>
       </c>
     </row>
@@ -929,6 +984,17 @@
       <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr"/>
       <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1069,6 +1135,37 @@
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>中信</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1209,6 +1306,17 @@
       <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1349,6 +1457,17 @@
       <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="inlineStr"/>
       <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1489,6 +1608,17 @@
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1629,6 +1759,33 @@
       <c r="BT7" t="inlineStr"/>
       <c r="BU7" t="inlineStr"/>
       <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1769,6 +1926,33 @@
       <c r="BT8" t="inlineStr"/>
       <c r="BU8" t="inlineStr"/>
       <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1909,6 +2093,17 @@
       <c r="BT9" t="inlineStr"/>
       <c r="BU9" t="inlineStr"/>
       <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2049,6 +2244,33 @@
       <c r="BT10" t="inlineStr"/>
       <c r="BU10" t="inlineStr"/>
       <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2189,6 +2411,17 @@
       <c r="BT11" t="inlineStr"/>
       <c r="BU11" t="inlineStr"/>
       <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2329,6 +2562,33 @@
       <c r="BT12" t="inlineStr"/>
       <c r="BU12" t="inlineStr"/>
       <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2469,6 +2729,17 @@
       <c r="BT13" t="inlineStr"/>
       <c r="BU13" t="inlineStr"/>
       <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2609,6 +2880,33 @@
       <c r="BT14" t="inlineStr"/>
       <c r="BU14" t="inlineStr"/>
       <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2749,6 +3047,17 @@
       <c r="BT15" t="inlineStr"/>
       <c r="BU15" t="inlineStr"/>
       <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2889,6 +3198,33 @@
       <c r="BT16" t="inlineStr"/>
       <c r="BU16" t="inlineStr"/>
       <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3029,6 +3365,17 @@
       <c r="BT17" t="inlineStr"/>
       <c r="BU17" t="inlineStr"/>
       <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3169,6 +3516,17 @@
       <c r="BT18" t="inlineStr"/>
       <c r="BU18" t="inlineStr"/>
       <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="inlineStr"/>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="inlineStr"/>
+      <c r="CA18" t="inlineStr"/>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr"/>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3309,6 +3667,17 @@
       <c r="BT19" t="inlineStr"/>
       <c r="BU19" t="inlineStr"/>
       <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr"/>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr"/>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3449,6 +3818,33 @@
       <c r="BT20" t="inlineStr"/>
       <c r="BU20" t="inlineStr"/>
       <c r="BV20" t="inlineStr"/>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="inlineStr"/>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr"/>
+      <c r="CC20" t="inlineStr"/>
+      <c r="CD20" t="inlineStr"/>
+      <c r="CE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF20" t="inlineStr"/>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3589,6 +3985,17 @@
       <c r="BT21" t="inlineStr"/>
       <c r="BU21" t="inlineStr"/>
       <c r="BV21" t="inlineStr"/>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="inlineStr"/>
+      <c r="BZ21" t="inlineStr"/>
+      <c r="CA21" t="inlineStr"/>
+      <c r="CB21" t="inlineStr"/>
+      <c r="CC21" t="inlineStr"/>
+      <c r="CD21" t="inlineStr"/>
+      <c r="CE21" t="inlineStr"/>
+      <c r="CF21" t="inlineStr"/>
+      <c r="CG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3729,6 +4136,17 @@
       <c r="BT22" t="inlineStr"/>
       <c r="BU22" t="inlineStr"/>
       <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="inlineStr"/>
+      <c r="CA22" t="inlineStr"/>
+      <c r="CB22" t="inlineStr"/>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3869,6 +4287,17 @@
       <c r="BT23" t="inlineStr"/>
       <c r="BU23" t="inlineStr"/>
       <c r="BV23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="inlineStr"/>
+      <c r="CA23" t="inlineStr"/>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4009,6 +4438,17 @@
       <c r="BT24" t="inlineStr"/>
       <c r="BU24" t="inlineStr"/>
       <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr"/>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr"/>
+      <c r="CG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4149,6 +4589,33 @@
       <c r="BT25" t="inlineStr"/>
       <c r="BU25" t="inlineStr"/>
       <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr"/>
+      <c r="CE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF25" t="inlineStr"/>
+      <c r="CG25" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4289,6 +4756,33 @@
       <c r="BT26" t="inlineStr"/>
       <c r="BU26" t="inlineStr"/>
       <c r="BV26" t="inlineStr"/>
+      <c r="BW26" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="inlineStr"/>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr"/>
+      <c r="CC26" t="inlineStr"/>
+      <c r="CD26" t="inlineStr"/>
+      <c r="CE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF26" t="inlineStr"/>
+      <c r="CG26" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4429,6 +4923,17 @@
       <c r="BT27" t="inlineStr"/>
       <c r="BU27" t="inlineStr"/>
       <c r="BV27" t="inlineStr"/>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr"/>
+      <c r="BY27" t="inlineStr"/>
+      <c r="BZ27" t="inlineStr"/>
+      <c r="CA27" t="inlineStr"/>
+      <c r="CB27" t="inlineStr"/>
+      <c r="CC27" t="inlineStr"/>
+      <c r="CD27" t="inlineStr"/>
+      <c r="CE27" t="inlineStr"/>
+      <c r="CF27" t="inlineStr"/>
+      <c r="CG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4569,6 +5074,17 @@
       <c r="BT28" t="inlineStr"/>
       <c r="BU28" t="inlineStr"/>
       <c r="BV28" t="inlineStr"/>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr"/>
+      <c r="BY28" t="inlineStr"/>
+      <c r="BZ28" t="inlineStr"/>
+      <c r="CA28" t="inlineStr"/>
+      <c r="CB28" t="inlineStr"/>
+      <c r="CC28" t="inlineStr"/>
+      <c r="CD28" t="inlineStr"/>
+      <c r="CE28" t="inlineStr"/>
+      <c r="CF28" t="inlineStr"/>
+      <c r="CG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4709,6 +5225,33 @@
       <c r="BT29" t="inlineStr"/>
       <c r="BU29" t="inlineStr"/>
       <c r="BV29" t="inlineStr"/>
+      <c r="BW29" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="inlineStr"/>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr"/>
+      <c r="CC29" t="inlineStr"/>
+      <c r="CD29" t="inlineStr"/>
+      <c r="CE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF29" t="inlineStr"/>
+      <c r="CG29" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4849,6 +5392,33 @@
       <c r="BT30" t="inlineStr"/>
       <c r="BU30" t="inlineStr"/>
       <c r="BV30" t="inlineStr"/>
+      <c r="BW30" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY30" t="inlineStr"/>
+      <c r="BZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="inlineStr"/>
+      <c r="CC30" t="inlineStr"/>
+      <c r="CD30" t="inlineStr"/>
+      <c r="CE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF30" t="inlineStr"/>
+      <c r="CG30" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4989,6 +5559,17 @@
       <c r="BT31" t="inlineStr"/>
       <c r="BU31" t="inlineStr"/>
       <c r="BV31" t="inlineStr"/>
+      <c r="BW31" t="inlineStr"/>
+      <c r="BX31" t="inlineStr"/>
+      <c r="BY31" t="inlineStr"/>
+      <c r="BZ31" t="inlineStr"/>
+      <c r="CA31" t="inlineStr"/>
+      <c r="CB31" t="inlineStr"/>
+      <c r="CC31" t="inlineStr"/>
+      <c r="CD31" t="inlineStr"/>
+      <c r="CE31" t="inlineStr"/>
+      <c r="CF31" t="inlineStr"/>
+      <c r="CG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5127,6 +5708,17 @@
       <c r="BT32" t="inlineStr"/>
       <c r="BU32" t="inlineStr"/>
       <c r="BV32" t="inlineStr"/>
+      <c r="BW32" t="inlineStr"/>
+      <c r="BX32" t="inlineStr"/>
+      <c r="BY32" t="inlineStr"/>
+      <c r="BZ32" t="inlineStr"/>
+      <c r="CA32" t="inlineStr"/>
+      <c r="CB32" t="inlineStr"/>
+      <c r="CC32" t="inlineStr"/>
+      <c r="CD32" t="inlineStr"/>
+      <c r="CE32" t="inlineStr"/>
+      <c r="CF32" t="inlineStr"/>
+      <c r="CG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5265,6 +5857,17 @@
       <c r="BT33" t="inlineStr"/>
       <c r="BU33" t="inlineStr"/>
       <c r="BV33" t="inlineStr"/>
+      <c r="BW33" t="inlineStr"/>
+      <c r="BX33" t="inlineStr"/>
+      <c r="BY33" t="inlineStr"/>
+      <c r="BZ33" t="inlineStr"/>
+      <c r="CA33" t="inlineStr"/>
+      <c r="CB33" t="inlineStr"/>
+      <c r="CC33" t="inlineStr"/>
+      <c r="CD33" t="inlineStr"/>
+      <c r="CE33" t="inlineStr"/>
+      <c r="CF33" t="inlineStr"/>
+      <c r="CG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5403,6 +6006,17 @@
       <c r="BT34" t="inlineStr"/>
       <c r="BU34" t="inlineStr"/>
       <c r="BV34" t="inlineStr"/>
+      <c r="BW34" t="inlineStr"/>
+      <c r="BX34" t="inlineStr"/>
+      <c r="BY34" t="inlineStr"/>
+      <c r="BZ34" t="inlineStr"/>
+      <c r="CA34" t="inlineStr"/>
+      <c r="CB34" t="inlineStr"/>
+      <c r="CC34" t="inlineStr"/>
+      <c r="CD34" t="inlineStr"/>
+      <c r="CE34" t="inlineStr"/>
+      <c r="CF34" t="inlineStr"/>
+      <c r="CG34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5541,6 +6155,33 @@
       <c r="BT35" t="inlineStr"/>
       <c r="BU35" t="inlineStr"/>
       <c r="BV35" t="inlineStr"/>
+      <c r="BW35" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY35" t="inlineStr"/>
+      <c r="BZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="inlineStr"/>
+      <c r="CC35" t="inlineStr"/>
+      <c r="CD35" t="inlineStr"/>
+      <c r="CE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF35" t="inlineStr"/>
+      <c r="CG35" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5679,6 +6320,33 @@
       <c r="BT36" t="inlineStr"/>
       <c r="BU36" t="inlineStr"/>
       <c r="BV36" t="inlineStr"/>
+      <c r="BW36" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY36" t="inlineStr"/>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="inlineStr"/>
+      <c r="CC36" t="inlineStr"/>
+      <c r="CD36" t="inlineStr"/>
+      <c r="CE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF36" t="inlineStr"/>
+      <c r="CG36" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5817,6 +6485,33 @@
       <c r="BT37" t="inlineStr"/>
       <c r="BU37" t="inlineStr"/>
       <c r="BV37" t="inlineStr"/>
+      <c r="BW37" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY37" t="inlineStr"/>
+      <c r="BZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="inlineStr"/>
+      <c r="CC37" t="inlineStr"/>
+      <c r="CD37" t="inlineStr"/>
+      <c r="CE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF37" t="inlineStr"/>
+      <c r="CG37" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5955,6 +6650,33 @@
       <c r="BT38" t="inlineStr"/>
       <c r="BU38" t="inlineStr"/>
       <c r="BV38" t="inlineStr"/>
+      <c r="BW38" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY38" t="inlineStr"/>
+      <c r="BZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="inlineStr"/>
+      <c r="CC38" t="inlineStr"/>
+      <c r="CD38" t="inlineStr"/>
+      <c r="CE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF38" t="inlineStr"/>
+      <c r="CG38" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6095,6 +6817,17 @@
       <c r="BT39" t="inlineStr"/>
       <c r="BU39" t="inlineStr"/>
       <c r="BV39" t="inlineStr"/>
+      <c r="BW39" t="inlineStr"/>
+      <c r="BX39" t="inlineStr"/>
+      <c r="BY39" t="inlineStr"/>
+      <c r="BZ39" t="inlineStr"/>
+      <c r="CA39" t="inlineStr"/>
+      <c r="CB39" t="inlineStr"/>
+      <c r="CC39" t="inlineStr"/>
+      <c r="CD39" t="inlineStr"/>
+      <c r="CE39" t="inlineStr"/>
+      <c r="CF39" t="inlineStr"/>
+      <c r="CG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6235,6 +6968,33 @@
       <c r="BT40" t="inlineStr"/>
       <c r="BU40" t="inlineStr"/>
       <c r="BV40" t="inlineStr"/>
+      <c r="BW40" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY40" t="inlineStr"/>
+      <c r="BZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="inlineStr"/>
+      <c r="CC40" t="inlineStr"/>
+      <c r="CD40" t="inlineStr"/>
+      <c r="CE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF40" t="inlineStr"/>
+      <c r="CG40" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6375,6 +7135,33 @@
       <c r="BT41" t="inlineStr"/>
       <c r="BU41" t="inlineStr"/>
       <c r="BV41" t="inlineStr"/>
+      <c r="BW41" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY41" t="inlineStr"/>
+      <c r="BZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB41" t="inlineStr"/>
+      <c r="CC41" t="inlineStr"/>
+      <c r="CD41" t="inlineStr"/>
+      <c r="CE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF41" t="inlineStr"/>
+      <c r="CG41" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6515,6 +7302,33 @@
       <c r="BT42" t="inlineStr"/>
       <c r="BU42" t="inlineStr"/>
       <c r="BV42" t="inlineStr"/>
+      <c r="BW42" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY42" t="inlineStr"/>
+      <c r="BZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB42" t="inlineStr"/>
+      <c r="CC42" t="inlineStr"/>
+      <c r="CD42" t="inlineStr"/>
+      <c r="CE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF42" t="inlineStr"/>
+      <c r="CG42" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6655,6 +7469,17 @@
       <c r="BT43" t="inlineStr"/>
       <c r="BU43" t="inlineStr"/>
       <c r="BV43" t="inlineStr"/>
+      <c r="BW43" t="inlineStr"/>
+      <c r="BX43" t="inlineStr"/>
+      <c r="BY43" t="inlineStr"/>
+      <c r="BZ43" t="inlineStr"/>
+      <c r="CA43" t="inlineStr"/>
+      <c r="CB43" t="inlineStr"/>
+      <c r="CC43" t="inlineStr"/>
+      <c r="CD43" t="inlineStr"/>
+      <c r="CE43" t="inlineStr"/>
+      <c r="CF43" t="inlineStr"/>
+      <c r="CG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6795,6 +7620,33 @@
       <c r="BT44" t="inlineStr"/>
       <c r="BU44" t="inlineStr"/>
       <c r="BV44" t="inlineStr"/>
+      <c r="BW44" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY44" t="inlineStr"/>
+      <c r="BZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB44" t="inlineStr"/>
+      <c r="CC44" t="inlineStr"/>
+      <c r="CD44" t="inlineStr"/>
+      <c r="CE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF44" t="inlineStr"/>
+      <c r="CG44" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6935,6 +7787,17 @@
       <c r="BT45" t="inlineStr"/>
       <c r="BU45" t="inlineStr"/>
       <c r="BV45" t="inlineStr"/>
+      <c r="BW45" t="inlineStr"/>
+      <c r="BX45" t="inlineStr"/>
+      <c r="BY45" t="inlineStr"/>
+      <c r="BZ45" t="inlineStr"/>
+      <c r="CA45" t="inlineStr"/>
+      <c r="CB45" t="inlineStr"/>
+      <c r="CC45" t="inlineStr"/>
+      <c r="CD45" t="inlineStr"/>
+      <c r="CE45" t="inlineStr"/>
+      <c r="CF45" t="inlineStr"/>
+      <c r="CG45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7075,6 +7938,33 @@
       <c r="BT46" t="inlineStr"/>
       <c r="BU46" t="inlineStr"/>
       <c r="BV46" t="inlineStr"/>
+      <c r="BW46" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY46" t="inlineStr"/>
+      <c r="BZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB46" t="inlineStr"/>
+      <c r="CC46" t="inlineStr"/>
+      <c r="CD46" t="inlineStr"/>
+      <c r="CE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF46" t="inlineStr"/>
+      <c r="CG46" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7215,6 +8105,33 @@
       <c r="BT47" t="inlineStr"/>
       <c r="BU47" t="inlineStr"/>
       <c r="BV47" t="inlineStr"/>
+      <c r="BW47" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY47" t="inlineStr"/>
+      <c r="BZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB47" t="inlineStr"/>
+      <c r="CC47" t="inlineStr"/>
+      <c r="CD47" t="inlineStr"/>
+      <c r="CE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF47" t="inlineStr"/>
+      <c r="CG47" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7355,6 +8272,17 @@
       <c r="BT48" t="inlineStr"/>
       <c r="BU48" t="inlineStr"/>
       <c r="BV48" t="inlineStr"/>
+      <c r="BW48" t="inlineStr"/>
+      <c r="BX48" t="inlineStr"/>
+      <c r="BY48" t="inlineStr"/>
+      <c r="BZ48" t="inlineStr"/>
+      <c r="CA48" t="inlineStr"/>
+      <c r="CB48" t="inlineStr"/>
+      <c r="CC48" t="inlineStr"/>
+      <c r="CD48" t="inlineStr"/>
+      <c r="CE48" t="inlineStr"/>
+      <c r="CF48" t="inlineStr"/>
+      <c r="CG48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7495,6 +8423,33 @@
       <c r="BT49" t="inlineStr"/>
       <c r="BU49" t="inlineStr"/>
       <c r="BV49" t="inlineStr"/>
+      <c r="BW49" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY49" t="inlineStr"/>
+      <c r="BZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB49" t="inlineStr"/>
+      <c r="CC49" t="inlineStr"/>
+      <c r="CD49" t="inlineStr"/>
+      <c r="CE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF49" t="inlineStr"/>
+      <c r="CG49" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7635,6 +8590,17 @@
       <c r="BT50" t="inlineStr"/>
       <c r="BU50" t="inlineStr"/>
       <c r="BV50" t="inlineStr"/>
+      <c r="BW50" t="inlineStr"/>
+      <c r="BX50" t="inlineStr"/>
+      <c r="BY50" t="inlineStr"/>
+      <c r="BZ50" t="inlineStr"/>
+      <c r="CA50" t="inlineStr"/>
+      <c r="CB50" t="inlineStr"/>
+      <c r="CC50" t="inlineStr"/>
+      <c r="CD50" t="inlineStr"/>
+      <c r="CE50" t="inlineStr"/>
+      <c r="CF50" t="inlineStr"/>
+      <c r="CG50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7775,6 +8741,33 @@
       <c r="BT51" t="inlineStr"/>
       <c r="BU51" t="inlineStr"/>
       <c r="BV51" t="inlineStr"/>
+      <c r="BW51" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY51" t="inlineStr"/>
+      <c r="BZ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB51" t="inlineStr"/>
+      <c r="CC51" t="inlineStr"/>
+      <c r="CD51" t="inlineStr"/>
+      <c r="CE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF51" t="inlineStr"/>
+      <c r="CG51" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7915,6 +8908,33 @@
       <c r="BT52" t="inlineStr"/>
       <c r="BU52" t="inlineStr"/>
       <c r="BV52" t="inlineStr"/>
+      <c r="BW52" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY52" t="inlineStr"/>
+      <c r="BZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB52" t="inlineStr"/>
+      <c r="CC52" t="inlineStr"/>
+      <c r="CD52" t="inlineStr"/>
+      <c r="CE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF52" t="inlineStr"/>
+      <c r="CG52" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8055,6 +9075,17 @@
       <c r="BT53" t="inlineStr"/>
       <c r="BU53" t="inlineStr"/>
       <c r="BV53" t="inlineStr"/>
+      <c r="BW53" t="inlineStr"/>
+      <c r="BX53" t="inlineStr"/>
+      <c r="BY53" t="inlineStr"/>
+      <c r="BZ53" t="inlineStr"/>
+      <c r="CA53" t="inlineStr"/>
+      <c r="CB53" t="inlineStr"/>
+      <c r="CC53" t="inlineStr"/>
+      <c r="CD53" t="inlineStr"/>
+      <c r="CE53" t="inlineStr"/>
+      <c r="CF53" t="inlineStr"/>
+      <c r="CG53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8195,6 +9226,17 @@
       <c r="BT54" t="inlineStr"/>
       <c r="BU54" t="inlineStr"/>
       <c r="BV54" t="inlineStr"/>
+      <c r="BW54" t="inlineStr"/>
+      <c r="BX54" t="inlineStr"/>
+      <c r="BY54" t="inlineStr"/>
+      <c r="BZ54" t="inlineStr"/>
+      <c r="CA54" t="inlineStr"/>
+      <c r="CB54" t="inlineStr"/>
+      <c r="CC54" t="inlineStr"/>
+      <c r="CD54" t="inlineStr"/>
+      <c r="CE54" t="inlineStr"/>
+      <c r="CF54" t="inlineStr"/>
+      <c r="CG54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8335,6 +9377,17 @@
       <c r="BT55" t="inlineStr"/>
       <c r="BU55" t="inlineStr"/>
       <c r="BV55" t="inlineStr"/>
+      <c r="BW55" t="inlineStr"/>
+      <c r="BX55" t="inlineStr"/>
+      <c r="BY55" t="inlineStr"/>
+      <c r="BZ55" t="inlineStr"/>
+      <c r="CA55" t="inlineStr"/>
+      <c r="CB55" t="inlineStr"/>
+      <c r="CC55" t="inlineStr"/>
+      <c r="CD55" t="inlineStr"/>
+      <c r="CE55" t="inlineStr"/>
+      <c r="CF55" t="inlineStr"/>
+      <c r="CG55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8475,6 +9528,17 @@
       <c r="BT56" t="inlineStr"/>
       <c r="BU56" t="inlineStr"/>
       <c r="BV56" t="inlineStr"/>
+      <c r="BW56" t="inlineStr"/>
+      <c r="BX56" t="inlineStr"/>
+      <c r="BY56" t="inlineStr"/>
+      <c r="BZ56" t="inlineStr"/>
+      <c r="CA56" t="inlineStr"/>
+      <c r="CB56" t="inlineStr"/>
+      <c r="CC56" t="inlineStr"/>
+      <c r="CD56" t="inlineStr"/>
+      <c r="CE56" t="inlineStr"/>
+      <c r="CF56" t="inlineStr"/>
+      <c r="CG56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8615,6 +9679,17 @@
       <c r="BT57" t="inlineStr"/>
       <c r="BU57" t="inlineStr"/>
       <c r="BV57" t="inlineStr"/>
+      <c r="BW57" t="inlineStr"/>
+      <c r="BX57" t="inlineStr"/>
+      <c r="BY57" t="inlineStr"/>
+      <c r="BZ57" t="inlineStr"/>
+      <c r="CA57" t="inlineStr"/>
+      <c r="CB57" t="inlineStr"/>
+      <c r="CC57" t="inlineStr"/>
+      <c r="CD57" t="inlineStr"/>
+      <c r="CE57" t="inlineStr"/>
+      <c r="CF57" t="inlineStr"/>
+      <c r="CG57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8755,6 +9830,33 @@
       <c r="BT58" t="inlineStr"/>
       <c r="BU58" t="inlineStr"/>
       <c r="BV58" t="inlineStr"/>
+      <c r="BW58" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY58" t="inlineStr"/>
+      <c r="BZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB58" t="inlineStr"/>
+      <c r="CC58" t="inlineStr"/>
+      <c r="CD58" t="inlineStr"/>
+      <c r="CE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF58" t="inlineStr"/>
+      <c r="CG58" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8895,6 +9997,17 @@
       <c r="BT59" t="inlineStr"/>
       <c r="BU59" t="inlineStr"/>
       <c r="BV59" t="inlineStr"/>
+      <c r="BW59" t="inlineStr"/>
+      <c r="BX59" t="inlineStr"/>
+      <c r="BY59" t="inlineStr"/>
+      <c r="BZ59" t="inlineStr"/>
+      <c r="CA59" t="inlineStr"/>
+      <c r="CB59" t="inlineStr"/>
+      <c r="CC59" t="inlineStr"/>
+      <c r="CD59" t="inlineStr"/>
+      <c r="CE59" t="inlineStr"/>
+      <c r="CF59" t="inlineStr"/>
+      <c r="CG59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9035,6 +10148,17 @@
       <c r="BT60" t="inlineStr"/>
       <c r="BU60" t="inlineStr"/>
       <c r="BV60" t="inlineStr"/>
+      <c r="BW60" t="inlineStr"/>
+      <c r="BX60" t="inlineStr"/>
+      <c r="BY60" t="inlineStr"/>
+      <c r="BZ60" t="inlineStr"/>
+      <c r="CA60" t="inlineStr"/>
+      <c r="CB60" t="inlineStr"/>
+      <c r="CC60" t="inlineStr"/>
+      <c r="CD60" t="inlineStr"/>
+      <c r="CE60" t="inlineStr"/>
+      <c r="CF60" t="inlineStr"/>
+      <c r="CG60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9175,6 +10299,17 @@
       <c r="BT61" t="inlineStr"/>
       <c r="BU61" t="inlineStr"/>
       <c r="BV61" t="inlineStr"/>
+      <c r="BW61" t="inlineStr"/>
+      <c r="BX61" t="inlineStr"/>
+      <c r="BY61" t="inlineStr"/>
+      <c r="BZ61" t="inlineStr"/>
+      <c r="CA61" t="inlineStr"/>
+      <c r="CB61" t="inlineStr"/>
+      <c r="CC61" t="inlineStr"/>
+      <c r="CD61" t="inlineStr"/>
+      <c r="CE61" t="inlineStr"/>
+      <c r="CF61" t="inlineStr"/>
+      <c r="CG61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9315,6 +10450,17 @@
       <c r="BT62" t="inlineStr"/>
       <c r="BU62" t="inlineStr"/>
       <c r="BV62" t="inlineStr"/>
+      <c r="BW62" t="inlineStr"/>
+      <c r="BX62" t="inlineStr"/>
+      <c r="BY62" t="inlineStr"/>
+      <c r="BZ62" t="inlineStr"/>
+      <c r="CA62" t="inlineStr"/>
+      <c r="CB62" t="inlineStr"/>
+      <c r="CC62" t="inlineStr"/>
+      <c r="CD62" t="inlineStr"/>
+      <c r="CE62" t="inlineStr"/>
+      <c r="CF62" t="inlineStr"/>
+      <c r="CG62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9455,6 +10601,17 @@
       <c r="BT63" t="inlineStr"/>
       <c r="BU63" t="inlineStr"/>
       <c r="BV63" t="inlineStr"/>
+      <c r="BW63" t="inlineStr"/>
+      <c r="BX63" t="inlineStr"/>
+      <c r="BY63" t="inlineStr"/>
+      <c r="BZ63" t="inlineStr"/>
+      <c r="CA63" t="inlineStr"/>
+      <c r="CB63" t="inlineStr"/>
+      <c r="CC63" t="inlineStr"/>
+      <c r="CD63" t="inlineStr"/>
+      <c r="CE63" t="inlineStr"/>
+      <c r="CF63" t="inlineStr"/>
+      <c r="CG63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9595,6 +10752,17 @@
       <c r="BT64" t="inlineStr"/>
       <c r="BU64" t="inlineStr"/>
       <c r="BV64" t="inlineStr"/>
+      <c r="BW64" t="inlineStr"/>
+      <c r="BX64" t="inlineStr"/>
+      <c r="BY64" t="inlineStr"/>
+      <c r="BZ64" t="inlineStr"/>
+      <c r="CA64" t="inlineStr"/>
+      <c r="CB64" t="inlineStr"/>
+      <c r="CC64" t="inlineStr"/>
+      <c r="CD64" t="inlineStr"/>
+      <c r="CE64" t="inlineStr"/>
+      <c r="CF64" t="inlineStr"/>
+      <c r="CG64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9735,6 +10903,17 @@
       <c r="BT65" t="inlineStr"/>
       <c r="BU65" t="inlineStr"/>
       <c r="BV65" t="inlineStr"/>
+      <c r="BW65" t="inlineStr"/>
+      <c r="BX65" t="inlineStr"/>
+      <c r="BY65" t="inlineStr"/>
+      <c r="BZ65" t="inlineStr"/>
+      <c r="CA65" t="inlineStr"/>
+      <c r="CB65" t="inlineStr"/>
+      <c r="CC65" t="inlineStr"/>
+      <c r="CD65" t="inlineStr"/>
+      <c r="CE65" t="inlineStr"/>
+      <c r="CF65" t="inlineStr"/>
+      <c r="CG65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9875,6 +11054,17 @@
       <c r="BT66" t="inlineStr"/>
       <c r="BU66" t="inlineStr"/>
       <c r="BV66" t="inlineStr"/>
+      <c r="BW66" t="inlineStr"/>
+      <c r="BX66" t="inlineStr"/>
+      <c r="BY66" t="inlineStr"/>
+      <c r="BZ66" t="inlineStr"/>
+      <c r="CA66" t="inlineStr"/>
+      <c r="CB66" t="inlineStr"/>
+      <c r="CC66" t="inlineStr"/>
+      <c r="CD66" t="inlineStr"/>
+      <c r="CE66" t="inlineStr"/>
+      <c r="CF66" t="inlineStr"/>
+      <c r="CG66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -10015,6 +11205,17 @@
       <c r="BT67" t="inlineStr"/>
       <c r="BU67" t="inlineStr"/>
       <c r="BV67" t="inlineStr"/>
+      <c r="BW67" t="inlineStr"/>
+      <c r="BX67" t="inlineStr"/>
+      <c r="BY67" t="inlineStr"/>
+      <c r="BZ67" t="inlineStr"/>
+      <c r="CA67" t="inlineStr"/>
+      <c r="CB67" t="inlineStr"/>
+      <c r="CC67" t="inlineStr"/>
+      <c r="CD67" t="inlineStr"/>
+      <c r="CE67" t="inlineStr"/>
+      <c r="CF67" t="inlineStr"/>
+      <c r="CG67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10155,6 +11356,17 @@
       <c r="BT68" t="inlineStr"/>
       <c r="BU68" t="inlineStr"/>
       <c r="BV68" t="inlineStr"/>
+      <c r="BW68" t="inlineStr"/>
+      <c r="BX68" t="inlineStr"/>
+      <c r="BY68" t="inlineStr"/>
+      <c r="BZ68" t="inlineStr"/>
+      <c r="CA68" t="inlineStr"/>
+      <c r="CB68" t="inlineStr"/>
+      <c r="CC68" t="inlineStr"/>
+      <c r="CD68" t="inlineStr"/>
+      <c r="CE68" t="inlineStr"/>
+      <c r="CF68" t="inlineStr"/>
+      <c r="CG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10293,6 +11505,33 @@
       <c r="BT69" t="inlineStr"/>
       <c r="BU69" t="inlineStr"/>
       <c r="BV69" t="inlineStr"/>
+      <c r="BW69" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY69" t="inlineStr"/>
+      <c r="BZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB69" t="inlineStr"/>
+      <c r="CC69" t="inlineStr"/>
+      <c r="CD69" t="inlineStr"/>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="inlineStr"/>
+      <c r="CG69" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10431,6 +11670,17 @@
       <c r="BT70" t="inlineStr"/>
       <c r="BU70" t="inlineStr"/>
       <c r="BV70" t="inlineStr"/>
+      <c r="BW70" t="inlineStr"/>
+      <c r="BX70" t="inlineStr"/>
+      <c r="BY70" t="inlineStr"/>
+      <c r="BZ70" t="inlineStr"/>
+      <c r="CA70" t="inlineStr"/>
+      <c r="CB70" t="inlineStr"/>
+      <c r="CC70" t="inlineStr"/>
+      <c r="CD70" t="inlineStr"/>
+      <c r="CE70" t="inlineStr"/>
+      <c r="CF70" t="inlineStr"/>
+      <c r="CG70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10569,6 +11819,17 @@
       <c r="BT71" t="inlineStr"/>
       <c r="BU71" t="inlineStr"/>
       <c r="BV71" t="inlineStr"/>
+      <c r="BW71" t="inlineStr"/>
+      <c r="BX71" t="inlineStr"/>
+      <c r="BY71" t="inlineStr"/>
+      <c r="BZ71" t="inlineStr"/>
+      <c r="CA71" t="inlineStr"/>
+      <c r="CB71" t="inlineStr"/>
+      <c r="CC71" t="inlineStr"/>
+      <c r="CD71" t="inlineStr"/>
+      <c r="CE71" t="inlineStr"/>
+      <c r="CF71" t="inlineStr"/>
+      <c r="CG71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10707,6 +11968,17 @@
       <c r="BT72" t="inlineStr"/>
       <c r="BU72" t="inlineStr"/>
       <c r="BV72" t="inlineStr"/>
+      <c r="BW72" t="inlineStr"/>
+      <c r="BX72" t="inlineStr"/>
+      <c r="BY72" t="inlineStr"/>
+      <c r="BZ72" t="inlineStr"/>
+      <c r="CA72" t="inlineStr"/>
+      <c r="CB72" t="inlineStr"/>
+      <c r="CC72" t="inlineStr"/>
+      <c r="CD72" t="inlineStr"/>
+      <c r="CE72" t="inlineStr"/>
+      <c r="CF72" t="inlineStr"/>
+      <c r="CG72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10845,6 +12117,17 @@
       <c r="BT73" t="inlineStr"/>
       <c r="BU73" t="inlineStr"/>
       <c r="BV73" t="inlineStr"/>
+      <c r="BW73" t="inlineStr"/>
+      <c r="BX73" t="inlineStr"/>
+      <c r="BY73" t="inlineStr"/>
+      <c r="BZ73" t="inlineStr"/>
+      <c r="CA73" t="inlineStr"/>
+      <c r="CB73" t="inlineStr"/>
+      <c r="CC73" t="inlineStr"/>
+      <c r="CD73" t="inlineStr"/>
+      <c r="CE73" t="inlineStr"/>
+      <c r="CF73" t="inlineStr"/>
+      <c r="CG73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10983,6 +12266,17 @@
       <c r="BT74" t="inlineStr"/>
       <c r="BU74" t="inlineStr"/>
       <c r="BV74" t="inlineStr"/>
+      <c r="BW74" t="inlineStr"/>
+      <c r="BX74" t="inlineStr"/>
+      <c r="BY74" t="inlineStr"/>
+      <c r="BZ74" t="inlineStr"/>
+      <c r="CA74" t="inlineStr"/>
+      <c r="CB74" t="inlineStr"/>
+      <c r="CC74" t="inlineStr"/>
+      <c r="CD74" t="inlineStr"/>
+      <c r="CE74" t="inlineStr"/>
+      <c r="CF74" t="inlineStr"/>
+      <c r="CG74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11121,6 +12415,17 @@
       <c r="BT75" t="inlineStr"/>
       <c r="BU75" t="inlineStr"/>
       <c r="BV75" t="inlineStr"/>
+      <c r="BW75" t="inlineStr"/>
+      <c r="BX75" t="inlineStr"/>
+      <c r="BY75" t="inlineStr"/>
+      <c r="BZ75" t="inlineStr"/>
+      <c r="CA75" t="inlineStr"/>
+      <c r="CB75" t="inlineStr"/>
+      <c r="CC75" t="inlineStr"/>
+      <c r="CD75" t="inlineStr"/>
+      <c r="CE75" t="inlineStr"/>
+      <c r="CF75" t="inlineStr"/>
+      <c r="CG75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11259,6 +12564,17 @@
       <c r="BT76" t="inlineStr"/>
       <c r="BU76" t="inlineStr"/>
       <c r="BV76" t="inlineStr"/>
+      <c r="BW76" t="inlineStr"/>
+      <c r="BX76" t="inlineStr"/>
+      <c r="BY76" t="inlineStr"/>
+      <c r="BZ76" t="inlineStr"/>
+      <c r="CA76" t="inlineStr"/>
+      <c r="CB76" t="inlineStr"/>
+      <c r="CC76" t="inlineStr"/>
+      <c r="CD76" t="inlineStr"/>
+      <c r="CE76" t="inlineStr"/>
+      <c r="CF76" t="inlineStr"/>
+      <c r="CG76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11397,6 +12713,17 @@
       <c r="BT77" t="inlineStr"/>
       <c r="BU77" t="inlineStr"/>
       <c r="BV77" t="inlineStr"/>
+      <c r="BW77" t="inlineStr"/>
+      <c r="BX77" t="inlineStr"/>
+      <c r="BY77" t="inlineStr"/>
+      <c r="BZ77" t="inlineStr"/>
+      <c r="CA77" t="inlineStr"/>
+      <c r="CB77" t="inlineStr"/>
+      <c r="CC77" t="inlineStr"/>
+      <c r="CD77" t="inlineStr"/>
+      <c r="CE77" t="inlineStr"/>
+      <c r="CF77" t="inlineStr"/>
+      <c r="CG77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11535,6 +12862,17 @@
       <c r="BT78" t="inlineStr"/>
       <c r="BU78" t="inlineStr"/>
       <c r="BV78" t="inlineStr"/>
+      <c r="BW78" t="inlineStr"/>
+      <c r="BX78" t="inlineStr"/>
+      <c r="BY78" t="inlineStr"/>
+      <c r="BZ78" t="inlineStr"/>
+      <c r="CA78" t="inlineStr"/>
+      <c r="CB78" t="inlineStr"/>
+      <c r="CC78" t="inlineStr"/>
+      <c r="CD78" t="inlineStr"/>
+      <c r="CE78" t="inlineStr"/>
+      <c r="CF78" t="inlineStr"/>
+      <c r="CG78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11673,6 +13011,17 @@
       <c r="BT79" t="inlineStr"/>
       <c r="BU79" t="inlineStr"/>
       <c r="BV79" t="inlineStr"/>
+      <c r="BW79" t="inlineStr"/>
+      <c r="BX79" t="inlineStr"/>
+      <c r="BY79" t="inlineStr"/>
+      <c r="BZ79" t="inlineStr"/>
+      <c r="CA79" t="inlineStr"/>
+      <c r="CB79" t="inlineStr"/>
+      <c r="CC79" t="inlineStr"/>
+      <c r="CD79" t="inlineStr"/>
+      <c r="CE79" t="inlineStr"/>
+      <c r="CF79" t="inlineStr"/>
+      <c r="CG79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11895,6 +13244,33 @@
       <c r="BT80" t="inlineStr"/>
       <c r="BU80" t="inlineStr"/>
       <c r="BV80" t="inlineStr"/>
+      <c r="BW80" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY80" t="inlineStr"/>
+      <c r="BZ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB80" t="inlineStr"/>
+      <c r="CC80" t="inlineStr"/>
+      <c r="CD80" t="inlineStr"/>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="inlineStr"/>
+      <c r="CG80" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -12117,6 +13493,33 @@
       <c r="BT81" t="inlineStr"/>
       <c r="BU81" t="inlineStr"/>
       <c r="BV81" t="inlineStr"/>
+      <c r="BW81" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY81" t="inlineStr"/>
+      <c r="BZ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB81" t="inlineStr"/>
+      <c r="CC81" t="inlineStr"/>
+      <c r="CD81" t="inlineStr"/>
+      <c r="CE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF81" t="inlineStr"/>
+      <c r="CG81" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -12339,6 +13742,33 @@
       <c r="BT82" t="inlineStr"/>
       <c r="BU82" t="inlineStr"/>
       <c r="BV82" t="inlineStr"/>
+      <c r="BW82" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY82" t="inlineStr"/>
+      <c r="BZ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB82" t="inlineStr"/>
+      <c r="CC82" t="inlineStr"/>
+      <c r="CD82" t="inlineStr"/>
+      <c r="CE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF82" t="inlineStr"/>
+      <c r="CG82" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12561,6 +13991,33 @@
       <c r="BT83" t="inlineStr"/>
       <c r="BU83" t="inlineStr"/>
       <c r="BV83" t="inlineStr"/>
+      <c r="BW83" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY83" t="inlineStr"/>
+      <c r="BZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB83" t="inlineStr"/>
+      <c r="CC83" t="inlineStr"/>
+      <c r="CD83" t="inlineStr"/>
+      <c r="CE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF83" t="inlineStr"/>
+      <c r="CG83" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12783,6 +14240,33 @@
       <c r="BT84" t="inlineStr"/>
       <c r="BU84" t="inlineStr"/>
       <c r="BV84" t="inlineStr"/>
+      <c r="BW84" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY84" t="inlineStr"/>
+      <c r="BZ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB84" t="inlineStr"/>
+      <c r="CC84" t="inlineStr"/>
+      <c r="CD84" t="inlineStr"/>
+      <c r="CE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF84" t="inlineStr"/>
+      <c r="CG84" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -13005,6 +14489,33 @@
       <c r="BT85" t="inlineStr"/>
       <c r="BU85" t="inlineStr"/>
       <c r="BV85" t="inlineStr"/>
+      <c r="BW85" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY85" t="inlineStr"/>
+      <c r="BZ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB85" t="inlineStr"/>
+      <c r="CC85" t="inlineStr"/>
+      <c r="CD85" t="inlineStr"/>
+      <c r="CE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF85" t="inlineStr"/>
+      <c r="CG85" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -13227,6 +14738,17 @@
       <c r="BT86" t="inlineStr"/>
       <c r="BU86" t="inlineStr"/>
       <c r="BV86" t="inlineStr"/>
+      <c r="BW86" t="inlineStr"/>
+      <c r="BX86" t="inlineStr"/>
+      <c r="BY86" t="inlineStr"/>
+      <c r="BZ86" t="inlineStr"/>
+      <c r="CA86" t="inlineStr"/>
+      <c r="CB86" t="inlineStr"/>
+      <c r="CC86" t="inlineStr"/>
+      <c r="CD86" t="inlineStr"/>
+      <c r="CE86" t="inlineStr"/>
+      <c r="CF86" t="inlineStr"/>
+      <c r="CG86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -13449,6 +14971,17 @@
       <c r="BT87" t="inlineStr"/>
       <c r="BU87" t="inlineStr"/>
       <c r="BV87" t="inlineStr"/>
+      <c r="BW87" t="inlineStr"/>
+      <c r="BX87" t="inlineStr"/>
+      <c r="BY87" t="inlineStr"/>
+      <c r="BZ87" t="inlineStr"/>
+      <c r="CA87" t="inlineStr"/>
+      <c r="CB87" t="inlineStr"/>
+      <c r="CC87" t="inlineStr"/>
+      <c r="CD87" t="inlineStr"/>
+      <c r="CE87" t="inlineStr"/>
+      <c r="CF87" t="inlineStr"/>
+      <c r="CG87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -13671,6 +15204,33 @@
       <c r="BT88" t="inlineStr"/>
       <c r="BU88" t="inlineStr"/>
       <c r="BV88" t="inlineStr"/>
+      <c r="BW88" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY88" t="inlineStr"/>
+      <c r="BZ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB88" t="inlineStr"/>
+      <c r="CC88" t="inlineStr"/>
+      <c r="CD88" t="inlineStr"/>
+      <c r="CE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF88" t="inlineStr"/>
+      <c r="CG88" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -13893,6 +15453,33 @@
       <c r="BT89" t="inlineStr"/>
       <c r="BU89" t="inlineStr"/>
       <c r="BV89" t="inlineStr"/>
+      <c r="BW89" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY89" t="inlineStr"/>
+      <c r="BZ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB89" t="inlineStr"/>
+      <c r="CC89" t="inlineStr"/>
+      <c r="CD89" t="inlineStr"/>
+      <c r="CE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF89" t="inlineStr"/>
+      <c r="CG89" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -14115,6 +15702,17 @@
       <c r="BT90" t="inlineStr"/>
       <c r="BU90" t="inlineStr"/>
       <c r="BV90" t="inlineStr"/>
+      <c r="BW90" t="inlineStr"/>
+      <c r="BX90" t="inlineStr"/>
+      <c r="BY90" t="inlineStr"/>
+      <c r="BZ90" t="inlineStr"/>
+      <c r="CA90" t="inlineStr"/>
+      <c r="CB90" t="inlineStr"/>
+      <c r="CC90" t="inlineStr"/>
+      <c r="CD90" t="inlineStr"/>
+      <c r="CE90" t="inlineStr"/>
+      <c r="CF90" t="inlineStr"/>
+      <c r="CG90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -14337,6 +15935,17 @@
       <c r="BT91" t="inlineStr"/>
       <c r="BU91" t="inlineStr"/>
       <c r="BV91" t="inlineStr"/>
+      <c r="BW91" t="inlineStr"/>
+      <c r="BX91" t="inlineStr"/>
+      <c r="BY91" t="inlineStr"/>
+      <c r="BZ91" t="inlineStr"/>
+      <c r="CA91" t="inlineStr"/>
+      <c r="CB91" t="inlineStr"/>
+      <c r="CC91" t="inlineStr"/>
+      <c r="CD91" t="inlineStr"/>
+      <c r="CE91" t="inlineStr"/>
+      <c r="CF91" t="inlineStr"/>
+      <c r="CG91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -14559,6 +16168,33 @@
       <c r="BT92" t="inlineStr"/>
       <c r="BU92" t="inlineStr"/>
       <c r="BV92" t="inlineStr"/>
+      <c r="BW92" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY92" t="inlineStr"/>
+      <c r="BZ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB92" t="inlineStr"/>
+      <c r="CC92" t="inlineStr"/>
+      <c r="CD92" t="inlineStr"/>
+      <c r="CE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF92" t="inlineStr"/>
+      <c r="CG92" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -14785,6 +16421,33 @@
       <c r="BT93" t="inlineStr"/>
       <c r="BU93" t="inlineStr"/>
       <c r="BV93" t="inlineStr"/>
+      <c r="BW93" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY93" t="inlineStr"/>
+      <c r="BZ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB93" t="inlineStr"/>
+      <c r="CC93" t="inlineStr"/>
+      <c r="CD93" t="inlineStr"/>
+      <c r="CE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF93" t="inlineStr"/>
+      <c r="CG93" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -15011,6 +16674,33 @@
       <c r="BT94" t="inlineStr"/>
       <c r="BU94" t="inlineStr"/>
       <c r="BV94" t="inlineStr"/>
+      <c r="BW94" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY94" t="inlineStr"/>
+      <c r="BZ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB94" t="inlineStr"/>
+      <c r="CC94" t="inlineStr"/>
+      <c r="CD94" t="inlineStr"/>
+      <c r="CE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF94" t="inlineStr"/>
+      <c r="CG94" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -15233,6 +16923,17 @@
       <c r="BT95" t="inlineStr"/>
       <c r="BU95" t="inlineStr"/>
       <c r="BV95" t="inlineStr"/>
+      <c r="BW95" t="inlineStr"/>
+      <c r="BX95" t="inlineStr"/>
+      <c r="BY95" t="inlineStr"/>
+      <c r="BZ95" t="inlineStr"/>
+      <c r="CA95" t="inlineStr"/>
+      <c r="CB95" t="inlineStr"/>
+      <c r="CC95" t="inlineStr"/>
+      <c r="CD95" t="inlineStr"/>
+      <c r="CE95" t="inlineStr"/>
+      <c r="CF95" t="inlineStr"/>
+      <c r="CG95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -15459,6 +17160,33 @@
       <c r="BT96" t="inlineStr"/>
       <c r="BU96" t="inlineStr"/>
       <c r="BV96" t="inlineStr"/>
+      <c r="BW96" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY96" t="inlineStr"/>
+      <c r="BZ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB96" t="inlineStr"/>
+      <c r="CC96" t="inlineStr"/>
+      <c r="CD96" t="inlineStr"/>
+      <c r="CE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF96" t="inlineStr"/>
+      <c r="CG96" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -15685,6 +17413,33 @@
       <c r="BT97" t="inlineStr"/>
       <c r="BU97" t="inlineStr"/>
       <c r="BV97" t="inlineStr"/>
+      <c r="BW97" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY97" t="inlineStr"/>
+      <c r="BZ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB97" t="inlineStr"/>
+      <c r="CC97" t="inlineStr"/>
+      <c r="CD97" t="inlineStr"/>
+      <c r="CE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF97" t="inlineStr"/>
+      <c r="CG97" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -15911,6 +17666,17 @@
       <c r="BT98" t="inlineStr"/>
       <c r="BU98" t="inlineStr"/>
       <c r="BV98" t="inlineStr"/>
+      <c r="BW98" t="inlineStr"/>
+      <c r="BX98" t="inlineStr"/>
+      <c r="BY98" t="inlineStr"/>
+      <c r="BZ98" t="inlineStr"/>
+      <c r="CA98" t="inlineStr"/>
+      <c r="CB98" t="inlineStr"/>
+      <c r="CC98" t="inlineStr"/>
+      <c r="CD98" t="inlineStr"/>
+      <c r="CE98" t="inlineStr"/>
+      <c r="CF98" t="inlineStr"/>
+      <c r="CG98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -16137,6 +17903,33 @@
       <c r="BT99" t="inlineStr"/>
       <c r="BU99" t="inlineStr"/>
       <c r="BV99" t="inlineStr"/>
+      <c r="BW99" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY99" t="inlineStr"/>
+      <c r="BZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB99" t="inlineStr"/>
+      <c r="CC99" t="inlineStr"/>
+      <c r="CD99" t="inlineStr"/>
+      <c r="CE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF99" t="inlineStr"/>
+      <c r="CG99" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -16363,6 +18156,33 @@
       <c r="BT100" t="inlineStr"/>
       <c r="BU100" t="inlineStr"/>
       <c r="BV100" t="inlineStr"/>
+      <c r="BW100" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY100" t="inlineStr"/>
+      <c r="BZ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB100" t="inlineStr"/>
+      <c r="CC100" t="inlineStr"/>
+      <c r="CD100" t="inlineStr"/>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="inlineStr"/>
+      <c r="CG100" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -16589,6 +18409,17 @@
       <c r="BT101" t="inlineStr"/>
       <c r="BU101" t="inlineStr"/>
       <c r="BV101" t="inlineStr"/>
+      <c r="BW101" t="inlineStr"/>
+      <c r="BX101" t="inlineStr"/>
+      <c r="BY101" t="inlineStr"/>
+      <c r="BZ101" t="inlineStr"/>
+      <c r="CA101" t="inlineStr"/>
+      <c r="CB101" t="inlineStr"/>
+      <c r="CC101" t="inlineStr"/>
+      <c r="CD101" t="inlineStr"/>
+      <c r="CE101" t="inlineStr"/>
+      <c r="CF101" t="inlineStr"/>
+      <c r="CG101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -16725,6 +18556,33 @@
       <c r="BT102" t="inlineStr"/>
       <c r="BU102" t="inlineStr"/>
       <c r="BV102" t="inlineStr"/>
+      <c r="BW102" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY102" t="inlineStr"/>
+      <c r="BZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB102" t="inlineStr"/>
+      <c r="CC102" t="inlineStr"/>
+      <c r="CD102" t="inlineStr"/>
+      <c r="CE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF102" t="inlineStr"/>
+      <c r="CG102" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -16861,6 +18719,17 @@
       <c r="BT103" t="inlineStr"/>
       <c r="BU103" t="inlineStr"/>
       <c r="BV103" t="inlineStr"/>
+      <c r="BW103" t="inlineStr"/>
+      <c r="BX103" t="inlineStr"/>
+      <c r="BY103" t="inlineStr"/>
+      <c r="BZ103" t="inlineStr"/>
+      <c r="CA103" t="inlineStr"/>
+      <c r="CB103" t="inlineStr"/>
+      <c r="CC103" t="inlineStr"/>
+      <c r="CD103" t="inlineStr"/>
+      <c r="CE103" t="inlineStr"/>
+      <c r="CF103" t="inlineStr"/>
+      <c r="CG103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -16997,6 +18866,33 @@
       <c r="BT104" t="inlineStr"/>
       <c r="BU104" t="inlineStr"/>
       <c r="BV104" t="inlineStr"/>
+      <c r="BW104" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY104" t="inlineStr"/>
+      <c r="BZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB104" t="inlineStr"/>
+      <c r="CC104" t="inlineStr"/>
+      <c r="CD104" t="inlineStr"/>
+      <c r="CE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF104" t="inlineStr"/>
+      <c r="CG104" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -17133,6 +19029,17 @@
       <c r="BT105" t="inlineStr"/>
       <c r="BU105" t="inlineStr"/>
       <c r="BV105" t="inlineStr"/>
+      <c r="BW105" t="inlineStr"/>
+      <c r="BX105" t="inlineStr"/>
+      <c r="BY105" t="inlineStr"/>
+      <c r="BZ105" t="inlineStr"/>
+      <c r="CA105" t="inlineStr"/>
+      <c r="CB105" t="inlineStr"/>
+      <c r="CC105" t="inlineStr"/>
+      <c r="CD105" t="inlineStr"/>
+      <c r="CE105" t="inlineStr"/>
+      <c r="CF105" t="inlineStr"/>
+      <c r="CG105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -17269,6 +19176,17 @@
       <c r="BT106" t="inlineStr"/>
       <c r="BU106" t="inlineStr"/>
       <c r="BV106" t="inlineStr"/>
+      <c r="BW106" t="inlineStr"/>
+      <c r="BX106" t="inlineStr"/>
+      <c r="BY106" t="inlineStr"/>
+      <c r="BZ106" t="inlineStr"/>
+      <c r="CA106" t="inlineStr"/>
+      <c r="CB106" t="inlineStr"/>
+      <c r="CC106" t="inlineStr"/>
+      <c r="CD106" t="inlineStr"/>
+      <c r="CE106" t="inlineStr"/>
+      <c r="CF106" t="inlineStr"/>
+      <c r="CG106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -17405,6 +19323,17 @@
       <c r="BT107" t="inlineStr"/>
       <c r="BU107" t="inlineStr"/>
       <c r="BV107" t="inlineStr"/>
+      <c r="BW107" t="inlineStr"/>
+      <c r="BX107" t="inlineStr"/>
+      <c r="BY107" t="inlineStr"/>
+      <c r="BZ107" t="inlineStr"/>
+      <c r="CA107" t="inlineStr"/>
+      <c r="CB107" t="inlineStr"/>
+      <c r="CC107" t="inlineStr"/>
+      <c r="CD107" t="inlineStr"/>
+      <c r="CE107" t="inlineStr"/>
+      <c r="CF107" t="inlineStr"/>
+      <c r="CG107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -17541,6 +19470,17 @@
       <c r="BT108" t="inlineStr"/>
       <c r="BU108" t="inlineStr"/>
       <c r="BV108" t="inlineStr"/>
+      <c r="BW108" t="inlineStr"/>
+      <c r="BX108" t="inlineStr"/>
+      <c r="BY108" t="inlineStr"/>
+      <c r="BZ108" t="inlineStr"/>
+      <c r="CA108" t="inlineStr"/>
+      <c r="CB108" t="inlineStr"/>
+      <c r="CC108" t="inlineStr"/>
+      <c r="CD108" t="inlineStr"/>
+      <c r="CE108" t="inlineStr"/>
+      <c r="CF108" t="inlineStr"/>
+      <c r="CG108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -17677,6 +19617,17 @@
       <c r="BT109" t="inlineStr"/>
       <c r="BU109" t="inlineStr"/>
       <c r="BV109" t="inlineStr"/>
+      <c r="BW109" t="inlineStr"/>
+      <c r="BX109" t="inlineStr"/>
+      <c r="BY109" t="inlineStr"/>
+      <c r="BZ109" t="inlineStr"/>
+      <c r="CA109" t="inlineStr"/>
+      <c r="CB109" t="inlineStr"/>
+      <c r="CC109" t="inlineStr"/>
+      <c r="CD109" t="inlineStr"/>
+      <c r="CE109" t="inlineStr"/>
+      <c r="CF109" t="inlineStr"/>
+      <c r="CG109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -17813,6 +19764,33 @@
       <c r="BT110" t="inlineStr"/>
       <c r="BU110" t="inlineStr"/>
       <c r="BV110" t="inlineStr"/>
+      <c r="BW110" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY110" t="inlineStr"/>
+      <c r="BZ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB110" t="inlineStr"/>
+      <c r="CC110" t="inlineStr"/>
+      <c r="CD110" t="inlineStr"/>
+      <c r="CE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF110" t="inlineStr"/>
+      <c r="CG110" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -17949,6 +19927,17 @@
       <c r="BT111" t="inlineStr"/>
       <c r="BU111" t="inlineStr"/>
       <c r="BV111" t="inlineStr"/>
+      <c r="BW111" t="inlineStr"/>
+      <c r="BX111" t="inlineStr"/>
+      <c r="BY111" t="inlineStr"/>
+      <c r="BZ111" t="inlineStr"/>
+      <c r="CA111" t="inlineStr"/>
+      <c r="CB111" t="inlineStr"/>
+      <c r="CC111" t="inlineStr"/>
+      <c r="CD111" t="inlineStr"/>
+      <c r="CE111" t="inlineStr"/>
+      <c r="CF111" t="inlineStr"/>
+      <c r="CG111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -18085,6 +20074,17 @@
       <c r="BT112" t="inlineStr"/>
       <c r="BU112" t="inlineStr"/>
       <c r="BV112" t="inlineStr"/>
+      <c r="BW112" t="inlineStr"/>
+      <c r="BX112" t="inlineStr"/>
+      <c r="BY112" t="inlineStr"/>
+      <c r="BZ112" t="inlineStr"/>
+      <c r="CA112" t="inlineStr"/>
+      <c r="CB112" t="inlineStr"/>
+      <c r="CC112" t="inlineStr"/>
+      <c r="CD112" t="inlineStr"/>
+      <c r="CE112" t="inlineStr"/>
+      <c r="CF112" t="inlineStr"/>
+      <c r="CG112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -18221,6 +20221,33 @@
       <c r="BT113" t="inlineStr"/>
       <c r="BU113" t="inlineStr"/>
       <c r="BV113" t="inlineStr"/>
+      <c r="BW113" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY113" t="inlineStr"/>
+      <c r="BZ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB113" t="inlineStr"/>
+      <c r="CC113" t="inlineStr"/>
+      <c r="CD113" t="inlineStr"/>
+      <c r="CE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF113" t="inlineStr"/>
+      <c r="CG113" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -18357,6 +20384,33 @@
       <c r="BT114" t="inlineStr"/>
       <c r="BU114" t="inlineStr"/>
       <c r="BV114" t="inlineStr"/>
+      <c r="BW114" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY114" t="inlineStr"/>
+      <c r="BZ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB114" t="inlineStr"/>
+      <c r="CC114" t="inlineStr"/>
+      <c r="CD114" t="inlineStr"/>
+      <c r="CE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF114" t="inlineStr"/>
+      <c r="CG114" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -18493,6 +20547,17 @@
       <c r="BT115" t="inlineStr"/>
       <c r="BU115" t="inlineStr"/>
       <c r="BV115" t="inlineStr"/>
+      <c r="BW115" t="inlineStr"/>
+      <c r="BX115" t="inlineStr"/>
+      <c r="BY115" t="inlineStr"/>
+      <c r="BZ115" t="inlineStr"/>
+      <c r="CA115" t="inlineStr"/>
+      <c r="CB115" t="inlineStr"/>
+      <c r="CC115" t="inlineStr"/>
+      <c r="CD115" t="inlineStr"/>
+      <c r="CE115" t="inlineStr"/>
+      <c r="CF115" t="inlineStr"/>
+      <c r="CG115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -18629,6 +20694,17 @@
       <c r="BT116" t="inlineStr"/>
       <c r="BU116" t="inlineStr"/>
       <c r="BV116" t="inlineStr"/>
+      <c r="BW116" t="inlineStr"/>
+      <c r="BX116" t="inlineStr"/>
+      <c r="BY116" t="inlineStr"/>
+      <c r="BZ116" t="inlineStr"/>
+      <c r="CA116" t="inlineStr"/>
+      <c r="CB116" t="inlineStr"/>
+      <c r="CC116" t="inlineStr"/>
+      <c r="CD116" t="inlineStr"/>
+      <c r="CE116" t="inlineStr"/>
+      <c r="CF116" t="inlineStr"/>
+      <c r="CG116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -18765,6 +20841,33 @@
       <c r="BT117" t="inlineStr"/>
       <c r="BU117" t="inlineStr"/>
       <c r="BV117" t="inlineStr"/>
+      <c r="BW117" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY117" t="inlineStr"/>
+      <c r="BZ117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB117" t="inlineStr"/>
+      <c r="CC117" t="inlineStr"/>
+      <c r="CD117" t="inlineStr"/>
+      <c r="CE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF117" t="inlineStr"/>
+      <c r="CG117" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -18901,6 +21004,33 @@
       <c r="BT118" t="inlineStr"/>
       <c r="BU118" t="inlineStr"/>
       <c r="BV118" t="inlineStr"/>
+      <c r="BW118" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY118" t="inlineStr"/>
+      <c r="BZ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB118" t="inlineStr"/>
+      <c r="CC118" t="inlineStr"/>
+      <c r="CD118" t="inlineStr"/>
+      <c r="CE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF118" t="inlineStr"/>
+      <c r="CG118" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -19037,6 +21167,17 @@
       <c r="BT119" t="inlineStr"/>
       <c r="BU119" t="inlineStr"/>
       <c r="BV119" t="inlineStr"/>
+      <c r="BW119" t="inlineStr"/>
+      <c r="BX119" t="inlineStr"/>
+      <c r="BY119" t="inlineStr"/>
+      <c r="BZ119" t="inlineStr"/>
+      <c r="CA119" t="inlineStr"/>
+      <c r="CB119" t="inlineStr"/>
+      <c r="CC119" t="inlineStr"/>
+      <c r="CD119" t="inlineStr"/>
+      <c r="CE119" t="inlineStr"/>
+      <c r="CF119" t="inlineStr"/>
+      <c r="CG119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -19173,6 +21314,33 @@
       <c r="BT120" t="inlineStr"/>
       <c r="BU120" t="inlineStr"/>
       <c r="BV120" t="inlineStr"/>
+      <c r="BW120" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY120" t="inlineStr"/>
+      <c r="BZ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB120" t="inlineStr"/>
+      <c r="CC120" t="inlineStr"/>
+      <c r="CD120" t="inlineStr"/>
+      <c r="CE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF120" t="inlineStr"/>
+      <c r="CG120" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -19309,6 +21477,33 @@
       <c r="BT121" t="inlineStr"/>
       <c r="BU121" t="inlineStr"/>
       <c r="BV121" t="inlineStr"/>
+      <c r="BW121" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY121" t="inlineStr"/>
+      <c r="BZ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB121" t="inlineStr"/>
+      <c r="CC121" t="inlineStr"/>
+      <c r="CD121" t="inlineStr"/>
+      <c r="CE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF121" t="inlineStr"/>
+      <c r="CG121" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -19445,6 +21640,33 @@
       <c r="BT122" t="inlineStr"/>
       <c r="BU122" t="inlineStr"/>
       <c r="BV122" t="inlineStr"/>
+      <c r="BW122" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY122" t="inlineStr"/>
+      <c r="BZ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB122" t="inlineStr"/>
+      <c r="CC122" t="inlineStr"/>
+      <c r="CD122" t="inlineStr"/>
+      <c r="CE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF122" t="inlineStr"/>
+      <c r="CG122" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -19581,6 +21803,33 @@
       <c r="BT123" t="inlineStr"/>
       <c r="BU123" t="inlineStr"/>
       <c r="BV123" t="inlineStr"/>
+      <c r="BW123" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY123" t="inlineStr"/>
+      <c r="BZ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB123" t="inlineStr"/>
+      <c r="CC123" t="inlineStr"/>
+      <c r="CD123" t="inlineStr"/>
+      <c r="CE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" t="inlineStr"/>
+      <c r="CG123" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -19717,6 +21966,37 @@
       <c r="BT124" t="inlineStr"/>
       <c r="BU124" t="inlineStr"/>
       <c r="BV124" t="inlineStr"/>
+      <c r="BW124" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY124" t="inlineStr"/>
+      <c r="BZ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB124" t="inlineStr"/>
+      <c r="CC124" t="inlineStr"/>
+      <c r="CD124" t="inlineStr"/>
+      <c r="CE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF124" t="inlineStr">
+        <is>
+          <t>華南</t>
+        </is>
+      </c>
+      <c r="CG124" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -19853,6 +22133,33 @@
       <c r="BT125" t="inlineStr"/>
       <c r="BU125" t="inlineStr"/>
       <c r="BV125" t="inlineStr"/>
+      <c r="BW125" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY125" t="inlineStr"/>
+      <c r="BZ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB125" t="inlineStr"/>
+      <c r="CC125" t="inlineStr"/>
+      <c r="CD125" t="inlineStr"/>
+      <c r="CE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF125" t="inlineStr"/>
+      <c r="CG125" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -19989,6 +22296,33 @@
       <c r="BT126" t="inlineStr"/>
       <c r="BU126" t="inlineStr"/>
       <c r="BV126" t="inlineStr"/>
+      <c r="BW126" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY126" t="inlineStr"/>
+      <c r="BZ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB126" t="inlineStr"/>
+      <c r="CC126" t="inlineStr"/>
+      <c r="CD126" t="inlineStr"/>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="inlineStr"/>
+      <c r="CG126" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -20125,6 +22459,33 @@
       <c r="BT127" t="inlineStr"/>
       <c r="BU127" t="inlineStr"/>
       <c r="BV127" t="inlineStr"/>
+      <c r="BW127" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY127" t="inlineStr"/>
+      <c r="BZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB127" t="inlineStr"/>
+      <c r="CC127" t="inlineStr"/>
+      <c r="CD127" t="inlineStr"/>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="inlineStr"/>
+      <c r="CG127" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -20261,6 +22622,33 @@
       <c r="BT128" t="inlineStr"/>
       <c r="BU128" t="inlineStr"/>
       <c r="BV128" t="inlineStr"/>
+      <c r="BW128" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY128" t="inlineStr"/>
+      <c r="BZ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB128" t="inlineStr"/>
+      <c r="CC128" t="inlineStr"/>
+      <c r="CD128" t="inlineStr"/>
+      <c r="CE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF128" t="inlineStr"/>
+      <c r="CG128" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -20397,6 +22785,33 @@
       <c r="BT129" t="inlineStr"/>
       <c r="BU129" t="inlineStr"/>
       <c r="BV129" t="inlineStr"/>
+      <c r="BW129" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY129" t="inlineStr"/>
+      <c r="BZ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB129" t="inlineStr"/>
+      <c r="CC129" t="inlineStr"/>
+      <c r="CD129" t="inlineStr"/>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="inlineStr"/>
+      <c r="CG129" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -20533,6 +22948,17 @@
       <c r="BT130" t="inlineStr"/>
       <c r="BU130" t="inlineStr"/>
       <c r="BV130" t="inlineStr"/>
+      <c r="BW130" t="inlineStr"/>
+      <c r="BX130" t="inlineStr"/>
+      <c r="BY130" t="inlineStr"/>
+      <c r="BZ130" t="inlineStr"/>
+      <c r="CA130" t="inlineStr"/>
+      <c r="CB130" t="inlineStr"/>
+      <c r="CC130" t="inlineStr"/>
+      <c r="CD130" t="inlineStr"/>
+      <c r="CE130" t="inlineStr"/>
+      <c r="CF130" t="inlineStr"/>
+      <c r="CG130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -20669,6 +23095,17 @@
       <c r="BT131" t="inlineStr"/>
       <c r="BU131" t="inlineStr"/>
       <c r="BV131" t="inlineStr"/>
+      <c r="BW131" t="inlineStr"/>
+      <c r="BX131" t="inlineStr"/>
+      <c r="BY131" t="inlineStr"/>
+      <c r="BZ131" t="inlineStr"/>
+      <c r="CA131" t="inlineStr"/>
+      <c r="CB131" t="inlineStr"/>
+      <c r="CC131" t="inlineStr"/>
+      <c r="CD131" t="inlineStr"/>
+      <c r="CE131" t="inlineStr"/>
+      <c r="CF131" t="inlineStr"/>
+      <c r="CG131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -20795,6 +23232,17 @@
       <c r="BT132" t="inlineStr"/>
       <c r="BU132" t="inlineStr"/>
       <c r="BV132" t="inlineStr"/>
+      <c r="BW132" t="inlineStr"/>
+      <c r="BX132" t="inlineStr"/>
+      <c r="BY132" t="inlineStr"/>
+      <c r="BZ132" t="inlineStr"/>
+      <c r="CA132" t="inlineStr"/>
+      <c r="CB132" t="inlineStr"/>
+      <c r="CC132" t="inlineStr"/>
+      <c r="CD132" t="inlineStr"/>
+      <c r="CE132" t="inlineStr"/>
+      <c r="CF132" t="inlineStr"/>
+      <c r="CG132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -20921,6 +23369,17 @@
       <c r="BT133" t="inlineStr"/>
       <c r="BU133" t="inlineStr"/>
       <c r="BV133" t="inlineStr"/>
+      <c r="BW133" t="inlineStr"/>
+      <c r="BX133" t="inlineStr"/>
+      <c r="BY133" t="inlineStr"/>
+      <c r="BZ133" t="inlineStr"/>
+      <c r="CA133" t="inlineStr"/>
+      <c r="CB133" t="inlineStr"/>
+      <c r="CC133" t="inlineStr"/>
+      <c r="CD133" t="inlineStr"/>
+      <c r="CE133" t="inlineStr"/>
+      <c r="CF133" t="inlineStr"/>
+      <c r="CG133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -21047,6 +23506,17 @@
       <c r="BT134" t="inlineStr"/>
       <c r="BU134" t="inlineStr"/>
       <c r="BV134" t="inlineStr"/>
+      <c r="BW134" t="inlineStr"/>
+      <c r="BX134" t="inlineStr"/>
+      <c r="BY134" t="inlineStr"/>
+      <c r="BZ134" t="inlineStr"/>
+      <c r="CA134" t="inlineStr"/>
+      <c r="CB134" t="inlineStr"/>
+      <c r="CC134" t="inlineStr"/>
+      <c r="CD134" t="inlineStr"/>
+      <c r="CE134" t="inlineStr"/>
+      <c r="CF134" t="inlineStr"/>
+      <c r="CG134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -21173,6 +23643,17 @@
       <c r="BT135" t="inlineStr"/>
       <c r="BU135" t="inlineStr"/>
       <c r="BV135" t="inlineStr"/>
+      <c r="BW135" t="inlineStr"/>
+      <c r="BX135" t="inlineStr"/>
+      <c r="BY135" t="inlineStr"/>
+      <c r="BZ135" t="inlineStr"/>
+      <c r="CA135" t="inlineStr"/>
+      <c r="CB135" t="inlineStr"/>
+      <c r="CC135" t="inlineStr"/>
+      <c r="CD135" t="inlineStr"/>
+      <c r="CE135" t="inlineStr"/>
+      <c r="CF135" t="inlineStr"/>
+      <c r="CG135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -21299,6 +23780,17 @@
       <c r="BT136" t="inlineStr"/>
       <c r="BU136" t="inlineStr"/>
       <c r="BV136" t="inlineStr"/>
+      <c r="BW136" t="inlineStr"/>
+      <c r="BX136" t="inlineStr"/>
+      <c r="BY136" t="inlineStr"/>
+      <c r="BZ136" t="inlineStr"/>
+      <c r="CA136" t="inlineStr"/>
+      <c r="CB136" t="inlineStr"/>
+      <c r="CC136" t="inlineStr"/>
+      <c r="CD136" t="inlineStr"/>
+      <c r="CE136" t="inlineStr"/>
+      <c r="CF136" t="inlineStr"/>
+      <c r="CG136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -21425,6 +23917,17 @@
       <c r="BT137" t="inlineStr"/>
       <c r="BU137" t="inlineStr"/>
       <c r="BV137" t="inlineStr"/>
+      <c r="BW137" t="inlineStr"/>
+      <c r="BX137" t="inlineStr"/>
+      <c r="BY137" t="inlineStr"/>
+      <c r="BZ137" t="inlineStr"/>
+      <c r="CA137" t="inlineStr"/>
+      <c r="CB137" t="inlineStr"/>
+      <c r="CC137" t="inlineStr"/>
+      <c r="CD137" t="inlineStr"/>
+      <c r="CE137" t="inlineStr"/>
+      <c r="CF137" t="inlineStr"/>
+      <c r="CG137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -21551,6 +24054,33 @@
       <c r="BT138" t="inlineStr"/>
       <c r="BU138" t="inlineStr"/>
       <c r="BV138" t="inlineStr"/>
+      <c r="BW138" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY138" t="inlineStr"/>
+      <c r="BZ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB138" t="inlineStr"/>
+      <c r="CC138" t="inlineStr"/>
+      <c r="CD138" t="inlineStr"/>
+      <c r="CE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF138" t="inlineStr"/>
+      <c r="CG138" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -21677,6 +24207,17 @@
       <c r="BT139" t="inlineStr"/>
       <c r="BU139" t="inlineStr"/>
       <c r="BV139" t="inlineStr"/>
+      <c r="BW139" t="inlineStr"/>
+      <c r="BX139" t="inlineStr"/>
+      <c r="BY139" t="inlineStr"/>
+      <c r="BZ139" t="inlineStr"/>
+      <c r="CA139" t="inlineStr"/>
+      <c r="CB139" t="inlineStr"/>
+      <c r="CC139" t="inlineStr"/>
+      <c r="CD139" t="inlineStr"/>
+      <c r="CE139" t="inlineStr"/>
+      <c r="CF139" t="inlineStr"/>
+      <c r="CG139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -21803,6 +24344,33 @@
       <c r="BT140" t="inlineStr"/>
       <c r="BU140" t="inlineStr"/>
       <c r="BV140" t="inlineStr"/>
+      <c r="BW140" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY140" t="inlineStr"/>
+      <c r="BZ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB140" t="inlineStr"/>
+      <c r="CC140" t="inlineStr"/>
+      <c r="CD140" t="inlineStr"/>
+      <c r="CE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF140" t="inlineStr"/>
+      <c r="CG140" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -21929,6 +24497,33 @@
       <c r="BT141" t="inlineStr"/>
       <c r="BU141" t="inlineStr"/>
       <c r="BV141" t="inlineStr"/>
+      <c r="BW141" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY141" t="inlineStr"/>
+      <c r="BZ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB141" t="inlineStr"/>
+      <c r="CC141" t="inlineStr"/>
+      <c r="CD141" t="inlineStr"/>
+      <c r="CE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF141" t="inlineStr"/>
+      <c r="CG141" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -22055,6 +24650,17 @@
       <c r="BT142" t="inlineStr"/>
       <c r="BU142" t="inlineStr"/>
       <c r="BV142" t="inlineStr"/>
+      <c r="BW142" t="inlineStr"/>
+      <c r="BX142" t="inlineStr"/>
+      <c r="BY142" t="inlineStr"/>
+      <c r="BZ142" t="inlineStr"/>
+      <c r="CA142" t="inlineStr"/>
+      <c r="CB142" t="inlineStr"/>
+      <c r="CC142" t="inlineStr"/>
+      <c r="CD142" t="inlineStr"/>
+      <c r="CE142" t="inlineStr"/>
+      <c r="CF142" t="inlineStr"/>
+      <c r="CG142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -22181,6 +24787,33 @@
       <c r="BT143" t="inlineStr"/>
       <c r="BU143" t="inlineStr"/>
       <c r="BV143" t="inlineStr"/>
+      <c r="BW143" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY143" t="inlineStr"/>
+      <c r="BZ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB143" t="inlineStr"/>
+      <c r="CC143" t="inlineStr"/>
+      <c r="CD143" t="inlineStr"/>
+      <c r="CE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF143" t="inlineStr"/>
+      <c r="CG143" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -22307,6 +24940,17 @@
       <c r="BT144" t="inlineStr"/>
       <c r="BU144" t="inlineStr"/>
       <c r="BV144" t="inlineStr"/>
+      <c r="BW144" t="inlineStr"/>
+      <c r="BX144" t="inlineStr"/>
+      <c r="BY144" t="inlineStr"/>
+      <c r="BZ144" t="inlineStr"/>
+      <c r="CA144" t="inlineStr"/>
+      <c r="CB144" t="inlineStr"/>
+      <c r="CC144" t="inlineStr"/>
+      <c r="CD144" t="inlineStr"/>
+      <c r="CE144" t="inlineStr"/>
+      <c r="CF144" t="inlineStr"/>
+      <c r="CG144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -22433,6 +25077,33 @@
       <c r="BT145" t="inlineStr"/>
       <c r="BU145" t="inlineStr"/>
       <c r="BV145" t="inlineStr"/>
+      <c r="BW145" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY145" t="inlineStr"/>
+      <c r="BZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB145" t="inlineStr"/>
+      <c r="CC145" t="inlineStr"/>
+      <c r="CD145" t="inlineStr"/>
+      <c r="CE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF145" t="inlineStr"/>
+      <c r="CG145" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -22559,6 +25230,33 @@
       <c r="BT146" t="inlineStr"/>
       <c r="BU146" t="inlineStr"/>
       <c r="BV146" t="inlineStr"/>
+      <c r="BW146" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY146" t="inlineStr"/>
+      <c r="BZ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB146" t="inlineStr"/>
+      <c r="CC146" t="inlineStr"/>
+      <c r="CD146" t="inlineStr"/>
+      <c r="CE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF146" t="inlineStr"/>
+      <c r="CG146" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -22685,6 +25383,17 @@
       <c r="BT147" t="inlineStr"/>
       <c r="BU147" t="inlineStr"/>
       <c r="BV147" t="inlineStr"/>
+      <c r="BW147" t="inlineStr"/>
+      <c r="BX147" t="inlineStr"/>
+      <c r="BY147" t="inlineStr"/>
+      <c r="BZ147" t="inlineStr"/>
+      <c r="CA147" t="inlineStr"/>
+      <c r="CB147" t="inlineStr"/>
+      <c r="CC147" t="inlineStr"/>
+      <c r="CD147" t="inlineStr"/>
+      <c r="CE147" t="inlineStr"/>
+      <c r="CF147" t="inlineStr"/>
+      <c r="CG147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -22811,6 +25520,17 @@
       <c r="BT148" t="inlineStr"/>
       <c r="BU148" t="inlineStr"/>
       <c r="BV148" t="inlineStr"/>
+      <c r="BW148" t="inlineStr"/>
+      <c r="BX148" t="inlineStr"/>
+      <c r="BY148" t="inlineStr"/>
+      <c r="BZ148" t="inlineStr"/>
+      <c r="CA148" t="inlineStr"/>
+      <c r="CB148" t="inlineStr"/>
+      <c r="CC148" t="inlineStr"/>
+      <c r="CD148" t="inlineStr"/>
+      <c r="CE148" t="inlineStr"/>
+      <c r="CF148" t="inlineStr"/>
+      <c r="CG148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -22937,6 +25657,17 @@
       <c r="BT149" t="inlineStr"/>
       <c r="BU149" t="inlineStr"/>
       <c r="BV149" t="inlineStr"/>
+      <c r="BW149" t="inlineStr"/>
+      <c r="BX149" t="inlineStr"/>
+      <c r="BY149" t="inlineStr"/>
+      <c r="BZ149" t="inlineStr"/>
+      <c r="CA149" t="inlineStr"/>
+      <c r="CB149" t="inlineStr"/>
+      <c r="CC149" t="inlineStr"/>
+      <c r="CD149" t="inlineStr"/>
+      <c r="CE149" t="inlineStr"/>
+      <c r="CF149" t="inlineStr"/>
+      <c r="CG149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -23063,6 +25794,17 @@
       <c r="BT150" t="inlineStr"/>
       <c r="BU150" t="inlineStr"/>
       <c r="BV150" t="inlineStr"/>
+      <c r="BW150" t="inlineStr"/>
+      <c r="BX150" t="inlineStr"/>
+      <c r="BY150" t="inlineStr"/>
+      <c r="BZ150" t="inlineStr"/>
+      <c r="CA150" t="inlineStr"/>
+      <c r="CB150" t="inlineStr"/>
+      <c r="CC150" t="inlineStr"/>
+      <c r="CD150" t="inlineStr"/>
+      <c r="CE150" t="inlineStr"/>
+      <c r="CF150" t="inlineStr"/>
+      <c r="CG150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -23189,6 +25931,17 @@
       <c r="BT151" t="inlineStr"/>
       <c r="BU151" t="inlineStr"/>
       <c r="BV151" t="inlineStr"/>
+      <c r="BW151" t="inlineStr"/>
+      <c r="BX151" t="inlineStr"/>
+      <c r="BY151" t="inlineStr"/>
+      <c r="BZ151" t="inlineStr"/>
+      <c r="CA151" t="inlineStr"/>
+      <c r="CB151" t="inlineStr"/>
+      <c r="CC151" t="inlineStr"/>
+      <c r="CD151" t="inlineStr"/>
+      <c r="CE151" t="inlineStr"/>
+      <c r="CF151" t="inlineStr"/>
+      <c r="CG151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -23315,6 +26068,17 @@
       <c r="BT152" t="inlineStr"/>
       <c r="BU152" t="inlineStr"/>
       <c r="BV152" t="inlineStr"/>
+      <c r="BW152" t="inlineStr"/>
+      <c r="BX152" t="inlineStr"/>
+      <c r="BY152" t="inlineStr"/>
+      <c r="BZ152" t="inlineStr"/>
+      <c r="CA152" t="inlineStr"/>
+      <c r="CB152" t="inlineStr"/>
+      <c r="CC152" t="inlineStr"/>
+      <c r="CD152" t="inlineStr"/>
+      <c r="CE152" t="inlineStr"/>
+      <c r="CF152" t="inlineStr"/>
+      <c r="CG152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -23441,6 +26205,17 @@
       <c r="BT153" t="inlineStr"/>
       <c r="BU153" t="inlineStr"/>
       <c r="BV153" t="inlineStr"/>
+      <c r="BW153" t="inlineStr"/>
+      <c r="BX153" t="inlineStr"/>
+      <c r="BY153" t="inlineStr"/>
+      <c r="BZ153" t="inlineStr"/>
+      <c r="CA153" t="inlineStr"/>
+      <c r="CB153" t="inlineStr"/>
+      <c r="CC153" t="inlineStr"/>
+      <c r="CD153" t="inlineStr"/>
+      <c r="CE153" t="inlineStr"/>
+      <c r="CF153" t="inlineStr"/>
+      <c r="CG153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -23567,6 +26342,33 @@
       <c r="BT154" t="inlineStr"/>
       <c r="BU154" t="inlineStr"/>
       <c r="BV154" t="inlineStr"/>
+      <c r="BW154" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY154" t="inlineStr"/>
+      <c r="BZ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB154" t="inlineStr"/>
+      <c r="CC154" t="inlineStr"/>
+      <c r="CD154" t="inlineStr"/>
+      <c r="CE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF154" t="inlineStr"/>
+      <c r="CG154" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -23693,6 +26495,37 @@
       <c r="BT155" t="inlineStr"/>
       <c r="BU155" t="inlineStr"/>
       <c r="BV155" t="inlineStr"/>
+      <c r="BW155" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY155" t="inlineStr"/>
+      <c r="BZ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB155" t="inlineStr"/>
+      <c r="CC155" t="inlineStr"/>
+      <c r="CD155" t="inlineStr"/>
+      <c r="CE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF155" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
+      <c r="CG155" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -23819,6 +26652,33 @@
       <c r="BT156" t="inlineStr"/>
       <c r="BU156" t="inlineStr"/>
       <c r="BV156" t="inlineStr"/>
+      <c r="BW156" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY156" t="inlineStr"/>
+      <c r="BZ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB156" t="inlineStr"/>
+      <c r="CC156" t="inlineStr"/>
+      <c r="CD156" t="inlineStr"/>
+      <c r="CE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF156" t="inlineStr"/>
+      <c r="CG156" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -23945,6 +26805,37 @@
       <c r="BT157" t="inlineStr"/>
       <c r="BU157" t="inlineStr"/>
       <c r="BV157" t="inlineStr"/>
+      <c r="BW157" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY157" t="inlineStr"/>
+      <c r="BZ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB157" t="inlineStr"/>
+      <c r="CC157" t="inlineStr"/>
+      <c r="CD157" t="inlineStr"/>
+      <c r="CE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF157" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
+      <c r="CG157" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -24071,6 +26962,37 @@
       <c r="BT158" t="inlineStr"/>
       <c r="BU158" t="inlineStr"/>
       <c r="BV158" t="inlineStr"/>
+      <c r="BW158" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY158" t="inlineStr"/>
+      <c r="BZ158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB158" t="inlineStr"/>
+      <c r="CC158" t="inlineStr"/>
+      <c r="CD158" t="inlineStr"/>
+      <c r="CE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF158" t="inlineStr">
+        <is>
+          <t>富邦</t>
+        </is>
+      </c>
+      <c r="CG158" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -24197,6 +27119,37 @@
       <c r="BT159" t="inlineStr"/>
       <c r="BU159" t="inlineStr"/>
       <c r="BV159" t="inlineStr"/>
+      <c r="BW159" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY159" t="inlineStr"/>
+      <c r="BZ159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB159" t="inlineStr"/>
+      <c r="CC159" t="inlineStr"/>
+      <c r="CD159" t="inlineStr"/>
+      <c r="CE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF159" t="inlineStr">
+        <is>
+          <t>國泰</t>
+        </is>
+      </c>
+      <c r="CG159" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -24323,6 +27276,37 @@
       <c r="BT160" t="inlineStr"/>
       <c r="BU160" t="inlineStr"/>
       <c r="BV160" t="inlineStr"/>
+      <c r="BW160" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY160" t="inlineStr"/>
+      <c r="BZ160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB160" t="inlineStr"/>
+      <c r="CC160" t="inlineStr"/>
+      <c r="CD160" t="inlineStr"/>
+      <c r="CE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF160" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
+      <c r="CG160" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -24449,6 +27433,33 @@
       <c r="BT161" t="inlineStr"/>
       <c r="BU161" t="inlineStr"/>
       <c r="BV161" t="inlineStr"/>
+      <c r="BW161" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY161" t="inlineStr"/>
+      <c r="BZ161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB161" t="inlineStr"/>
+      <c r="CC161" t="inlineStr"/>
+      <c r="CD161" t="inlineStr"/>
+      <c r="CE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF161" t="inlineStr"/>
+      <c r="CG161" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -24575,6 +27586,33 @@
       <c r="BT162" t="inlineStr"/>
       <c r="BU162" t="inlineStr"/>
       <c r="BV162" t="inlineStr"/>
+      <c r="BW162" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY162" t="inlineStr"/>
+      <c r="BZ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB162" t="inlineStr"/>
+      <c r="CC162" t="inlineStr"/>
+      <c r="CD162" t="inlineStr"/>
+      <c r="CE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF162" t="inlineStr"/>
+      <c r="CG162" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -24701,6 +27739,17 @@
       <c r="BT163" t="inlineStr"/>
       <c r="BU163" t="inlineStr"/>
       <c r="BV163" t="inlineStr"/>
+      <c r="BW163" t="inlineStr"/>
+      <c r="BX163" t="inlineStr"/>
+      <c r="BY163" t="inlineStr"/>
+      <c r="BZ163" t="inlineStr"/>
+      <c r="CA163" t="inlineStr"/>
+      <c r="CB163" t="inlineStr"/>
+      <c r="CC163" t="inlineStr"/>
+      <c r="CD163" t="inlineStr"/>
+      <c r="CE163" t="inlineStr"/>
+      <c r="CF163" t="inlineStr"/>
+      <c r="CG163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -24827,6 +27876,33 @@
       <c r="BT164" t="inlineStr"/>
       <c r="BU164" t="inlineStr"/>
       <c r="BV164" t="inlineStr"/>
+      <c r="BW164" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY164" t="inlineStr"/>
+      <c r="BZ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB164" t="inlineStr"/>
+      <c r="CC164" t="inlineStr"/>
+      <c r="CD164" t="inlineStr"/>
+      <c r="CE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF164" t="inlineStr"/>
+      <c r="CG164" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -24953,6 +28029,33 @@
       <c r="BT165" t="inlineStr"/>
       <c r="BU165" t="inlineStr"/>
       <c r="BV165" t="inlineStr"/>
+      <c r="BW165" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY165" t="inlineStr"/>
+      <c r="BZ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB165" t="inlineStr"/>
+      <c r="CC165" t="inlineStr"/>
+      <c r="CD165" t="inlineStr"/>
+      <c r="CE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF165" t="inlineStr"/>
+      <c r="CG165" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -25079,6 +28182,33 @@
       <c r="BT166" t="inlineStr"/>
       <c r="BU166" t="inlineStr"/>
       <c r="BV166" t="inlineStr"/>
+      <c r="BW166" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY166" t="inlineStr"/>
+      <c r="BZ166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB166" t="inlineStr"/>
+      <c r="CC166" t="inlineStr"/>
+      <c r="CD166" t="inlineStr"/>
+      <c r="CE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF166" t="inlineStr"/>
+      <c r="CG166" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -25205,6 +28335,33 @@
       <c r="BT167" t="inlineStr"/>
       <c r="BU167" t="inlineStr"/>
       <c r="BV167" t="inlineStr"/>
+      <c r="BW167" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY167" t="inlineStr"/>
+      <c r="BZ167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB167" t="inlineStr"/>
+      <c r="CC167" t="inlineStr"/>
+      <c r="CD167" t="inlineStr"/>
+      <c r="CE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF167" t="inlineStr"/>
+      <c r="CG167" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -25331,6 +28488,33 @@
       <c r="BT168" t="inlineStr"/>
       <c r="BU168" t="inlineStr"/>
       <c r="BV168" t="inlineStr"/>
+      <c r="BW168" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY168" t="inlineStr"/>
+      <c r="BZ168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB168" t="inlineStr"/>
+      <c r="CC168" t="inlineStr"/>
+      <c r="CD168" t="inlineStr"/>
+      <c r="CE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF168" t="inlineStr"/>
+      <c r="CG168" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -25457,6 +28641,33 @@
       <c r="BT169" t="inlineStr"/>
       <c r="BU169" t="inlineStr"/>
       <c r="BV169" t="inlineStr"/>
+      <c r="BW169" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY169" t="inlineStr"/>
+      <c r="BZ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB169" t="inlineStr"/>
+      <c r="CC169" t="inlineStr"/>
+      <c r="CD169" t="inlineStr"/>
+      <c r="CE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF169" t="inlineStr"/>
+      <c r="CG169" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -25583,6 +28794,33 @@
       <c r="BT170" t="inlineStr"/>
       <c r="BU170" t="inlineStr"/>
       <c r="BV170" t="inlineStr"/>
+      <c r="BW170" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY170" t="inlineStr"/>
+      <c r="BZ170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB170" t="inlineStr"/>
+      <c r="CC170" t="inlineStr"/>
+      <c r="CD170" t="inlineStr"/>
+      <c r="CE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF170" t="inlineStr"/>
+      <c r="CG170" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -25709,6 +28947,33 @@
       <c r="BT171" t="inlineStr"/>
       <c r="BU171" t="inlineStr"/>
       <c r="BV171" t="inlineStr"/>
+      <c r="BW171" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY171" t="inlineStr"/>
+      <c r="BZ171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB171" t="inlineStr"/>
+      <c r="CC171" t="inlineStr"/>
+      <c r="CD171" t="inlineStr"/>
+      <c r="CE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF171" t="inlineStr"/>
+      <c r="CG171" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -25835,6 +29100,17 @@
       <c r="BT172" t="inlineStr"/>
       <c r="BU172" t="inlineStr"/>
       <c r="BV172" t="inlineStr"/>
+      <c r="BW172" t="inlineStr"/>
+      <c r="BX172" t="inlineStr"/>
+      <c r="BY172" t="inlineStr"/>
+      <c r="BZ172" t="inlineStr"/>
+      <c r="CA172" t="inlineStr"/>
+      <c r="CB172" t="inlineStr"/>
+      <c r="CC172" t="inlineStr"/>
+      <c r="CD172" t="inlineStr"/>
+      <c r="CE172" t="inlineStr"/>
+      <c r="CF172" t="inlineStr"/>
+      <c r="CG172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -25961,6 +29237,17 @@
       <c r="BT173" t="inlineStr"/>
       <c r="BU173" t="inlineStr"/>
       <c r="BV173" t="inlineStr"/>
+      <c r="BW173" t="inlineStr"/>
+      <c r="BX173" t="inlineStr"/>
+      <c r="BY173" t="inlineStr"/>
+      <c r="BZ173" t="inlineStr"/>
+      <c r="CA173" t="inlineStr"/>
+      <c r="CB173" t="inlineStr"/>
+      <c r="CC173" t="inlineStr"/>
+      <c r="CD173" t="inlineStr"/>
+      <c r="CE173" t="inlineStr"/>
+      <c r="CF173" t="inlineStr"/>
+      <c r="CG173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -26087,6 +29374,17 @@
       <c r="BT174" t="inlineStr"/>
       <c r="BU174" t="inlineStr"/>
       <c r="BV174" t="inlineStr"/>
+      <c r="BW174" t="inlineStr"/>
+      <c r="BX174" t="inlineStr"/>
+      <c r="BY174" t="inlineStr"/>
+      <c r="BZ174" t="inlineStr"/>
+      <c r="CA174" t="inlineStr"/>
+      <c r="CB174" t="inlineStr"/>
+      <c r="CC174" t="inlineStr"/>
+      <c r="CD174" t="inlineStr"/>
+      <c r="CE174" t="inlineStr"/>
+      <c r="CF174" t="inlineStr"/>
+      <c r="CG174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -26213,6 +29511,33 @@
       <c r="BT175" t="inlineStr"/>
       <c r="BU175" t="inlineStr"/>
       <c r="BV175" t="inlineStr"/>
+      <c r="BW175" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY175" t="inlineStr"/>
+      <c r="BZ175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB175" t="inlineStr"/>
+      <c r="CC175" t="inlineStr"/>
+      <c r="CD175" t="inlineStr"/>
+      <c r="CE175" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF175" t="inlineStr"/>
+      <c r="CG175" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -26339,6 +29664,33 @@
       <c r="BT176" t="inlineStr"/>
       <c r="BU176" t="inlineStr"/>
       <c r="BV176" t="inlineStr"/>
+      <c r="BW176" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY176" t="inlineStr"/>
+      <c r="BZ176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB176" t="inlineStr"/>
+      <c r="CC176" t="inlineStr"/>
+      <c r="CD176" t="inlineStr"/>
+      <c r="CE176" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF176" t="inlineStr"/>
+      <c r="CG176" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -26465,6 +29817,17 @@
       <c r="BT177" t="inlineStr"/>
       <c r="BU177" t="inlineStr"/>
       <c r="BV177" t="inlineStr"/>
+      <c r="BW177" t="inlineStr"/>
+      <c r="BX177" t="inlineStr"/>
+      <c r="BY177" t="inlineStr"/>
+      <c r="BZ177" t="inlineStr"/>
+      <c r="CA177" t="inlineStr"/>
+      <c r="CB177" t="inlineStr"/>
+      <c r="CC177" t="inlineStr"/>
+      <c r="CD177" t="inlineStr"/>
+      <c r="CE177" t="inlineStr"/>
+      <c r="CF177" t="inlineStr"/>
+      <c r="CG177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -26591,6 +29954,33 @@
       <c r="BT178" t="inlineStr"/>
       <c r="BU178" t="inlineStr"/>
       <c r="BV178" t="inlineStr"/>
+      <c r="BW178" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY178" t="inlineStr"/>
+      <c r="BZ178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB178" t="inlineStr"/>
+      <c r="CC178" t="inlineStr"/>
+      <c r="CD178" t="inlineStr"/>
+      <c r="CE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF178" t="inlineStr"/>
+      <c r="CG178" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -26717,6 +30107,33 @@
       <c r="BT179" t="inlineStr"/>
       <c r="BU179" t="inlineStr"/>
       <c r="BV179" t="inlineStr"/>
+      <c r="BW179" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY179" t="inlineStr"/>
+      <c r="BZ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB179" t="inlineStr"/>
+      <c r="CC179" t="inlineStr"/>
+      <c r="CD179" t="inlineStr"/>
+      <c r="CE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF179" t="inlineStr"/>
+      <c r="CG179" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -26843,6 +30260,17 @@
       <c r="BT180" t="inlineStr"/>
       <c r="BU180" t="inlineStr"/>
       <c r="BV180" t="inlineStr"/>
+      <c r="BW180" t="inlineStr"/>
+      <c r="BX180" t="inlineStr"/>
+      <c r="BY180" t="inlineStr"/>
+      <c r="BZ180" t="inlineStr"/>
+      <c r="CA180" t="inlineStr"/>
+      <c r="CB180" t="inlineStr"/>
+      <c r="CC180" t="inlineStr"/>
+      <c r="CD180" t="inlineStr"/>
+      <c r="CE180" t="inlineStr"/>
+      <c r="CF180" t="inlineStr"/>
+      <c r="CG180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -26969,6 +30397,33 @@
       <c r="BT181" t="inlineStr"/>
       <c r="BU181" t="inlineStr"/>
       <c r="BV181" t="inlineStr"/>
+      <c r="BW181" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY181" t="inlineStr"/>
+      <c r="BZ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB181" t="inlineStr"/>
+      <c r="CC181" t="inlineStr"/>
+      <c r="CD181" t="inlineStr"/>
+      <c r="CE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF181" t="inlineStr"/>
+      <c r="CG181" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -27095,6 +30550,37 @@
       <c r="BT182" t="inlineStr"/>
       <c r="BU182" t="inlineStr"/>
       <c r="BV182" t="inlineStr"/>
+      <c r="BW182" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY182" t="inlineStr"/>
+      <c r="BZ182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB182" t="inlineStr"/>
+      <c r="CC182" t="inlineStr"/>
+      <c r="CD182" t="inlineStr"/>
+      <c r="CE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF182" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
+      <c r="CG182" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -27221,6 +30707,17 @@
       <c r="BT183" t="inlineStr"/>
       <c r="BU183" t="inlineStr"/>
       <c r="BV183" t="inlineStr"/>
+      <c r="BW183" t="inlineStr"/>
+      <c r="BX183" t="inlineStr"/>
+      <c r="BY183" t="inlineStr"/>
+      <c r="BZ183" t="inlineStr"/>
+      <c r="CA183" t="inlineStr"/>
+      <c r="CB183" t="inlineStr"/>
+      <c r="CC183" t="inlineStr"/>
+      <c r="CD183" t="inlineStr"/>
+      <c r="CE183" t="inlineStr"/>
+      <c r="CF183" t="inlineStr"/>
+      <c r="CG183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -27347,6 +30844,17 @@
       <c r="BT184" t="inlineStr"/>
       <c r="BU184" t="inlineStr"/>
       <c r="BV184" t="inlineStr"/>
+      <c r="BW184" t="inlineStr"/>
+      <c r="BX184" t="inlineStr"/>
+      <c r="BY184" t="inlineStr"/>
+      <c r="BZ184" t="inlineStr"/>
+      <c r="CA184" t="inlineStr"/>
+      <c r="CB184" t="inlineStr"/>
+      <c r="CC184" t="inlineStr"/>
+      <c r="CD184" t="inlineStr"/>
+      <c r="CE184" t="inlineStr"/>
+      <c r="CF184" t="inlineStr"/>
+      <c r="CG184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -27473,6 +30981,33 @@
       <c r="BT185" t="inlineStr"/>
       <c r="BU185" t="inlineStr"/>
       <c r="BV185" t="inlineStr"/>
+      <c r="BW185" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY185" t="inlineStr"/>
+      <c r="BZ185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB185" t="inlineStr"/>
+      <c r="CC185" t="inlineStr"/>
+      <c r="CD185" t="inlineStr"/>
+      <c r="CE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF185" t="inlineStr"/>
+      <c r="CG185" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -27599,6 +31134,33 @@
       <c r="BT186" t="inlineStr"/>
       <c r="BU186" t="inlineStr"/>
       <c r="BV186" t="inlineStr"/>
+      <c r="BW186" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY186" t="inlineStr"/>
+      <c r="BZ186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB186" t="inlineStr"/>
+      <c r="CC186" t="inlineStr"/>
+      <c r="CD186" t="inlineStr"/>
+      <c r="CE186" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF186" t="inlineStr"/>
+      <c r="CG186" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -27725,6 +31287,17 @@
       <c r="BT187" t="inlineStr"/>
       <c r="BU187" t="inlineStr"/>
       <c r="BV187" t="inlineStr"/>
+      <c r="BW187" t="inlineStr"/>
+      <c r="BX187" t="inlineStr"/>
+      <c r="BY187" t="inlineStr"/>
+      <c r="BZ187" t="inlineStr"/>
+      <c r="CA187" t="inlineStr"/>
+      <c r="CB187" t="inlineStr"/>
+      <c r="CC187" t="inlineStr"/>
+      <c r="CD187" t="inlineStr"/>
+      <c r="CE187" t="inlineStr"/>
+      <c r="CF187" t="inlineStr"/>
+      <c r="CG187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -27851,6 +31424,33 @@
       <c r="BT188" t="inlineStr"/>
       <c r="BU188" t="inlineStr"/>
       <c r="BV188" t="inlineStr"/>
+      <c r="BW188" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY188" t="inlineStr"/>
+      <c r="BZ188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB188" t="inlineStr"/>
+      <c r="CC188" t="inlineStr"/>
+      <c r="CD188" t="inlineStr"/>
+      <c r="CE188" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF188" t="inlineStr"/>
+      <c r="CG188" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -27977,6 +31577,17 @@
       <c r="BT189" t="inlineStr"/>
       <c r="BU189" t="inlineStr"/>
       <c r="BV189" t="inlineStr"/>
+      <c r="BW189" t="inlineStr"/>
+      <c r="BX189" t="inlineStr"/>
+      <c r="BY189" t="inlineStr"/>
+      <c r="BZ189" t="inlineStr"/>
+      <c r="CA189" t="inlineStr"/>
+      <c r="CB189" t="inlineStr"/>
+      <c r="CC189" t="inlineStr"/>
+      <c r="CD189" t="inlineStr"/>
+      <c r="CE189" t="inlineStr"/>
+      <c r="CF189" t="inlineStr"/>
+      <c r="CG189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -28103,6 +31714,33 @@
       <c r="BT190" t="inlineStr"/>
       <c r="BU190" t="inlineStr"/>
       <c r="BV190" t="inlineStr"/>
+      <c r="BW190" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY190" t="inlineStr"/>
+      <c r="BZ190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB190" t="inlineStr"/>
+      <c r="CC190" t="inlineStr"/>
+      <c r="CD190" t="inlineStr"/>
+      <c r="CE190" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF190" t="inlineStr"/>
+      <c r="CG190" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -28229,6 +31867,33 @@
       <c r="BT191" t="inlineStr"/>
       <c r="BU191" t="inlineStr"/>
       <c r="BV191" t="inlineStr"/>
+      <c r="BW191" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY191" t="inlineStr"/>
+      <c r="BZ191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB191" t="inlineStr"/>
+      <c r="CC191" t="inlineStr"/>
+      <c r="CD191" t="inlineStr"/>
+      <c r="CE191" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF191" t="inlineStr"/>
+      <c r="CG191" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -28355,6 +32020,33 @@
       <c r="BT192" t="inlineStr"/>
       <c r="BU192" t="inlineStr"/>
       <c r="BV192" t="inlineStr"/>
+      <c r="BW192" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY192" t="inlineStr"/>
+      <c r="BZ192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB192" t="inlineStr"/>
+      <c r="CC192" t="inlineStr"/>
+      <c r="CD192" t="inlineStr"/>
+      <c r="CE192" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF192" t="inlineStr"/>
+      <c r="CG192" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -28481,6 +32173,17 @@
       <c r="BT193" t="inlineStr"/>
       <c r="BU193" t="inlineStr"/>
       <c r="BV193" t="inlineStr"/>
+      <c r="BW193" t="inlineStr"/>
+      <c r="BX193" t="inlineStr"/>
+      <c r="BY193" t="inlineStr"/>
+      <c r="BZ193" t="inlineStr"/>
+      <c r="CA193" t="inlineStr"/>
+      <c r="CB193" t="inlineStr"/>
+      <c r="CC193" t="inlineStr"/>
+      <c r="CD193" t="inlineStr"/>
+      <c r="CE193" t="inlineStr"/>
+      <c r="CF193" t="inlineStr"/>
+      <c r="CG193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -28607,6 +32310,17 @@
       <c r="BT194" t="inlineStr"/>
       <c r="BU194" t="inlineStr"/>
       <c r="BV194" t="inlineStr"/>
+      <c r="BW194" t="inlineStr"/>
+      <c r="BX194" t="inlineStr"/>
+      <c r="BY194" t="inlineStr"/>
+      <c r="BZ194" t="inlineStr"/>
+      <c r="CA194" t="inlineStr"/>
+      <c r="CB194" t="inlineStr"/>
+      <c r="CC194" t="inlineStr"/>
+      <c r="CD194" t="inlineStr"/>
+      <c r="CE194" t="inlineStr"/>
+      <c r="CF194" t="inlineStr"/>
+      <c r="CG194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -28733,6 +32447,17 @@
       <c r="BT195" t="inlineStr"/>
       <c r="BU195" t="inlineStr"/>
       <c r="BV195" t="inlineStr"/>
+      <c r="BW195" t="inlineStr"/>
+      <c r="BX195" t="inlineStr"/>
+      <c r="BY195" t="inlineStr"/>
+      <c r="BZ195" t="inlineStr"/>
+      <c r="CA195" t="inlineStr"/>
+      <c r="CB195" t="inlineStr"/>
+      <c r="CC195" t="inlineStr"/>
+      <c r="CD195" t="inlineStr"/>
+      <c r="CE195" t="inlineStr"/>
+      <c r="CF195" t="inlineStr"/>
+      <c r="CG195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -28859,6 +32584,33 @@
       <c r="BT196" t="inlineStr"/>
       <c r="BU196" t="inlineStr"/>
       <c r="BV196" t="inlineStr"/>
+      <c r="BW196" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY196" t="inlineStr"/>
+      <c r="BZ196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB196" t="inlineStr"/>
+      <c r="CC196" t="inlineStr"/>
+      <c r="CD196" t="inlineStr"/>
+      <c r="CE196" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF196" t="inlineStr"/>
+      <c r="CG196" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -28985,6 +32737,17 @@
       <c r="BT197" t="inlineStr"/>
       <c r="BU197" t="inlineStr"/>
       <c r="BV197" t="inlineStr"/>
+      <c r="BW197" t="inlineStr"/>
+      <c r="BX197" t="inlineStr"/>
+      <c r="BY197" t="inlineStr"/>
+      <c r="BZ197" t="inlineStr"/>
+      <c r="CA197" t="inlineStr"/>
+      <c r="CB197" t="inlineStr"/>
+      <c r="CC197" t="inlineStr"/>
+      <c r="CD197" t="inlineStr"/>
+      <c r="CE197" t="inlineStr"/>
+      <c r="CF197" t="inlineStr"/>
+      <c r="CG197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -29111,6 +32874,17 @@
       <c r="BT198" t="inlineStr"/>
       <c r="BU198" t="inlineStr"/>
       <c r="BV198" t="inlineStr"/>
+      <c r="BW198" t="inlineStr"/>
+      <c r="BX198" t="inlineStr"/>
+      <c r="BY198" t="inlineStr"/>
+      <c r="BZ198" t="inlineStr"/>
+      <c r="CA198" t="inlineStr"/>
+      <c r="CB198" t="inlineStr"/>
+      <c r="CC198" t="inlineStr"/>
+      <c r="CD198" t="inlineStr"/>
+      <c r="CE198" t="inlineStr"/>
+      <c r="CF198" t="inlineStr"/>
+      <c r="CG198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -29237,6 +33011,33 @@
       <c r="BT199" t="inlineStr"/>
       <c r="BU199" t="inlineStr"/>
       <c r="BV199" t="inlineStr"/>
+      <c r="BW199" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY199" t="inlineStr"/>
+      <c r="BZ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB199" t="inlineStr"/>
+      <c r="CC199" t="inlineStr"/>
+      <c r="CD199" t="inlineStr"/>
+      <c r="CE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF199" t="inlineStr"/>
+      <c r="CG199" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -29363,6 +33164,37 @@
       <c r="BT200" t="inlineStr"/>
       <c r="BU200" t="inlineStr"/>
       <c r="BV200" t="inlineStr"/>
+      <c r="BW200" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY200" t="inlineStr"/>
+      <c r="BZ200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB200" t="inlineStr"/>
+      <c r="CC200" t="inlineStr"/>
+      <c r="CD200" t="inlineStr"/>
+      <c r="CE200" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF200" t="inlineStr">
+        <is>
+          <t>中信</t>
+        </is>
+      </c>
+      <c r="CG200" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -29489,6 +33321,37 @@
       <c r="BT201" t="inlineStr"/>
       <c r="BU201" t="inlineStr"/>
       <c r="BV201" t="inlineStr"/>
+      <c r="BW201" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY201" t="inlineStr"/>
+      <c r="BZ201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB201" t="inlineStr"/>
+      <c r="CC201" t="inlineStr"/>
+      <c r="CD201" t="inlineStr"/>
+      <c r="CE201" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF201" t="inlineStr">
+        <is>
+          <t>兆豐</t>
+        </is>
+      </c>
+      <c r="CG201" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -29615,6 +33478,33 @@
       <c r="BT202" t="inlineStr"/>
       <c r="BU202" t="inlineStr"/>
       <c r="BV202" t="inlineStr"/>
+      <c r="BW202" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY202" t="inlineStr"/>
+      <c r="BZ202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB202" t="inlineStr"/>
+      <c r="CC202" t="inlineStr"/>
+      <c r="CD202" t="inlineStr"/>
+      <c r="CE202" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF202" t="inlineStr"/>
+      <c r="CG202" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -29741,6 +33631,33 @@
       <c r="BT203" t="inlineStr"/>
       <c r="BU203" t="inlineStr"/>
       <c r="BV203" t="inlineStr"/>
+      <c r="BW203" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY203" t="inlineStr"/>
+      <c r="BZ203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB203" t="inlineStr"/>
+      <c r="CC203" t="inlineStr"/>
+      <c r="CD203" t="inlineStr"/>
+      <c r="CE203" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF203" t="inlineStr"/>
+      <c r="CG203" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -29867,6 +33784,17 @@
       <c r="BT204" t="inlineStr"/>
       <c r="BU204" t="inlineStr"/>
       <c r="BV204" t="inlineStr"/>
+      <c r="BW204" t="inlineStr"/>
+      <c r="BX204" t="inlineStr"/>
+      <c r="BY204" t="inlineStr"/>
+      <c r="BZ204" t="inlineStr"/>
+      <c r="CA204" t="inlineStr"/>
+      <c r="CB204" t="inlineStr"/>
+      <c r="CC204" t="inlineStr"/>
+      <c r="CD204" t="inlineStr"/>
+      <c r="CE204" t="inlineStr"/>
+      <c r="CF204" t="inlineStr"/>
+      <c r="CG204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -29993,6 +33921,33 @@
       <c r="BT205" t="inlineStr"/>
       <c r="BU205" t="inlineStr"/>
       <c r="BV205" t="inlineStr"/>
+      <c r="BW205" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX205" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY205" t="inlineStr"/>
+      <c r="BZ205" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA205" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB205" t="inlineStr"/>
+      <c r="CC205" t="inlineStr"/>
+      <c r="CD205" t="inlineStr"/>
+      <c r="CE205" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF205" t="inlineStr"/>
+      <c r="CG205" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -30119,6 +34074,33 @@
       <c r="BT206" t="inlineStr"/>
       <c r="BU206" t="inlineStr"/>
       <c r="BV206" t="inlineStr"/>
+      <c r="BW206" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX206" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY206" t="inlineStr"/>
+      <c r="BZ206" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA206" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB206" t="inlineStr"/>
+      <c r="CC206" t="inlineStr"/>
+      <c r="CD206" t="inlineStr"/>
+      <c r="CE206" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF206" t="inlineStr"/>
+      <c r="CG206" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -30245,6 +34227,17 @@
       <c r="BT207" t="inlineStr"/>
       <c r="BU207" t="inlineStr"/>
       <c r="BV207" t="inlineStr"/>
+      <c r="BW207" t="inlineStr"/>
+      <c r="BX207" t="inlineStr"/>
+      <c r="BY207" t="inlineStr"/>
+      <c r="BZ207" t="inlineStr"/>
+      <c r="CA207" t="inlineStr"/>
+      <c r="CB207" t="inlineStr"/>
+      <c r="CC207" t="inlineStr"/>
+      <c r="CD207" t="inlineStr"/>
+      <c r="CE207" t="inlineStr"/>
+      <c r="CF207" t="inlineStr"/>
+      <c r="CG207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -30371,6 +34364,17 @@
       <c r="BT208" t="inlineStr"/>
       <c r="BU208" t="inlineStr"/>
       <c r="BV208" t="inlineStr"/>
+      <c r="BW208" t="inlineStr"/>
+      <c r="BX208" t="inlineStr"/>
+      <c r="BY208" t="inlineStr"/>
+      <c r="BZ208" t="inlineStr"/>
+      <c r="CA208" t="inlineStr"/>
+      <c r="CB208" t="inlineStr"/>
+      <c r="CC208" t="inlineStr"/>
+      <c r="CD208" t="inlineStr"/>
+      <c r="CE208" t="inlineStr"/>
+      <c r="CF208" t="inlineStr"/>
+      <c r="CG208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -30497,6 +34501,33 @@
       <c r="BT209" t="inlineStr"/>
       <c r="BU209" t="inlineStr"/>
       <c r="BV209" t="inlineStr"/>
+      <c r="BW209" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY209" t="inlineStr"/>
+      <c r="BZ209" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA209" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB209" t="inlineStr"/>
+      <c r="CC209" t="inlineStr"/>
+      <c r="CD209" t="inlineStr"/>
+      <c r="CE209" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF209" t="inlineStr"/>
+      <c r="CG209" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -30623,6 +34654,17 @@
       <c r="BT210" t="inlineStr"/>
       <c r="BU210" t="inlineStr"/>
       <c r="BV210" t="inlineStr"/>
+      <c r="BW210" t="inlineStr"/>
+      <c r="BX210" t="inlineStr"/>
+      <c r="BY210" t="inlineStr"/>
+      <c r="BZ210" t="inlineStr"/>
+      <c r="CA210" t="inlineStr"/>
+      <c r="CB210" t="inlineStr"/>
+      <c r="CC210" t="inlineStr"/>
+      <c r="CD210" t="inlineStr"/>
+      <c r="CE210" t="inlineStr"/>
+      <c r="CF210" t="inlineStr"/>
+      <c r="CG210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -30749,6 +34791,33 @@
       <c r="BT211" t="inlineStr"/>
       <c r="BU211" t="inlineStr"/>
       <c r="BV211" t="inlineStr"/>
+      <c r="BW211" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY211" t="inlineStr"/>
+      <c r="BZ211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB211" t="inlineStr"/>
+      <c r="CC211" t="inlineStr"/>
+      <c r="CD211" t="inlineStr"/>
+      <c r="CE211" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF211" t="inlineStr"/>
+      <c r="CG211" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -30875,6 +34944,17 @@
       <c r="BT212" t="inlineStr"/>
       <c r="BU212" t="inlineStr"/>
       <c r="BV212" t="inlineStr"/>
+      <c r="BW212" t="inlineStr"/>
+      <c r="BX212" t="inlineStr"/>
+      <c r="BY212" t="inlineStr"/>
+      <c r="BZ212" t="inlineStr"/>
+      <c r="CA212" t="inlineStr"/>
+      <c r="CB212" t="inlineStr"/>
+      <c r="CC212" t="inlineStr"/>
+      <c r="CD212" t="inlineStr"/>
+      <c r="CE212" t="inlineStr"/>
+      <c r="CF212" t="inlineStr"/>
+      <c r="CG212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -31001,6 +35081,17 @@
       <c r="BT213" t="inlineStr"/>
       <c r="BU213" t="inlineStr"/>
       <c r="BV213" t="inlineStr"/>
+      <c r="BW213" t="inlineStr"/>
+      <c r="BX213" t="inlineStr"/>
+      <c r="BY213" t="inlineStr"/>
+      <c r="BZ213" t="inlineStr"/>
+      <c r="CA213" t="inlineStr"/>
+      <c r="CB213" t="inlineStr"/>
+      <c r="CC213" t="inlineStr"/>
+      <c r="CD213" t="inlineStr"/>
+      <c r="CE213" t="inlineStr"/>
+      <c r="CF213" t="inlineStr"/>
+      <c r="CG213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -31127,6 +35218,17 @@
       <c r="BT214" t="inlineStr"/>
       <c r="BU214" t="inlineStr"/>
       <c r="BV214" t="inlineStr"/>
+      <c r="BW214" t="inlineStr"/>
+      <c r="BX214" t="inlineStr"/>
+      <c r="BY214" t="inlineStr"/>
+      <c r="BZ214" t="inlineStr"/>
+      <c r="CA214" t="inlineStr"/>
+      <c r="CB214" t="inlineStr"/>
+      <c r="CC214" t="inlineStr"/>
+      <c r="CD214" t="inlineStr"/>
+      <c r="CE214" t="inlineStr"/>
+      <c r="CF214" t="inlineStr"/>
+      <c r="CG214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -31253,6 +35355,17 @@
       <c r="BT215" t="inlineStr"/>
       <c r="BU215" t="inlineStr"/>
       <c r="BV215" t="inlineStr"/>
+      <c r="BW215" t="inlineStr"/>
+      <c r="BX215" t="inlineStr"/>
+      <c r="BY215" t="inlineStr"/>
+      <c r="BZ215" t="inlineStr"/>
+      <c r="CA215" t="inlineStr"/>
+      <c r="CB215" t="inlineStr"/>
+      <c r="CC215" t="inlineStr"/>
+      <c r="CD215" t="inlineStr"/>
+      <c r="CE215" t="inlineStr"/>
+      <c r="CF215" t="inlineStr"/>
+      <c r="CG215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -31379,6 +35492,33 @@
       <c r="BT216" t="inlineStr"/>
       <c r="BU216" t="inlineStr"/>
       <c r="BV216" t="inlineStr"/>
+      <c r="BW216" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX216" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY216" t="inlineStr"/>
+      <c r="BZ216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB216" t="inlineStr"/>
+      <c r="CC216" t="inlineStr"/>
+      <c r="CD216" t="inlineStr"/>
+      <c r="CE216" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF216" t="inlineStr"/>
+      <c r="CG216" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -31505,6 +35645,33 @@
       <c r="BT217" t="inlineStr"/>
       <c r="BU217" t="inlineStr"/>
       <c r="BV217" t="inlineStr"/>
+      <c r="BW217" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY217" t="inlineStr"/>
+      <c r="BZ217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB217" t="inlineStr"/>
+      <c r="CC217" t="inlineStr"/>
+      <c r="CD217" t="inlineStr"/>
+      <c r="CE217" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF217" t="inlineStr"/>
+      <c r="CG217" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -31631,6 +35798,33 @@
       <c r="BT218" t="inlineStr"/>
       <c r="BU218" t="inlineStr"/>
       <c r="BV218" t="inlineStr"/>
+      <c r="BW218" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX218" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY218" t="inlineStr"/>
+      <c r="BZ218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB218" t="inlineStr"/>
+      <c r="CC218" t="inlineStr"/>
+      <c r="CD218" t="inlineStr"/>
+      <c r="CE218" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF218" t="inlineStr"/>
+      <c r="CG218" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -31757,6 +35951,17 @@
       <c r="BT219" t="inlineStr"/>
       <c r="BU219" t="inlineStr"/>
       <c r="BV219" t="inlineStr"/>
+      <c r="BW219" t="inlineStr"/>
+      <c r="BX219" t="inlineStr"/>
+      <c r="BY219" t="inlineStr"/>
+      <c r="BZ219" t="inlineStr"/>
+      <c r="CA219" t="inlineStr"/>
+      <c r="CB219" t="inlineStr"/>
+      <c r="CC219" t="inlineStr"/>
+      <c r="CD219" t="inlineStr"/>
+      <c r="CE219" t="inlineStr"/>
+      <c r="CF219" t="inlineStr"/>
+      <c r="CG219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -31883,6 +36088,33 @@
       <c r="BT220" t="inlineStr"/>
       <c r="BU220" t="inlineStr"/>
       <c r="BV220" t="inlineStr"/>
+      <c r="BW220" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX220" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY220" t="inlineStr"/>
+      <c r="BZ220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB220" t="inlineStr"/>
+      <c r="CC220" t="inlineStr"/>
+      <c r="CD220" t="inlineStr"/>
+      <c r="CE220" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF220" t="inlineStr"/>
+      <c r="CG220" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -32009,6 +36241,33 @@
       <c r="BT221" t="inlineStr"/>
       <c r="BU221" t="inlineStr"/>
       <c r="BV221" t="inlineStr"/>
+      <c r="BW221" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY221" t="inlineStr"/>
+      <c r="BZ221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB221" t="inlineStr"/>
+      <c r="CC221" t="inlineStr"/>
+      <c r="CD221" t="inlineStr"/>
+      <c r="CE221" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF221" t="inlineStr"/>
+      <c r="CG221" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -32135,6 +36394,17 @@
       <c r="BT222" t="inlineStr"/>
       <c r="BU222" t="inlineStr"/>
       <c r="BV222" t="inlineStr"/>
+      <c r="BW222" t="inlineStr"/>
+      <c r="BX222" t="inlineStr"/>
+      <c r="BY222" t="inlineStr"/>
+      <c r="BZ222" t="inlineStr"/>
+      <c r="CA222" t="inlineStr"/>
+      <c r="CB222" t="inlineStr"/>
+      <c r="CC222" t="inlineStr"/>
+      <c r="CD222" t="inlineStr"/>
+      <c r="CE222" t="inlineStr"/>
+      <c r="CF222" t="inlineStr"/>
+      <c r="CG222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -32261,6 +36531,33 @@
       <c r="BT223" t="inlineStr"/>
       <c r="BU223" t="inlineStr"/>
       <c r="BV223" t="inlineStr"/>
+      <c r="BW223" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX223" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY223" t="inlineStr"/>
+      <c r="BZ223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB223" t="inlineStr"/>
+      <c r="CC223" t="inlineStr"/>
+      <c r="CD223" t="inlineStr"/>
+      <c r="CE223" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF223" t="inlineStr"/>
+      <c r="CG223" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -32387,6 +36684,33 @@
       <c r="BT224" t="inlineStr"/>
       <c r="BU224" t="inlineStr"/>
       <c r="BV224" t="inlineStr"/>
+      <c r="BW224" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX224" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY224" t="inlineStr"/>
+      <c r="BZ224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB224" t="inlineStr"/>
+      <c r="CC224" t="inlineStr"/>
+      <c r="CD224" t="inlineStr"/>
+      <c r="CE224" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF224" t="inlineStr"/>
+      <c r="CG224" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -32513,6 +36837,17 @@
       <c r="BT225" t="inlineStr"/>
       <c r="BU225" t="inlineStr"/>
       <c r="BV225" t="inlineStr"/>
+      <c r="BW225" t="inlineStr"/>
+      <c r="BX225" t="inlineStr"/>
+      <c r="BY225" t="inlineStr"/>
+      <c r="BZ225" t="inlineStr"/>
+      <c r="CA225" t="inlineStr"/>
+      <c r="CB225" t="inlineStr"/>
+      <c r="CC225" t="inlineStr"/>
+      <c r="CD225" t="inlineStr"/>
+      <c r="CE225" t="inlineStr"/>
+      <c r="CF225" t="inlineStr"/>
+      <c r="CG225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -32639,6 +36974,17 @@
       <c r="BT226" t="inlineStr"/>
       <c r="BU226" t="inlineStr"/>
       <c r="BV226" t="inlineStr"/>
+      <c r="BW226" t="inlineStr"/>
+      <c r="BX226" t="inlineStr"/>
+      <c r="BY226" t="inlineStr"/>
+      <c r="BZ226" t="inlineStr"/>
+      <c r="CA226" t="inlineStr"/>
+      <c r="CB226" t="inlineStr"/>
+      <c r="CC226" t="inlineStr"/>
+      <c r="CD226" t="inlineStr"/>
+      <c r="CE226" t="inlineStr"/>
+      <c r="CF226" t="inlineStr"/>
+      <c r="CG226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -32765,6 +37111,17 @@
       <c r="BT227" t="inlineStr"/>
       <c r="BU227" t="inlineStr"/>
       <c r="BV227" t="inlineStr"/>
+      <c r="BW227" t="inlineStr"/>
+      <c r="BX227" t="inlineStr"/>
+      <c r="BY227" t="inlineStr"/>
+      <c r="BZ227" t="inlineStr"/>
+      <c r="CA227" t="inlineStr"/>
+      <c r="CB227" t="inlineStr"/>
+      <c r="CC227" t="inlineStr"/>
+      <c r="CD227" t="inlineStr"/>
+      <c r="CE227" t="inlineStr"/>
+      <c r="CF227" t="inlineStr"/>
+      <c r="CG227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -32891,6 +37248,33 @@
       <c r="BT228" t="inlineStr"/>
       <c r="BU228" t="inlineStr"/>
       <c r="BV228" t="inlineStr"/>
+      <c r="BW228" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY228" t="inlineStr"/>
+      <c r="BZ228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB228" t="inlineStr"/>
+      <c r="CC228" t="inlineStr"/>
+      <c r="CD228" t="inlineStr"/>
+      <c r="CE228" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF228" t="inlineStr"/>
+      <c r="CG228" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -33017,6 +37401,33 @@
       <c r="BT229" t="inlineStr"/>
       <c r="BU229" t="inlineStr"/>
       <c r="BV229" t="inlineStr"/>
+      <c r="BW229" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX229" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY229" t="inlineStr"/>
+      <c r="BZ229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB229" t="inlineStr"/>
+      <c r="CC229" t="inlineStr"/>
+      <c r="CD229" t="inlineStr"/>
+      <c r="CE229" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF229" t="inlineStr"/>
+      <c r="CG229" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -33143,6 +37554,33 @@
       <c r="BT230" t="inlineStr"/>
       <c r="BU230" t="inlineStr"/>
       <c r="BV230" t="inlineStr"/>
+      <c r="BW230" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX230" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY230" t="inlineStr"/>
+      <c r="BZ230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB230" t="inlineStr"/>
+      <c r="CC230" t="inlineStr"/>
+      <c r="CD230" t="inlineStr"/>
+      <c r="CE230" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF230" t="inlineStr"/>
+      <c r="CG230" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -33269,6 +37707,17 @@
       <c r="BT231" t="inlineStr"/>
       <c r="BU231" t="inlineStr"/>
       <c r="BV231" t="inlineStr"/>
+      <c r="BW231" t="inlineStr"/>
+      <c r="BX231" t="inlineStr"/>
+      <c r="BY231" t="inlineStr"/>
+      <c r="BZ231" t="inlineStr"/>
+      <c r="CA231" t="inlineStr"/>
+      <c r="CB231" t="inlineStr"/>
+      <c r="CC231" t="inlineStr"/>
+      <c r="CD231" t="inlineStr"/>
+      <c r="CE231" t="inlineStr"/>
+      <c r="CF231" t="inlineStr"/>
+      <c r="CG231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -33395,6 +37844,33 @@
       <c r="BT232" t="inlineStr"/>
       <c r="BU232" t="inlineStr"/>
       <c r="BV232" t="inlineStr"/>
+      <c r="BW232" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX232" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY232" t="inlineStr"/>
+      <c r="BZ232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB232" t="inlineStr"/>
+      <c r="CC232" t="inlineStr"/>
+      <c r="CD232" t="inlineStr"/>
+      <c r="CE232" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF232" t="inlineStr"/>
+      <c r="CG232" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -33521,6 +37997,33 @@
       <c r="BT233" t="inlineStr"/>
       <c r="BU233" t="inlineStr"/>
       <c r="BV233" t="inlineStr"/>
+      <c r="BW233" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX233" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY233" t="inlineStr"/>
+      <c r="BZ233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB233" t="inlineStr"/>
+      <c r="CC233" t="inlineStr"/>
+      <c r="CD233" t="inlineStr"/>
+      <c r="CE233" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF233" t="inlineStr"/>
+      <c r="CG233" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -33647,6 +38150,33 @@
       <c r="BT234" t="inlineStr"/>
       <c r="BU234" t="inlineStr"/>
       <c r="BV234" t="inlineStr"/>
+      <c r="BW234" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX234" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY234" t="inlineStr"/>
+      <c r="BZ234" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA234" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB234" t="inlineStr"/>
+      <c r="CC234" t="inlineStr"/>
+      <c r="CD234" t="inlineStr"/>
+      <c r="CE234" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF234" t="inlineStr"/>
+      <c r="CG234" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -33773,6 +38303,33 @@
       <c r="BT235" t="inlineStr"/>
       <c r="BU235" t="inlineStr"/>
       <c r="BV235" t="inlineStr"/>
+      <c r="BW235" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX235" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY235" t="inlineStr"/>
+      <c r="BZ235" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA235" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB235" t="inlineStr"/>
+      <c r="CC235" t="inlineStr"/>
+      <c r="CD235" t="inlineStr"/>
+      <c r="CE235" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF235" t="inlineStr"/>
+      <c r="CG235" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -33899,6 +38456,33 @@
       <c r="BT236" t="inlineStr"/>
       <c r="BU236" t="inlineStr"/>
       <c r="BV236" t="inlineStr"/>
+      <c r="BW236" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX236" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY236" t="inlineStr"/>
+      <c r="BZ236" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA236" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB236" t="inlineStr"/>
+      <c r="CC236" t="inlineStr"/>
+      <c r="CD236" t="inlineStr"/>
+      <c r="CE236" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF236" t="inlineStr"/>
+      <c r="CG236" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -34025,6 +38609,37 @@
       <c r="BT237" t="inlineStr"/>
       <c r="BU237" t="inlineStr"/>
       <c r="BV237" t="inlineStr"/>
+      <c r="BW237" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX237" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY237" t="inlineStr"/>
+      <c r="BZ237" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA237" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB237" t="inlineStr"/>
+      <c r="CC237" t="inlineStr"/>
+      <c r="CD237" t="inlineStr"/>
+      <c r="CE237" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF237" t="inlineStr">
+        <is>
+          <t>第一</t>
+        </is>
+      </c>
+      <c r="CG237" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -34151,6 +38766,33 @@
       <c r="BT238" t="inlineStr"/>
       <c r="BU238" t="inlineStr"/>
       <c r="BV238" t="inlineStr"/>
+      <c r="BW238" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX238" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY238" t="inlineStr"/>
+      <c r="BZ238" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA238" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB238" t="inlineStr"/>
+      <c r="CC238" t="inlineStr"/>
+      <c r="CD238" t="inlineStr"/>
+      <c r="CE238" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF238" t="inlineStr"/>
+      <c r="CG238" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -34277,6 +38919,33 @@
       <c r="BT239" t="inlineStr"/>
       <c r="BU239" t="inlineStr"/>
       <c r="BV239" t="inlineStr"/>
+      <c r="BW239" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX239" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY239" t="inlineStr"/>
+      <c r="BZ239" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA239" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB239" t="inlineStr"/>
+      <c r="CC239" t="inlineStr"/>
+      <c r="CD239" t="inlineStr"/>
+      <c r="CE239" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF239" t="inlineStr"/>
+      <c r="CG239" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -34403,6 +39072,33 @@
       <c r="BT240" t="inlineStr"/>
       <c r="BU240" t="inlineStr"/>
       <c r="BV240" t="inlineStr"/>
+      <c r="BW240" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY240" t="inlineStr"/>
+      <c r="BZ240" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA240" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB240" t="inlineStr"/>
+      <c r="CC240" t="inlineStr"/>
+      <c r="CD240" t="inlineStr"/>
+      <c r="CE240" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF240" t="inlineStr"/>
+      <c r="CG240" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -34529,6 +39225,33 @@
       <c r="BT241" t="inlineStr"/>
       <c r="BU241" t="inlineStr"/>
       <c r="BV241" t="inlineStr"/>
+      <c r="BW241" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX241" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY241" t="inlineStr"/>
+      <c r="BZ241" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA241" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB241" t="inlineStr"/>
+      <c r="CC241" t="inlineStr"/>
+      <c r="CD241" t="inlineStr"/>
+      <c r="CE241" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF241" t="inlineStr"/>
+      <c r="CG241" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -34655,6 +39378,37 @@
       <c r="BT242" t="inlineStr"/>
       <c r="BU242" t="inlineStr"/>
       <c r="BV242" t="inlineStr"/>
+      <c r="BW242" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX242" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY242" t="inlineStr"/>
+      <c r="BZ242" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA242" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB242" t="inlineStr"/>
+      <c r="CC242" t="inlineStr"/>
+      <c r="CD242" t="inlineStr"/>
+      <c r="CE242" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF242" t="inlineStr">
+        <is>
+          <t>玉山</t>
+        </is>
+      </c>
+      <c r="CG242" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -34781,6 +39535,33 @@
       <c r="BT243" t="inlineStr"/>
       <c r="BU243" t="inlineStr"/>
       <c r="BV243" t="inlineStr"/>
+      <c r="BW243" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX243" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY243" t="inlineStr"/>
+      <c r="BZ243" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA243" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB243" t="inlineStr"/>
+      <c r="CC243" t="inlineStr"/>
+      <c r="CD243" t="inlineStr"/>
+      <c r="CE243" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF243" t="inlineStr"/>
+      <c r="CG243" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -34907,6 +39688,33 @@
       <c r="BT244" t="inlineStr"/>
       <c r="BU244" t="inlineStr"/>
       <c r="BV244" t="inlineStr"/>
+      <c r="BW244" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX244" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY244" t="inlineStr"/>
+      <c r="BZ244" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA244" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB244" t="inlineStr"/>
+      <c r="CC244" t="inlineStr"/>
+      <c r="CD244" t="inlineStr"/>
+      <c r="CE244" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF244" t="inlineStr"/>
+      <c r="CG244" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -35033,6 +39841,33 @@
       <c r="BT245" t="inlineStr"/>
       <c r="BU245" t="inlineStr"/>
       <c r="BV245" t="inlineStr"/>
+      <c r="BW245" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX245" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY245" t="inlineStr"/>
+      <c r="BZ245" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA245" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB245" t="inlineStr"/>
+      <c r="CC245" t="inlineStr"/>
+      <c r="CD245" t="inlineStr"/>
+      <c r="CE245" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF245" t="inlineStr"/>
+      <c r="CG245" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -35159,6 +39994,17 @@
       <c r="BT246" t="inlineStr"/>
       <c r="BU246" t="inlineStr"/>
       <c r="BV246" t="inlineStr"/>
+      <c r="BW246" t="inlineStr"/>
+      <c r="BX246" t="inlineStr"/>
+      <c r="BY246" t="inlineStr"/>
+      <c r="BZ246" t="inlineStr"/>
+      <c r="CA246" t="inlineStr"/>
+      <c r="CB246" t="inlineStr"/>
+      <c r="CC246" t="inlineStr"/>
+      <c r="CD246" t="inlineStr"/>
+      <c r="CE246" t="inlineStr"/>
+      <c r="CF246" t="inlineStr"/>
+      <c r="CG246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -35285,6 +40131,17 @@
       <c r="BT247" t="inlineStr"/>
       <c r="BU247" t="inlineStr"/>
       <c r="BV247" t="inlineStr"/>
+      <c r="BW247" t="inlineStr"/>
+      <c r="BX247" t="inlineStr"/>
+      <c r="BY247" t="inlineStr"/>
+      <c r="BZ247" t="inlineStr"/>
+      <c r="CA247" t="inlineStr"/>
+      <c r="CB247" t="inlineStr"/>
+      <c r="CC247" t="inlineStr"/>
+      <c r="CD247" t="inlineStr"/>
+      <c r="CE247" t="inlineStr"/>
+      <c r="CF247" t="inlineStr"/>
+      <c r="CG247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -35411,6 +40268,33 @@
       <c r="BT248" t="inlineStr"/>
       <c r="BU248" t="inlineStr"/>
       <c r="BV248" t="inlineStr"/>
+      <c r="BW248" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX248" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY248" t="inlineStr"/>
+      <c r="BZ248" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA248" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB248" t="inlineStr"/>
+      <c r="CC248" t="inlineStr"/>
+      <c r="CD248" t="inlineStr"/>
+      <c r="CE248" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF248" t="inlineStr"/>
+      <c r="CG248" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -35537,6 +40421,17 @@
       <c r="BT249" t="inlineStr"/>
       <c r="BU249" t="inlineStr"/>
       <c r="BV249" t="inlineStr"/>
+      <c r="BW249" t="inlineStr"/>
+      <c r="BX249" t="inlineStr"/>
+      <c r="BY249" t="inlineStr"/>
+      <c r="BZ249" t="inlineStr"/>
+      <c r="CA249" t="inlineStr"/>
+      <c r="CB249" t="inlineStr"/>
+      <c r="CC249" t="inlineStr"/>
+      <c r="CD249" t="inlineStr"/>
+      <c r="CE249" t="inlineStr"/>
+      <c r="CF249" t="inlineStr"/>
+      <c r="CG249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -35663,6 +40558,17 @@
       <c r="BT250" t="inlineStr"/>
       <c r="BU250" t="inlineStr"/>
       <c r="BV250" t="inlineStr"/>
+      <c r="BW250" t="inlineStr"/>
+      <c r="BX250" t="inlineStr"/>
+      <c r="BY250" t="inlineStr"/>
+      <c r="BZ250" t="inlineStr"/>
+      <c r="CA250" t="inlineStr"/>
+      <c r="CB250" t="inlineStr"/>
+      <c r="CC250" t="inlineStr"/>
+      <c r="CD250" t="inlineStr"/>
+      <c r="CE250" t="inlineStr"/>
+      <c r="CF250" t="inlineStr"/>
+      <c r="CG250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -35789,6 +40695,33 @@
       <c r="BT251" t="inlineStr"/>
       <c r="BU251" t="inlineStr"/>
       <c r="BV251" t="inlineStr"/>
+      <c r="BW251" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX251" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY251" t="inlineStr"/>
+      <c r="BZ251" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA251" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB251" t="inlineStr"/>
+      <c r="CC251" t="inlineStr"/>
+      <c r="CD251" t="inlineStr"/>
+      <c r="CE251" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF251" t="inlineStr"/>
+      <c r="CG251" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -35915,6 +40848,17 @@
       <c r="BT252" t="inlineStr"/>
       <c r="BU252" t="inlineStr"/>
       <c r="BV252" t="inlineStr"/>
+      <c r="BW252" t="inlineStr"/>
+      <c r="BX252" t="inlineStr"/>
+      <c r="BY252" t="inlineStr"/>
+      <c r="BZ252" t="inlineStr"/>
+      <c r="CA252" t="inlineStr"/>
+      <c r="CB252" t="inlineStr"/>
+      <c r="CC252" t="inlineStr"/>
+      <c r="CD252" t="inlineStr"/>
+      <c r="CE252" t="inlineStr"/>
+      <c r="CF252" t="inlineStr"/>
+      <c r="CG252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -36041,6 +40985,17 @@
       <c r="BT253" t="inlineStr"/>
       <c r="BU253" t="inlineStr"/>
       <c r="BV253" t="inlineStr"/>
+      <c r="BW253" t="inlineStr"/>
+      <c r="BX253" t="inlineStr"/>
+      <c r="BY253" t="inlineStr"/>
+      <c r="BZ253" t="inlineStr"/>
+      <c r="CA253" t="inlineStr"/>
+      <c r="CB253" t="inlineStr"/>
+      <c r="CC253" t="inlineStr"/>
+      <c r="CD253" t="inlineStr"/>
+      <c r="CE253" t="inlineStr"/>
+      <c r="CF253" t="inlineStr"/>
+      <c r="CG253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -36167,6 +41122,33 @@
       <c r="BT254" t="inlineStr"/>
       <c r="BU254" t="inlineStr"/>
       <c r="BV254" t="inlineStr"/>
+      <c r="BW254" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX254" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY254" t="inlineStr"/>
+      <c r="BZ254" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA254" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB254" t="inlineStr"/>
+      <c r="CC254" t="inlineStr"/>
+      <c r="CD254" t="inlineStr"/>
+      <c r="CE254" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF254" t="inlineStr"/>
+      <c r="CG254" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -36293,6 +41275,33 @@
       <c r="BT255" t="inlineStr"/>
       <c r="BU255" t="inlineStr"/>
       <c r="BV255" t="inlineStr"/>
+      <c r="BW255" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX255" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY255" t="inlineStr"/>
+      <c r="BZ255" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA255" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB255" t="inlineStr"/>
+      <c r="CC255" t="inlineStr"/>
+      <c r="CD255" t="inlineStr"/>
+      <c r="CE255" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF255" t="inlineStr"/>
+      <c r="CG255" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -36419,6 +41428,17 @@
       <c r="BT256" t="inlineStr"/>
       <c r="BU256" t="inlineStr"/>
       <c r="BV256" t="inlineStr"/>
+      <c r="BW256" t="inlineStr"/>
+      <c r="BX256" t="inlineStr"/>
+      <c r="BY256" t="inlineStr"/>
+      <c r="BZ256" t="inlineStr"/>
+      <c r="CA256" t="inlineStr"/>
+      <c r="CB256" t="inlineStr"/>
+      <c r="CC256" t="inlineStr"/>
+      <c r="CD256" t="inlineStr"/>
+      <c r="CE256" t="inlineStr"/>
+      <c r="CF256" t="inlineStr"/>
+      <c r="CG256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -36545,6 +41565,33 @@
       <c r="BT257" t="inlineStr"/>
       <c r="BU257" t="inlineStr"/>
       <c r="BV257" t="inlineStr"/>
+      <c r="BW257" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX257" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY257" t="inlineStr"/>
+      <c r="BZ257" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA257" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB257" t="inlineStr"/>
+      <c r="CC257" t="inlineStr"/>
+      <c r="CD257" t="inlineStr"/>
+      <c r="CE257" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF257" t="inlineStr"/>
+      <c r="CG257" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -36671,6 +41718,17 @@
       <c r="BT258" t="inlineStr"/>
       <c r="BU258" t="inlineStr"/>
       <c r="BV258" t="inlineStr"/>
+      <c r="BW258" t="inlineStr"/>
+      <c r="BX258" t="inlineStr"/>
+      <c r="BY258" t="inlineStr"/>
+      <c r="BZ258" t="inlineStr"/>
+      <c r="CA258" t="inlineStr"/>
+      <c r="CB258" t="inlineStr"/>
+      <c r="CC258" t="inlineStr"/>
+      <c r="CD258" t="inlineStr"/>
+      <c r="CE258" t="inlineStr"/>
+      <c r="CF258" t="inlineStr"/>
+      <c r="CG258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -36797,6 +41855,17 @@
       <c r="BT259" t="inlineStr"/>
       <c r="BU259" t="inlineStr"/>
       <c r="BV259" t="inlineStr"/>
+      <c r="BW259" t="inlineStr"/>
+      <c r="BX259" t="inlineStr"/>
+      <c r="BY259" t="inlineStr"/>
+      <c r="BZ259" t="inlineStr"/>
+      <c r="CA259" t="inlineStr"/>
+      <c r="CB259" t="inlineStr"/>
+      <c r="CC259" t="inlineStr"/>
+      <c r="CD259" t="inlineStr"/>
+      <c r="CE259" t="inlineStr"/>
+      <c r="CF259" t="inlineStr"/>
+      <c r="CG259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -36923,6 +41992,17 @@
       <c r="BT260" t="inlineStr"/>
       <c r="BU260" t="inlineStr"/>
       <c r="BV260" t="inlineStr"/>
+      <c r="BW260" t="inlineStr"/>
+      <c r="BX260" t="inlineStr"/>
+      <c r="BY260" t="inlineStr"/>
+      <c r="BZ260" t="inlineStr"/>
+      <c r="CA260" t="inlineStr"/>
+      <c r="CB260" t="inlineStr"/>
+      <c r="CC260" t="inlineStr"/>
+      <c r="CD260" t="inlineStr"/>
+      <c r="CE260" t="inlineStr"/>
+      <c r="CF260" t="inlineStr"/>
+      <c r="CG260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -37049,6 +42129,17 @@
       <c r="BT261" t="inlineStr"/>
       <c r="BU261" t="inlineStr"/>
       <c r="BV261" t="inlineStr"/>
+      <c r="BW261" t="inlineStr"/>
+      <c r="BX261" t="inlineStr"/>
+      <c r="BY261" t="inlineStr"/>
+      <c r="BZ261" t="inlineStr"/>
+      <c r="CA261" t="inlineStr"/>
+      <c r="CB261" t="inlineStr"/>
+      <c r="CC261" t="inlineStr"/>
+      <c r="CD261" t="inlineStr"/>
+      <c r="CE261" t="inlineStr"/>
+      <c r="CF261" t="inlineStr"/>
+      <c r="CG261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -37175,6 +42266,33 @@
       <c r="BT262" t="inlineStr"/>
       <c r="BU262" t="inlineStr"/>
       <c r="BV262" t="inlineStr"/>
+      <c r="BW262" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX262" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY262" t="inlineStr"/>
+      <c r="BZ262" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA262" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB262" t="inlineStr"/>
+      <c r="CC262" t="inlineStr"/>
+      <c r="CD262" t="inlineStr"/>
+      <c r="CE262" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF262" t="inlineStr"/>
+      <c r="CG262" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -37301,6 +42419,17 @@
       <c r="BT263" t="inlineStr"/>
       <c r="BU263" t="inlineStr"/>
       <c r="BV263" t="inlineStr"/>
+      <c r="BW263" t="inlineStr"/>
+      <c r="BX263" t="inlineStr"/>
+      <c r="BY263" t="inlineStr"/>
+      <c r="BZ263" t="inlineStr"/>
+      <c r="CA263" t="inlineStr"/>
+      <c r="CB263" t="inlineStr"/>
+      <c r="CC263" t="inlineStr"/>
+      <c r="CD263" t="inlineStr"/>
+      <c r="CE263" t="inlineStr"/>
+      <c r="CF263" t="inlineStr"/>
+      <c r="CG263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -37427,6 +42556,33 @@
       <c r="BT264" t="inlineStr"/>
       <c r="BU264" t="inlineStr"/>
       <c r="BV264" t="inlineStr"/>
+      <c r="BW264" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX264" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY264" t="inlineStr"/>
+      <c r="BZ264" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA264" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB264" t="inlineStr"/>
+      <c r="CC264" t="inlineStr"/>
+      <c r="CD264" t="inlineStr"/>
+      <c r="CE264" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF264" t="inlineStr"/>
+      <c r="CG264" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -37553,6 +42709,17 @@
       <c r="BT265" t="inlineStr"/>
       <c r="BU265" t="inlineStr"/>
       <c r="BV265" t="inlineStr"/>
+      <c r="BW265" t="inlineStr"/>
+      <c r="BX265" t="inlineStr"/>
+      <c r="BY265" t="inlineStr"/>
+      <c r="BZ265" t="inlineStr"/>
+      <c r="CA265" t="inlineStr"/>
+      <c r="CB265" t="inlineStr"/>
+      <c r="CC265" t="inlineStr"/>
+      <c r="CD265" t="inlineStr"/>
+      <c r="CE265" t="inlineStr"/>
+      <c r="CF265" t="inlineStr"/>
+      <c r="CG265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -37679,6 +42846,33 @@
       <c r="BT266" t="inlineStr"/>
       <c r="BU266" t="inlineStr"/>
       <c r="BV266" t="inlineStr"/>
+      <c r="BW266" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY266" t="inlineStr"/>
+      <c r="BZ266" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA266" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB266" t="inlineStr"/>
+      <c r="CC266" t="inlineStr"/>
+      <c r="CD266" t="inlineStr"/>
+      <c r="CE266" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF266" t="inlineStr"/>
+      <c r="CG266" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -37805,6 +42999,33 @@
       <c r="BT267" t="inlineStr"/>
       <c r="BU267" t="inlineStr"/>
       <c r="BV267" t="inlineStr"/>
+      <c r="BW267" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY267" t="inlineStr"/>
+      <c r="BZ267" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA267" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB267" t="inlineStr"/>
+      <c r="CC267" t="inlineStr"/>
+      <c r="CD267" t="inlineStr"/>
+      <c r="CE267" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF267" t="inlineStr"/>
+      <c r="CG267" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -37931,6 +43152,33 @@
       <c r="BT268" t="inlineStr"/>
       <c r="BU268" t="inlineStr"/>
       <c r="BV268" t="inlineStr"/>
+      <c r="BW268" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY268" t="inlineStr"/>
+      <c r="BZ268" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA268" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB268" t="inlineStr"/>
+      <c r="CC268" t="inlineStr"/>
+      <c r="CD268" t="inlineStr"/>
+      <c r="CE268" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF268" t="inlineStr"/>
+      <c r="CG268" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -38057,6 +43305,17 @@
       <c r="BT269" t="inlineStr"/>
       <c r="BU269" t="inlineStr"/>
       <c r="BV269" t="inlineStr"/>
+      <c r="BW269" t="inlineStr"/>
+      <c r="BX269" t="inlineStr"/>
+      <c r="BY269" t="inlineStr"/>
+      <c r="BZ269" t="inlineStr"/>
+      <c r="CA269" t="inlineStr"/>
+      <c r="CB269" t="inlineStr"/>
+      <c r="CC269" t="inlineStr"/>
+      <c r="CD269" t="inlineStr"/>
+      <c r="CE269" t="inlineStr"/>
+      <c r="CF269" t="inlineStr"/>
+      <c r="CG269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -38183,6 +43442,17 @@
       <c r="BT270" t="inlineStr"/>
       <c r="BU270" t="inlineStr"/>
       <c r="BV270" t="inlineStr"/>
+      <c r="BW270" t="inlineStr"/>
+      <c r="BX270" t="inlineStr"/>
+      <c r="BY270" t="inlineStr"/>
+      <c r="BZ270" t="inlineStr"/>
+      <c r="CA270" t="inlineStr"/>
+      <c r="CB270" t="inlineStr"/>
+      <c r="CC270" t="inlineStr"/>
+      <c r="CD270" t="inlineStr"/>
+      <c r="CE270" t="inlineStr"/>
+      <c r="CF270" t="inlineStr"/>
+      <c r="CG270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -38309,6 +43579,33 @@
       <c r="BT271" t="inlineStr"/>
       <c r="BU271" t="inlineStr"/>
       <c r="BV271" t="inlineStr"/>
+      <c r="BW271" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY271" t="inlineStr"/>
+      <c r="BZ271" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA271" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB271" t="inlineStr"/>
+      <c r="CC271" t="inlineStr"/>
+      <c r="CD271" t="inlineStr"/>
+      <c r="CE271" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF271" t="inlineStr"/>
+      <c r="CG271" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -38435,6 +43732,17 @@
       <c r="BT272" t="inlineStr"/>
       <c r="BU272" t="inlineStr"/>
       <c r="BV272" t="inlineStr"/>
+      <c r="BW272" t="inlineStr"/>
+      <c r="BX272" t="inlineStr"/>
+      <c r="BY272" t="inlineStr"/>
+      <c r="BZ272" t="inlineStr"/>
+      <c r="CA272" t="inlineStr"/>
+      <c r="CB272" t="inlineStr"/>
+      <c r="CC272" t="inlineStr"/>
+      <c r="CD272" t="inlineStr"/>
+      <c r="CE272" t="inlineStr"/>
+      <c r="CF272" t="inlineStr"/>
+      <c r="CG272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -38561,6 +43869,17 @@
       <c r="BT273" t="inlineStr"/>
       <c r="BU273" t="inlineStr"/>
       <c r="BV273" t="inlineStr"/>
+      <c r="BW273" t="inlineStr"/>
+      <c r="BX273" t="inlineStr"/>
+      <c r="BY273" t="inlineStr"/>
+      <c r="BZ273" t="inlineStr"/>
+      <c r="CA273" t="inlineStr"/>
+      <c r="CB273" t="inlineStr"/>
+      <c r="CC273" t="inlineStr"/>
+      <c r="CD273" t="inlineStr"/>
+      <c r="CE273" t="inlineStr"/>
+      <c r="CF273" t="inlineStr"/>
+      <c r="CG273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -38697,6 +44016,33 @@
       <c r="BT274" t="inlineStr"/>
       <c r="BU274" t="inlineStr"/>
       <c r="BV274" t="inlineStr"/>
+      <c r="BW274" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX274" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY274" t="inlineStr"/>
+      <c r="BZ274" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA274" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB274" t="inlineStr"/>
+      <c r="CC274" t="inlineStr"/>
+      <c r="CD274" t="inlineStr"/>
+      <c r="CE274" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF274" t="inlineStr"/>
+      <c r="CG274" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -38833,6 +44179,33 @@
       <c r="BT275" t="inlineStr"/>
       <c r="BU275" t="inlineStr"/>
       <c r="BV275" t="inlineStr"/>
+      <c r="BW275" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX275" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY275" t="inlineStr"/>
+      <c r="BZ275" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA275" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB275" t="inlineStr"/>
+      <c r="CC275" t="inlineStr"/>
+      <c r="CD275" t="inlineStr"/>
+      <c r="CE275" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF275" t="inlineStr"/>
+      <c r="CG275" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -38969,6 +44342,33 @@
       <c r="BT276" t="inlineStr"/>
       <c r="BU276" t="inlineStr"/>
       <c r="BV276" t="inlineStr"/>
+      <c r="BW276" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX276" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY276" t="inlineStr"/>
+      <c r="BZ276" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA276" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB276" t="inlineStr"/>
+      <c r="CC276" t="inlineStr"/>
+      <c r="CD276" t="inlineStr"/>
+      <c r="CE276" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF276" t="inlineStr"/>
+      <c r="CG276" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -39105,6 +44505,37 @@
       <c r="BT277" t="inlineStr"/>
       <c r="BU277" t="inlineStr"/>
       <c r="BV277" t="inlineStr"/>
+      <c r="BW277" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX277" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY277" t="inlineStr"/>
+      <c r="BZ277" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA277" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB277" t="inlineStr"/>
+      <c r="CC277" t="inlineStr"/>
+      <c r="CD277" t="inlineStr"/>
+      <c r="CE277" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF277" t="inlineStr">
+        <is>
+          <t>中信</t>
+        </is>
+      </c>
+      <c r="CG277" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -39241,6 +44672,17 @@
       <c r="BT278" t="inlineStr"/>
       <c r="BU278" t="inlineStr"/>
       <c r="BV278" t="inlineStr"/>
+      <c r="BW278" t="inlineStr"/>
+      <c r="BX278" t="inlineStr"/>
+      <c r="BY278" t="inlineStr"/>
+      <c r="BZ278" t="inlineStr"/>
+      <c r="CA278" t="inlineStr"/>
+      <c r="CB278" t="inlineStr"/>
+      <c r="CC278" t="inlineStr"/>
+      <c r="CD278" t="inlineStr"/>
+      <c r="CE278" t="inlineStr"/>
+      <c r="CF278" t="inlineStr"/>
+      <c r="CG278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -39377,6 +44819,33 @@
       <c r="BT279" t="inlineStr"/>
       <c r="BU279" t="inlineStr"/>
       <c r="BV279" t="inlineStr"/>
+      <c r="BW279" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX279" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY279" t="inlineStr"/>
+      <c r="BZ279" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA279" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB279" t="inlineStr"/>
+      <c r="CC279" t="inlineStr"/>
+      <c r="CD279" t="inlineStr"/>
+      <c r="CE279" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF279" t="inlineStr"/>
+      <c r="CG279" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -39513,6 +44982,17 @@
       <c r="BT280" t="inlineStr"/>
       <c r="BU280" t="inlineStr"/>
       <c r="BV280" t="inlineStr"/>
+      <c r="BW280" t="inlineStr"/>
+      <c r="BX280" t="inlineStr"/>
+      <c r="BY280" t="inlineStr"/>
+      <c r="BZ280" t="inlineStr"/>
+      <c r="CA280" t="inlineStr"/>
+      <c r="CB280" t="inlineStr"/>
+      <c r="CC280" t="inlineStr"/>
+      <c r="CD280" t="inlineStr"/>
+      <c r="CE280" t="inlineStr"/>
+      <c r="CF280" t="inlineStr"/>
+      <c r="CG280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -39649,6 +45129,33 @@
       <c r="BT281" t="inlineStr"/>
       <c r="BU281" t="inlineStr"/>
       <c r="BV281" t="inlineStr"/>
+      <c r="BW281" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX281" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY281" t="inlineStr"/>
+      <c r="BZ281" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA281" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB281" t="inlineStr"/>
+      <c r="CC281" t="inlineStr"/>
+      <c r="CD281" t="inlineStr"/>
+      <c r="CE281" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF281" t="inlineStr"/>
+      <c r="CG281" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -39775,6 +45282,17 @@
       <c r="BT282" t="inlineStr"/>
       <c r="BU282" t="inlineStr"/>
       <c r="BV282" t="inlineStr"/>
+      <c r="BW282" t="inlineStr"/>
+      <c r="BX282" t="inlineStr"/>
+      <c r="BY282" t="inlineStr"/>
+      <c r="BZ282" t="inlineStr"/>
+      <c r="CA282" t="inlineStr"/>
+      <c r="CB282" t="inlineStr"/>
+      <c r="CC282" t="inlineStr"/>
+      <c r="CD282" t="inlineStr"/>
+      <c r="CE282" t="inlineStr"/>
+      <c r="CF282" t="inlineStr"/>
+      <c r="CG282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -39901,6 +45419,33 @@
       <c r="BT283" t="inlineStr"/>
       <c r="BU283" t="inlineStr"/>
       <c r="BV283" t="inlineStr"/>
+      <c r="BW283" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX283" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY283" t="inlineStr"/>
+      <c r="BZ283" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA283" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB283" t="inlineStr"/>
+      <c r="CC283" t="inlineStr"/>
+      <c r="CD283" t="inlineStr"/>
+      <c r="CE283" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF283" t="inlineStr"/>
+      <c r="CG283" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -40027,6 +45572,33 @@
       <c r="BT284" t="inlineStr"/>
       <c r="BU284" t="inlineStr"/>
       <c r="BV284" t="inlineStr"/>
+      <c r="BW284" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX284" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY284" t="inlineStr"/>
+      <c r="BZ284" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA284" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB284" t="inlineStr"/>
+      <c r="CC284" t="inlineStr"/>
+      <c r="CD284" t="inlineStr"/>
+      <c r="CE284" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF284" t="inlineStr"/>
+      <c r="CG284" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -40153,6 +45725,33 @@
       <c r="BT285" t="inlineStr"/>
       <c r="BU285" t="inlineStr"/>
       <c r="BV285" t="inlineStr"/>
+      <c r="BW285" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX285" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY285" t="inlineStr"/>
+      <c r="BZ285" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA285" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB285" t="inlineStr"/>
+      <c r="CC285" t="inlineStr"/>
+      <c r="CD285" t="inlineStr"/>
+      <c r="CE285" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF285" t="inlineStr"/>
+      <c r="CG285" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -40279,6 +45878,33 @@
       <c r="BT286" t="inlineStr"/>
       <c r="BU286" t="inlineStr"/>
       <c r="BV286" t="inlineStr"/>
+      <c r="BW286" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX286" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY286" t="inlineStr"/>
+      <c r="BZ286" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA286" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB286" t="inlineStr"/>
+      <c r="CC286" t="inlineStr"/>
+      <c r="CD286" t="inlineStr"/>
+      <c r="CE286" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF286" t="inlineStr"/>
+      <c r="CG286" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -40405,6 +46031,17 @@
       <c r="BT287" t="inlineStr"/>
       <c r="BU287" t="inlineStr"/>
       <c r="BV287" t="inlineStr"/>
+      <c r="BW287" t="inlineStr"/>
+      <c r="BX287" t="inlineStr"/>
+      <c r="BY287" t="inlineStr"/>
+      <c r="BZ287" t="inlineStr"/>
+      <c r="CA287" t="inlineStr"/>
+      <c r="CB287" t="inlineStr"/>
+      <c r="CC287" t="inlineStr"/>
+      <c r="CD287" t="inlineStr"/>
+      <c r="CE287" t="inlineStr"/>
+      <c r="CF287" t="inlineStr"/>
+      <c r="CG287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -40531,6 +46168,17 @@
       <c r="BT288" t="inlineStr"/>
       <c r="BU288" t="inlineStr"/>
       <c r="BV288" t="inlineStr"/>
+      <c r="BW288" t="inlineStr"/>
+      <c r="BX288" t="inlineStr"/>
+      <c r="BY288" t="inlineStr"/>
+      <c r="BZ288" t="inlineStr"/>
+      <c r="CA288" t="inlineStr"/>
+      <c r="CB288" t="inlineStr"/>
+      <c r="CC288" t="inlineStr"/>
+      <c r="CD288" t="inlineStr"/>
+      <c r="CE288" t="inlineStr"/>
+      <c r="CF288" t="inlineStr"/>
+      <c r="CG288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -40657,6 +46305,17 @@
       <c r="BT289" t="inlineStr"/>
       <c r="BU289" t="inlineStr"/>
       <c r="BV289" t="inlineStr"/>
+      <c r="BW289" t="inlineStr"/>
+      <c r="BX289" t="inlineStr"/>
+      <c r="BY289" t="inlineStr"/>
+      <c r="BZ289" t="inlineStr"/>
+      <c r="CA289" t="inlineStr"/>
+      <c r="CB289" t="inlineStr"/>
+      <c r="CC289" t="inlineStr"/>
+      <c r="CD289" t="inlineStr"/>
+      <c r="CE289" t="inlineStr"/>
+      <c r="CF289" t="inlineStr"/>
+      <c r="CG289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -40783,6 +46442,17 @@
       <c r="BT290" t="inlineStr"/>
       <c r="BU290" t="inlineStr"/>
       <c r="BV290" t="inlineStr"/>
+      <c r="BW290" t="inlineStr"/>
+      <c r="BX290" t="inlineStr"/>
+      <c r="BY290" t="inlineStr"/>
+      <c r="BZ290" t="inlineStr"/>
+      <c r="CA290" t="inlineStr"/>
+      <c r="CB290" t="inlineStr"/>
+      <c r="CC290" t="inlineStr"/>
+      <c r="CD290" t="inlineStr"/>
+      <c r="CE290" t="inlineStr"/>
+      <c r="CF290" t="inlineStr"/>
+      <c r="CG290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -40909,6 +46579,33 @@
       <c r="BT291" t="inlineStr"/>
       <c r="BU291" t="inlineStr"/>
       <c r="BV291" t="inlineStr"/>
+      <c r="BW291" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX291" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY291" t="inlineStr"/>
+      <c r="BZ291" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA291" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB291" t="inlineStr"/>
+      <c r="CC291" t="inlineStr"/>
+      <c r="CD291" t="inlineStr"/>
+      <c r="CE291" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF291" t="inlineStr"/>
+      <c r="CG291" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -41035,6 +46732,33 @@
       <c r="BT292" t="inlineStr"/>
       <c r="BU292" t="inlineStr"/>
       <c r="BV292" t="inlineStr"/>
+      <c r="BW292" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX292" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY292" t="inlineStr"/>
+      <c r="BZ292" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA292" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB292" t="inlineStr"/>
+      <c r="CC292" t="inlineStr"/>
+      <c r="CD292" t="inlineStr"/>
+      <c r="CE292" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF292" t="inlineStr"/>
+      <c r="CG292" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -41161,6 +46885,17 @@
       <c r="BT293" t="inlineStr"/>
       <c r="BU293" t="inlineStr"/>
       <c r="BV293" t="inlineStr"/>
+      <c r="BW293" t="inlineStr"/>
+      <c r="BX293" t="inlineStr"/>
+      <c r="BY293" t="inlineStr"/>
+      <c r="BZ293" t="inlineStr"/>
+      <c r="CA293" t="inlineStr"/>
+      <c r="CB293" t="inlineStr"/>
+      <c r="CC293" t="inlineStr"/>
+      <c r="CD293" t="inlineStr"/>
+      <c r="CE293" t="inlineStr"/>
+      <c r="CF293" t="inlineStr"/>
+      <c r="CG293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -41287,6 +47022,33 @@
       <c r="BT294" t="inlineStr"/>
       <c r="BU294" t="inlineStr"/>
       <c r="BV294" t="inlineStr"/>
+      <c r="BW294" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX294" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY294" t="inlineStr"/>
+      <c r="BZ294" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA294" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB294" t="inlineStr"/>
+      <c r="CC294" t="inlineStr"/>
+      <c r="CD294" t="inlineStr"/>
+      <c r="CE294" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF294" t="inlineStr"/>
+      <c r="CG294" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -41413,6 +47175,33 @@
       <c r="BT295" t="inlineStr"/>
       <c r="BU295" t="inlineStr"/>
       <c r="BV295" t="inlineStr"/>
+      <c r="BW295" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX295" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY295" t="inlineStr"/>
+      <c r="BZ295" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA295" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB295" t="inlineStr"/>
+      <c r="CC295" t="inlineStr"/>
+      <c r="CD295" t="inlineStr"/>
+      <c r="CE295" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF295" t="inlineStr"/>
+      <c r="CG295" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -41539,6 +47328,33 @@
       <c r="BT296" t="inlineStr"/>
       <c r="BU296" t="inlineStr"/>
       <c r="BV296" t="inlineStr"/>
+      <c r="BW296" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX296" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY296" t="inlineStr"/>
+      <c r="BZ296" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA296" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB296" t="inlineStr"/>
+      <c r="CC296" t="inlineStr"/>
+      <c r="CD296" t="inlineStr"/>
+      <c r="CE296" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF296" t="inlineStr"/>
+      <c r="CG296" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -41665,6 +47481,17 @@
       <c r="BT297" t="inlineStr"/>
       <c r="BU297" t="inlineStr"/>
       <c r="BV297" t="inlineStr"/>
+      <c r="BW297" t="inlineStr"/>
+      <c r="BX297" t="inlineStr"/>
+      <c r="BY297" t="inlineStr"/>
+      <c r="BZ297" t="inlineStr"/>
+      <c r="CA297" t="inlineStr"/>
+      <c r="CB297" t="inlineStr"/>
+      <c r="CC297" t="inlineStr"/>
+      <c r="CD297" t="inlineStr"/>
+      <c r="CE297" t="inlineStr"/>
+      <c r="CF297" t="inlineStr"/>
+      <c r="CG297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -41791,6 +47618,33 @@
       <c r="BT298" t="inlineStr"/>
       <c r="BU298" t="inlineStr"/>
       <c r="BV298" t="inlineStr"/>
+      <c r="BW298" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX298" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY298" t="inlineStr"/>
+      <c r="BZ298" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA298" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB298" t="inlineStr"/>
+      <c r="CC298" t="inlineStr"/>
+      <c r="CD298" t="inlineStr"/>
+      <c r="CE298" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF298" t="inlineStr"/>
+      <c r="CG298" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -41917,6 +47771,33 @@
       <c r="BT299" t="inlineStr"/>
       <c r="BU299" t="inlineStr"/>
       <c r="BV299" t="inlineStr"/>
+      <c r="BW299" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX299" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY299" t="inlineStr"/>
+      <c r="BZ299" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA299" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB299" t="inlineStr"/>
+      <c r="CC299" t="inlineStr"/>
+      <c r="CD299" t="inlineStr"/>
+      <c r="CE299" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF299" t="inlineStr"/>
+      <c r="CG299" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -42043,6 +47924,17 @@
       <c r="BT300" t="inlineStr"/>
       <c r="BU300" t="inlineStr"/>
       <c r="BV300" t="inlineStr"/>
+      <c r="BW300" t="inlineStr"/>
+      <c r="BX300" t="inlineStr"/>
+      <c r="BY300" t="inlineStr"/>
+      <c r="BZ300" t="inlineStr"/>
+      <c r="CA300" t="inlineStr"/>
+      <c r="CB300" t="inlineStr"/>
+      <c r="CC300" t="inlineStr"/>
+      <c r="CD300" t="inlineStr"/>
+      <c r="CE300" t="inlineStr"/>
+      <c r="CF300" t="inlineStr"/>
+      <c r="CG300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -42169,6 +48061,17 @@
       <c r="BT301" t="inlineStr"/>
       <c r="BU301" t="inlineStr"/>
       <c r="BV301" t="inlineStr"/>
+      <c r="BW301" t="inlineStr"/>
+      <c r="BX301" t="inlineStr"/>
+      <c r="BY301" t="inlineStr"/>
+      <c r="BZ301" t="inlineStr"/>
+      <c r="CA301" t="inlineStr"/>
+      <c r="CB301" t="inlineStr"/>
+      <c r="CC301" t="inlineStr"/>
+      <c r="CD301" t="inlineStr"/>
+      <c r="CE301" t="inlineStr"/>
+      <c r="CF301" t="inlineStr"/>
+      <c r="CG301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -42295,6 +48198,33 @@
       <c r="BT302" t="inlineStr"/>
       <c r="BU302" t="inlineStr"/>
       <c r="BV302" t="inlineStr"/>
+      <c r="BW302" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY302" t="inlineStr"/>
+      <c r="BZ302" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA302" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB302" t="inlineStr"/>
+      <c r="CC302" t="inlineStr"/>
+      <c r="CD302" t="inlineStr"/>
+      <c r="CE302" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF302" t="inlineStr"/>
+      <c r="CG302" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -42421,6 +48351,33 @@
       <c r="BT303" t="inlineStr"/>
       <c r="BU303" t="inlineStr"/>
       <c r="BV303" t="inlineStr"/>
+      <c r="BW303" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX303" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY303" t="inlineStr"/>
+      <c r="BZ303" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA303" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB303" t="inlineStr"/>
+      <c r="CC303" t="inlineStr"/>
+      <c r="CD303" t="inlineStr"/>
+      <c r="CE303" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF303" t="inlineStr"/>
+      <c r="CG303" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -42547,6 +48504,33 @@
       <c r="BT304" t="inlineStr"/>
       <c r="BU304" t="inlineStr"/>
       <c r="BV304" t="inlineStr"/>
+      <c r="BW304" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX304" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY304" t="inlineStr"/>
+      <c r="BZ304" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA304" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB304" t="inlineStr"/>
+      <c r="CC304" t="inlineStr"/>
+      <c r="CD304" t="inlineStr"/>
+      <c r="CE304" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF304" t="inlineStr"/>
+      <c r="CG304" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -42673,6 +48657,17 @@
       <c r="BT305" t="inlineStr"/>
       <c r="BU305" t="inlineStr"/>
       <c r="BV305" t="inlineStr"/>
+      <c r="BW305" t="inlineStr"/>
+      <c r="BX305" t="inlineStr"/>
+      <c r="BY305" t="inlineStr"/>
+      <c r="BZ305" t="inlineStr"/>
+      <c r="CA305" t="inlineStr"/>
+      <c r="CB305" t="inlineStr"/>
+      <c r="CC305" t="inlineStr"/>
+      <c r="CD305" t="inlineStr"/>
+      <c r="CE305" t="inlineStr"/>
+      <c r="CF305" t="inlineStr"/>
+      <c r="CG305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -42799,6 +48794,17 @@
       <c r="BT306" t="inlineStr"/>
       <c r="BU306" t="inlineStr"/>
       <c r="BV306" t="inlineStr"/>
+      <c r="BW306" t="inlineStr"/>
+      <c r="BX306" t="inlineStr"/>
+      <c r="BY306" t="inlineStr"/>
+      <c r="BZ306" t="inlineStr"/>
+      <c r="CA306" t="inlineStr"/>
+      <c r="CB306" t="inlineStr"/>
+      <c r="CC306" t="inlineStr"/>
+      <c r="CD306" t="inlineStr"/>
+      <c r="CE306" t="inlineStr"/>
+      <c r="CF306" t="inlineStr"/>
+      <c r="CG306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -42925,6 +48931,17 @@
       <c r="BT307" t="inlineStr"/>
       <c r="BU307" t="inlineStr"/>
       <c r="BV307" t="inlineStr"/>
+      <c r="BW307" t="inlineStr"/>
+      <c r="BX307" t="inlineStr"/>
+      <c r="BY307" t="inlineStr"/>
+      <c r="BZ307" t="inlineStr"/>
+      <c r="CA307" t="inlineStr"/>
+      <c r="CB307" t="inlineStr"/>
+      <c r="CC307" t="inlineStr"/>
+      <c r="CD307" t="inlineStr"/>
+      <c r="CE307" t="inlineStr"/>
+      <c r="CF307" t="inlineStr"/>
+      <c r="CG307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -43051,6 +49068,33 @@
       <c r="BT308" t="inlineStr"/>
       <c r="BU308" t="inlineStr"/>
       <c r="BV308" t="inlineStr"/>
+      <c r="BW308" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX308" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY308" t="inlineStr"/>
+      <c r="BZ308" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA308" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB308" t="inlineStr"/>
+      <c r="CC308" t="inlineStr"/>
+      <c r="CD308" t="inlineStr"/>
+      <c r="CE308" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF308" t="inlineStr"/>
+      <c r="CG308" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -43177,6 +49221,33 @@
       <c r="BT309" t="inlineStr"/>
       <c r="BU309" t="inlineStr"/>
       <c r="BV309" t="inlineStr"/>
+      <c r="BW309" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX309" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY309" t="inlineStr"/>
+      <c r="BZ309" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA309" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB309" t="inlineStr"/>
+      <c r="CC309" t="inlineStr"/>
+      <c r="CD309" t="inlineStr"/>
+      <c r="CE309" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF309" t="inlineStr"/>
+      <c r="CG309" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -43303,6 +49374,33 @@
       <c r="BT310" t="inlineStr"/>
       <c r="BU310" t="inlineStr"/>
       <c r="BV310" t="inlineStr"/>
+      <c r="BW310" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX310" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY310" t="inlineStr"/>
+      <c r="BZ310" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA310" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB310" t="inlineStr"/>
+      <c r="CC310" t="inlineStr"/>
+      <c r="CD310" t="inlineStr"/>
+      <c r="CE310" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF310" t="inlineStr"/>
+      <c r="CG310" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -43429,6 +49527,33 @@
       <c r="BT311" t="inlineStr"/>
       <c r="BU311" t="inlineStr"/>
       <c r="BV311" t="inlineStr"/>
+      <c r="BW311" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
+      <c r="BX311" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY311" t="inlineStr"/>
+      <c r="BZ311" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA311" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB311" t="inlineStr"/>
+      <c r="CC311" t="inlineStr"/>
+      <c r="CD311" t="inlineStr"/>
+      <c r="CE311" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF311" t="inlineStr"/>
+      <c r="CG311" t="inlineStr">
+        <is>
+          <t>今日無可用權證成交金額</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/latest/all_candidates_latest.xlsx
+++ b/output/latest/all_candidates_latest.xlsx
@@ -1068,7 +1068,7 @@
       </c>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>12822110</v>
       </c>
       <c r="BP3" t="n">
         <v>0</v>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>中信</t>
+          <t>富邦</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>3310770</v>
       </c>
       <c r="BP7" t="n">
         <v>0</v>
@@ -1659,10 +1659,14 @@
       <c r="BT7" t="n">
         <v>0</v>
       </c>
-      <c r="BU7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>群益</t>
+        </is>
+      </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1808,7 @@
       </c>
       <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>5411230</v>
       </c>
       <c r="BP8" t="n">
         <v>0</v>
@@ -1815,10 +1819,14 @@
       <c r="BT8" t="n">
         <v>0</v>
       </c>
-      <c r="BU8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2108,7 @@
       </c>
       <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>5112570</v>
       </c>
       <c r="BP10" t="n">
         <v>0</v>
@@ -2111,10 +2119,14 @@
       <c r="BT10" t="n">
         <v>0</v>
       </c>
-      <c r="BU10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2408,7 @@
       </c>
       <c r="BN12" t="inlineStr"/>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>12839340</v>
       </c>
       <c r="BP12" t="n">
         <v>0</v>
@@ -2407,10 +2419,14 @@
       <c r="BT12" t="n">
         <v>0</v>
       </c>
-      <c r="BU12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2708,7 @@
       </c>
       <c r="BN14" t="inlineStr"/>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>4399570</v>
       </c>
       <c r="BP14" t="n">
         <v>0</v>
@@ -2703,10 +2719,14 @@
       <c r="BT14" t="n">
         <v>0</v>
       </c>
-      <c r="BU14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -2988,21 +3008,27 @@
       </c>
       <c r="BN16" t="inlineStr"/>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>27533660</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="inlineStr"/>
+        <v>2160</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>12747.06</v>
+      </c>
       <c r="BR16" t="inlineStr"/>
       <c r="BS16" t="inlineStr"/>
       <c r="BT16" t="n">
         <v>0</v>
       </c>
-      <c r="BU16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3590,7 @@
       </c>
       <c r="BN20" t="inlineStr"/>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>12195890</v>
       </c>
       <c r="BP20" t="n">
         <v>0</v>
@@ -3575,10 +3601,14 @@
       <c r="BT20" t="n">
         <v>0</v>
       </c>
-      <c r="BU20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4310,7 @@
       </c>
       <c r="BN25" t="inlineStr"/>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>7815950</v>
       </c>
       <c r="BP25" t="n">
         <v>0</v>
@@ -4291,10 +4321,14 @@
       <c r="BT25" t="n">
         <v>0</v>
       </c>
-      <c r="BU25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>富邦</t>
+        </is>
+      </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -4436,21 +4470,27 @@
       </c>
       <c r="BN26" t="inlineStr"/>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>8294530</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ26" t="inlineStr"/>
+        <v>2500</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>3317.81</v>
+      </c>
       <c r="BR26" t="inlineStr"/>
       <c r="BS26" t="inlineStr"/>
       <c r="BT26" t="n">
         <v>0</v>
       </c>
-      <c r="BU26" t="inlineStr"/>
+      <c r="BU26" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4912,7 @@
       </c>
       <c r="BN29" t="inlineStr"/>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>24533050</v>
       </c>
       <c r="BP29" t="n">
         <v>0</v>
@@ -4883,10 +4923,14 @@
       <c r="BT29" t="n">
         <v>0</v>
       </c>
-      <c r="BU29" t="inlineStr"/>
+      <c r="BU29" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5072,7 @@
       </c>
       <c r="BN30" t="inlineStr"/>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>7317650</v>
       </c>
       <c r="BP30" t="n">
         <v>0</v>
@@ -5039,10 +5083,14 @@
       <c r="BT30" t="n">
         <v>0</v>
       </c>
-      <c r="BU30" t="inlineStr"/>
+      <c r="BU30" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5784,7 @@
       </c>
       <c r="BN35" t="inlineStr"/>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>3928020</v>
       </c>
       <c r="BP35" t="n">
         <v>0</v>
@@ -5747,10 +5795,14 @@
       <c r="BT35" t="n">
         <v>0</v>
       </c>
-      <c r="BU35" t="inlineStr"/>
+      <c r="BU35" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV35" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -5890,21 +5942,27 @@
       </c>
       <c r="BN36" t="inlineStr"/>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>111096700</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ36" t="inlineStr"/>
+        <v>2356440</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>47.15</v>
+      </c>
       <c r="BR36" t="inlineStr"/>
       <c r="BS36" t="inlineStr"/>
       <c r="BT36" t="n">
         <v>0</v>
       </c>
-      <c r="BU36" t="inlineStr"/>
+      <c r="BU36" t="inlineStr">
+        <is>
+          <t>台新</t>
+        </is>
+      </c>
       <c r="BV36" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6102,7 @@
       </c>
       <c r="BN37" t="inlineStr"/>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>10995170</v>
       </c>
       <c r="BP37" t="n">
         <v>0</v>
@@ -6055,10 +6113,14 @@
       <c r="BT37" t="n">
         <v>0</v>
       </c>
-      <c r="BU37" t="inlineStr"/>
+      <c r="BU37" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV37" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6260,7 @@
       </c>
       <c r="BN38" t="inlineStr"/>
       <c r="BO38" t="n">
-        <v>0</v>
+        <v>4346590</v>
       </c>
       <c r="BP38" t="n">
         <v>0</v>
@@ -6209,10 +6271,14 @@
       <c r="BT38" t="n">
         <v>0</v>
       </c>
-      <c r="BU38" t="inlineStr"/>
+      <c r="BU38" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="BV38" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6560,7 @@
       </c>
       <c r="BN40" t="inlineStr"/>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>21086550</v>
       </c>
       <c r="BP40" t="n">
         <v>0</v>
@@ -6505,10 +6571,14 @@
       <c r="BT40" t="n">
         <v>0</v>
       </c>
-      <c r="BU40" t="inlineStr"/>
+      <c r="BU40" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV40" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -6650,21 +6720,27 @@
       </c>
       <c r="BN41" t="inlineStr"/>
       <c r="BO41" t="n">
-        <v>0</v>
+        <v>23015150</v>
       </c>
       <c r="BP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ41" t="inlineStr"/>
+        <v>17920</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>1284.33</v>
+      </c>
       <c r="BR41" t="inlineStr"/>
       <c r="BS41" t="inlineStr"/>
       <c r="BT41" t="n">
         <v>0</v>
       </c>
-      <c r="BU41" t="inlineStr"/>
+      <c r="BU41" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6882,7 @@
       </c>
       <c r="BN42" t="inlineStr"/>
       <c r="BO42" t="n">
-        <v>0</v>
+        <v>22794310</v>
       </c>
       <c r="BP42" t="n">
         <v>0</v>
@@ -6817,10 +6893,14 @@
       <c r="BT42" t="n">
         <v>0</v>
       </c>
-      <c r="BU42" t="inlineStr"/>
+      <c r="BU42" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV42" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -7102,21 +7182,27 @@
       </c>
       <c r="BN44" t="inlineStr"/>
       <c r="BO44" t="n">
-        <v>0</v>
+        <v>14647410</v>
       </c>
       <c r="BP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ44" t="inlineStr"/>
+        <v>112610</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>130.07</v>
+      </c>
       <c r="BR44" t="inlineStr"/>
       <c r="BS44" t="inlineStr"/>
       <c r="BT44" t="n">
         <v>0</v>
       </c>
-      <c r="BU44" t="inlineStr"/>
+      <c r="BU44" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV44" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -7398,21 +7484,27 @@
       </c>
       <c r="BN46" t="inlineStr"/>
       <c r="BO46" t="n">
-        <v>0</v>
+        <v>21235500</v>
       </c>
       <c r="BP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ46" t="inlineStr"/>
+        <v>97700</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>217.35</v>
+      </c>
       <c r="BR46" t="inlineStr"/>
       <c r="BS46" t="inlineStr"/>
       <c r="BT46" t="n">
         <v>0</v>
       </c>
-      <c r="BU46" t="inlineStr"/>
+      <c r="BU46" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV46" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7646,7 @@
       </c>
       <c r="BN47" t="inlineStr"/>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>412690</v>
       </c>
       <c r="BP47" t="n">
         <v>0</v>
@@ -7565,10 +7657,14 @@
       <c r="BT47" t="n">
         <v>0</v>
       </c>
-      <c r="BU47" t="inlineStr"/>
+      <c r="BU47" t="inlineStr">
+        <is>
+          <t>國泰</t>
+        </is>
+      </c>
       <c r="BV47" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7946,7 @@
       </c>
       <c r="BN49" t="inlineStr"/>
       <c r="BO49" t="n">
-        <v>0</v>
+        <v>20297100</v>
       </c>
       <c r="BP49" t="n">
         <v>0</v>
@@ -7861,10 +7957,14 @@
       <c r="BT49" t="n">
         <v>0</v>
       </c>
-      <c r="BU49" t="inlineStr"/>
+      <c r="BU49" t="inlineStr">
+        <is>
+          <t>群益</t>
+        </is>
+      </c>
       <c r="BV49" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -8146,21 +8246,27 @@
       </c>
       <c r="BN51" t="inlineStr"/>
       <c r="BO51" t="n">
-        <v>0</v>
+        <v>22554130</v>
       </c>
       <c r="BP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ51" t="inlineStr"/>
+        <v>134440</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>167.76</v>
+      </c>
       <c r="BR51" t="inlineStr"/>
       <c r="BS51" t="inlineStr"/>
       <c r="BT51" t="n">
         <v>0</v>
       </c>
-      <c r="BU51" t="inlineStr"/>
+      <c r="BU51" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV51" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8408,7 @@
       </c>
       <c r="BN52" t="inlineStr"/>
       <c r="BO52" t="n">
-        <v>0</v>
+        <v>742620</v>
       </c>
       <c r="BP52" t="n">
         <v>0</v>
@@ -8313,10 +8419,14 @@
       <c r="BT52" t="n">
         <v>0</v>
       </c>
-      <c r="BU52" t="inlineStr"/>
+      <c r="BU52" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV52" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9268,7 @@
       </c>
       <c r="BN58" t="inlineStr"/>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>1074970</v>
       </c>
       <c r="BP58" t="n">
         <v>0</v>
@@ -9169,10 +9279,14 @@
       <c r="BT58" t="n">
         <v>0</v>
       </c>
-      <c r="BU58" t="inlineStr"/>
+      <c r="BU58" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV58" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10826,7 @@
       </c>
       <c r="BN69" t="inlineStr"/>
       <c r="BO69" t="n">
-        <v>0</v>
+        <v>4432990</v>
       </c>
       <c r="BP69" t="n">
         <v>0</v>
@@ -10723,10 +10837,14 @@
       <c r="BT69" t="n">
         <v>0</v>
       </c>
-      <c r="BU69" t="inlineStr"/>
+      <c r="BU69" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV69" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12448,7 @@
       </c>
       <c r="BN80" t="inlineStr"/>
       <c r="BO80" t="n">
-        <v>0</v>
+        <v>8504380</v>
       </c>
       <c r="BP80" t="n">
         <v>0</v>
@@ -12341,10 +12459,14 @@
       <c r="BT80" t="n">
         <v>0</v>
       </c>
-      <c r="BU80" t="inlineStr"/>
+      <c r="BU80" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV80" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -12568,7 +12690,7 @@
       </c>
       <c r="BN81" t="inlineStr"/>
       <c r="BO81" t="n">
-        <v>0</v>
+        <v>822090</v>
       </c>
       <c r="BP81" t="n">
         <v>0</v>
@@ -12579,10 +12701,14 @@
       <c r="BT81" t="n">
         <v>0</v>
       </c>
-      <c r="BU81" t="inlineStr"/>
+      <c r="BU81" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV81" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -12806,7 +12932,7 @@
       </c>
       <c r="BN82" t="inlineStr"/>
       <c r="BO82" t="n">
-        <v>0</v>
+        <v>4361860</v>
       </c>
       <c r="BP82" t="n">
         <v>0</v>
@@ -12817,10 +12943,14 @@
       <c r="BT82" t="n">
         <v>0</v>
       </c>
-      <c r="BU82" t="inlineStr"/>
+      <c r="BU82" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV82" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -13044,21 +13174,27 @@
       </c>
       <c r="BN83" t="inlineStr"/>
       <c r="BO83" t="n">
-        <v>0</v>
+        <v>13728580</v>
       </c>
       <c r="BP83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ83" t="inlineStr"/>
+        <v>456310</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>30.09</v>
+      </c>
       <c r="BR83" t="inlineStr"/>
       <c r="BS83" t="inlineStr"/>
       <c r="BT83" t="n">
         <v>0</v>
       </c>
-      <c r="BU83" t="inlineStr"/>
+      <c r="BU83" t="inlineStr">
+        <is>
+          <t>群益</t>
+        </is>
+      </c>
       <c r="BV83" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13418,7 @@
       </c>
       <c r="BN84" t="inlineStr"/>
       <c r="BO84" t="n">
-        <v>0</v>
+        <v>20066610</v>
       </c>
       <c r="BP84" t="n">
         <v>0</v>
@@ -13293,10 +13429,14 @@
       <c r="BT84" t="n">
         <v>0</v>
       </c>
-      <c r="BU84" t="inlineStr"/>
+      <c r="BU84" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV84" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -13520,21 +13660,27 @@
       </c>
       <c r="BN85" t="inlineStr"/>
       <c r="BO85" t="n">
-        <v>0</v>
+        <v>6760120</v>
       </c>
       <c r="BP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ85" t="inlineStr"/>
+        <v>1050</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>6438.21</v>
+      </c>
       <c r="BR85" t="inlineStr"/>
       <c r="BS85" t="inlineStr"/>
       <c r="BT85" t="n">
         <v>0</v>
       </c>
-      <c r="BU85" t="inlineStr"/>
+      <c r="BU85" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV85" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14348,7 @@
       </c>
       <c r="BN88" t="inlineStr"/>
       <c r="BO88" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="BP88" t="n">
         <v>0</v>
@@ -14213,10 +14359,14 @@
       <c r="BT88" t="n">
         <v>0</v>
       </c>
-      <c r="BU88" t="inlineStr"/>
+      <c r="BU88" t="inlineStr">
+        <is>
+          <t>兆豐</t>
+        </is>
+      </c>
       <c r="BV88" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14590,7 @@
       </c>
       <c r="BN89" t="inlineStr"/>
       <c r="BO89" t="n">
-        <v>0</v>
+        <v>28530</v>
       </c>
       <c r="BP89" t="n">
         <v>0</v>
@@ -14451,10 +14601,14 @@
       <c r="BT89" t="n">
         <v>0</v>
       </c>
-      <c r="BU89" t="inlineStr"/>
+      <c r="BU89" t="inlineStr">
+        <is>
+          <t>國泰</t>
+        </is>
+      </c>
       <c r="BV89" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15276,7 @@
       </c>
       <c r="BN92" t="inlineStr"/>
       <c r="BO92" t="n">
-        <v>0</v>
+        <v>8047800</v>
       </c>
       <c r="BP92" t="n">
         <v>0</v>
@@ -15133,10 +15287,14 @@
       <c r="BT92" t="n">
         <v>0</v>
       </c>
-      <c r="BU92" t="inlineStr"/>
+      <c r="BU92" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV92" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -15364,21 +15522,27 @@
       </c>
       <c r="BN93" t="inlineStr"/>
       <c r="BO93" t="n">
-        <v>0</v>
+        <v>9053860</v>
       </c>
       <c r="BP93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ93" t="inlineStr"/>
+        <v>189820</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>47.7</v>
+      </c>
       <c r="BR93" t="inlineStr"/>
       <c r="BS93" t="inlineStr"/>
       <c r="BT93" t="n">
         <v>0</v>
       </c>
-      <c r="BU93" t="inlineStr"/>
+      <c r="BU93" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV93" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -15606,21 +15770,27 @@
       </c>
       <c r="BN94" t="inlineStr"/>
       <c r="BO94" t="n">
-        <v>0</v>
+        <v>67969770</v>
       </c>
       <c r="BP94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ94" t="inlineStr"/>
+        <v>84510</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>804.28</v>
+      </c>
       <c r="BR94" t="inlineStr"/>
       <c r="BS94" t="inlineStr"/>
       <c r="BT94" t="n">
         <v>0</v>
       </c>
-      <c r="BU94" t="inlineStr"/>
+      <c r="BU94" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV94" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -16070,7 +16240,7 @@
       </c>
       <c r="BN96" t="inlineStr"/>
       <c r="BO96" t="n">
-        <v>0</v>
+        <v>102470</v>
       </c>
       <c r="BP96" t="n">
         <v>0</v>
@@ -16081,10 +16251,14 @@
       <c r="BT96" t="n">
         <v>0</v>
       </c>
-      <c r="BU96" t="inlineStr"/>
+      <c r="BU96" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV96" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -16312,7 +16486,7 @@
       </c>
       <c r="BN97" t="inlineStr"/>
       <c r="BO97" t="n">
-        <v>0</v>
+        <v>5953770</v>
       </c>
       <c r="BP97" t="n">
         <v>0</v>
@@ -16323,10 +16497,14 @@
       <c r="BT97" t="n">
         <v>0</v>
       </c>
-      <c r="BU97" t="inlineStr"/>
+      <c r="BU97" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV97" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -16780,21 +16958,27 @@
       </c>
       <c r="BN99" t="inlineStr"/>
       <c r="BO99" t="n">
-        <v>0</v>
+        <v>23537930</v>
       </c>
       <c r="BP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ99" t="inlineStr"/>
+        <v>22850</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>1030.11</v>
+      </c>
       <c r="BR99" t="inlineStr"/>
       <c r="BS99" t="inlineStr"/>
       <c r="BT99" t="n">
         <v>0</v>
       </c>
-      <c r="BU99" t="inlineStr"/>
+      <c r="BU99" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV99" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -17022,21 +17206,27 @@
       </c>
       <c r="BN100" t="inlineStr"/>
       <c r="BO100" t="n">
-        <v>0</v>
+        <v>21479790</v>
       </c>
       <c r="BP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ100" t="inlineStr"/>
+        <v>6680</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>3215.54</v>
+      </c>
       <c r="BR100" t="inlineStr"/>
       <c r="BS100" t="inlineStr"/>
       <c r="BT100" t="n">
         <v>0</v>
       </c>
-      <c r="BU100" t="inlineStr"/>
+      <c r="BU100" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV100" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -17400,21 +17590,27 @@
       </c>
       <c r="BN102" t="inlineStr"/>
       <c r="BO102" t="n">
-        <v>0</v>
+        <v>6259170</v>
       </c>
       <c r="BP102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ102" t="inlineStr"/>
+        <v>145780</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>42.94</v>
+      </c>
       <c r="BR102" t="inlineStr"/>
       <c r="BS102" t="inlineStr"/>
       <c r="BT102" t="n">
         <v>0</v>
       </c>
-      <c r="BU102" t="inlineStr"/>
+      <c r="BU102" t="inlineStr">
+        <is>
+          <t>兆豐</t>
+        </is>
+      </c>
       <c r="BV102" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -17688,21 +17884,27 @@
       </c>
       <c r="BN104" t="inlineStr"/>
       <c r="BO104" t="n">
-        <v>0</v>
+        <v>9053860</v>
       </c>
       <c r="BP104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ104" t="inlineStr"/>
+        <v>189820</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>47.7</v>
+      </c>
       <c r="BR104" t="inlineStr"/>
       <c r="BS104" t="inlineStr"/>
       <c r="BT104" t="n">
         <v>0</v>
       </c>
-      <c r="BU104" t="inlineStr"/>
+      <c r="BU104" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV104" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -18520,21 +18722,27 @@
       </c>
       <c r="BN110" t="inlineStr"/>
       <c r="BO110" t="n">
-        <v>0</v>
+        <v>21479790</v>
       </c>
       <c r="BP110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ110" t="inlineStr"/>
+        <v>6680</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>3215.54</v>
+      </c>
       <c r="BR110" t="inlineStr"/>
       <c r="BS110" t="inlineStr"/>
       <c r="BT110" t="n">
         <v>0</v>
       </c>
-      <c r="BU110" t="inlineStr"/>
+      <c r="BU110" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV110" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -18944,21 +19152,27 @@
       </c>
       <c r="BN113" t="inlineStr"/>
       <c r="BO113" t="n">
-        <v>0</v>
+        <v>30260740</v>
       </c>
       <c r="BP113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ113" t="inlineStr"/>
+        <v>5725560</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>5.29</v>
+      </c>
       <c r="BR113" t="inlineStr"/>
       <c r="BS113" t="inlineStr"/>
       <c r="BT113" t="n">
         <v>0</v>
       </c>
-      <c r="BU113" t="inlineStr"/>
+      <c r="BU113" t="inlineStr">
+        <is>
+          <t>群益</t>
+        </is>
+      </c>
       <c r="BV113" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -19096,21 +19310,27 @@
       </c>
       <c r="BN114" t="inlineStr"/>
       <c r="BO114" t="n">
-        <v>0</v>
+        <v>9478170</v>
       </c>
       <c r="BP114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ114" t="inlineStr"/>
+        <v>20140</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>470.61</v>
+      </c>
       <c r="BR114" t="inlineStr"/>
       <c r="BS114" t="inlineStr"/>
       <c r="BT114" t="n">
         <v>0</v>
       </c>
-      <c r="BU114" t="inlineStr"/>
+      <c r="BU114" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="BV114" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -19520,21 +19740,27 @@
       </c>
       <c r="BN117" t="inlineStr"/>
       <c r="BO117" t="n">
-        <v>0</v>
+        <v>7852990</v>
       </c>
       <c r="BP117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ117" t="inlineStr"/>
+        <v>130</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>60407.62</v>
+      </c>
       <c r="BR117" t="inlineStr"/>
       <c r="BS117" t="inlineStr"/>
       <c r="BT117" t="n">
         <v>0</v>
       </c>
-      <c r="BU117" t="inlineStr"/>
+      <c r="BU117" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV117" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -19672,21 +19898,27 @@
       </c>
       <c r="BN118" t="inlineStr"/>
       <c r="BO118" t="n">
-        <v>0</v>
+        <v>2591890</v>
       </c>
       <c r="BP118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ118" t="inlineStr"/>
+        <v>26900</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>96.34999999999999</v>
+      </c>
       <c r="BR118" t="inlineStr"/>
       <c r="BS118" t="inlineStr"/>
       <c r="BT118" t="n">
         <v>0</v>
       </c>
-      <c r="BU118" t="inlineStr"/>
+      <c r="BU118" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV118" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -19960,21 +20192,27 @@
       </c>
       <c r="BN120" t="inlineStr"/>
       <c r="BO120" t="n">
-        <v>0</v>
+        <v>3068470</v>
       </c>
       <c r="BP120" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ120" t="inlineStr"/>
+        <v>1950</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1573.57</v>
+      </c>
       <c r="BR120" t="inlineStr"/>
       <c r="BS120" t="inlineStr"/>
       <c r="BT120" t="n">
         <v>0</v>
       </c>
-      <c r="BU120" t="inlineStr"/>
+      <c r="BU120" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV120" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -20112,21 +20350,27 @@
       </c>
       <c r="BN121" t="inlineStr"/>
       <c r="BO121" t="n">
-        <v>0</v>
+        <v>25964060</v>
       </c>
       <c r="BP121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ121" t="inlineStr"/>
+        <v>222610</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>116.63</v>
+      </c>
       <c r="BR121" t="inlineStr"/>
       <c r="BS121" t="inlineStr"/>
       <c r="BT121" t="n">
         <v>0</v>
       </c>
-      <c r="BU121" t="inlineStr"/>
+      <c r="BU121" t="inlineStr">
+        <is>
+          <t>元富</t>
+        </is>
+      </c>
       <c r="BV121" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -20264,21 +20508,27 @@
       </c>
       <c r="BN122" t="inlineStr"/>
       <c r="BO122" t="n">
-        <v>0</v>
+        <v>1963740</v>
       </c>
       <c r="BP122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ122" t="inlineStr"/>
+        <v>5200</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>377.64</v>
+      </c>
       <c r="BR122" t="inlineStr"/>
       <c r="BS122" t="inlineStr"/>
       <c r="BT122" t="n">
         <v>0</v>
       </c>
-      <c r="BU122" t="inlineStr"/>
+      <c r="BU122" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV122" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -20416,21 +20666,27 @@
       </c>
       <c r="BN123" t="inlineStr"/>
       <c r="BO123" t="n">
-        <v>0</v>
+        <v>24351970</v>
       </c>
       <c r="BP123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ123" t="inlineStr"/>
+        <v>798830</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>30.48</v>
+      </c>
       <c r="BR123" t="inlineStr"/>
       <c r="BS123" t="inlineStr"/>
       <c r="BT123" t="n">
         <v>0</v>
       </c>
-      <c r="BU123" t="inlineStr"/>
+      <c r="BU123" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV123" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -20581,7 +20837,7 @@
       </c>
       <c r="BU124" t="inlineStr">
         <is>
-          <t>華南</t>
+          <t>中信</t>
         </is>
       </c>
       <c r="BV124" t="inlineStr">
@@ -20724,7 +20980,7 @@
       </c>
       <c r="BN125" t="inlineStr"/>
       <c r="BO125" t="n">
-        <v>0</v>
+        <v>1313240</v>
       </c>
       <c r="BP125" t="n">
         <v>0</v>
@@ -20735,10 +20991,14 @@
       <c r="BT125" t="n">
         <v>0</v>
       </c>
-      <c r="BU125" t="inlineStr"/>
+      <c r="BU125" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV125" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -20876,7 +21136,7 @@
       </c>
       <c r="BN126" t="inlineStr"/>
       <c r="BO126" t="n">
-        <v>0</v>
+        <v>3572240</v>
       </c>
       <c r="BP126" t="n">
         <v>0</v>
@@ -20887,10 +21147,14 @@
       <c r="BT126" t="n">
         <v>0</v>
       </c>
-      <c r="BU126" t="inlineStr"/>
+      <c r="BU126" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
       <c r="BV126" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21292,7 @@
       </c>
       <c r="BN127" t="inlineStr"/>
       <c r="BO127" t="n">
-        <v>0</v>
+        <v>852570</v>
       </c>
       <c r="BP127" t="n">
         <v>0</v>
@@ -21039,10 +21303,14 @@
       <c r="BT127" t="n">
         <v>0</v>
       </c>
-      <c r="BU127" t="inlineStr"/>
+      <c r="BU127" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV127" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -21180,21 +21448,27 @@
       </c>
       <c r="BN128" t="inlineStr"/>
       <c r="BO128" t="n">
-        <v>0</v>
+        <v>37425840</v>
       </c>
       <c r="BP128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ128" t="inlineStr"/>
+        <v>1356510</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>27.59</v>
+      </c>
       <c r="BR128" t="inlineStr"/>
       <c r="BS128" t="inlineStr"/>
       <c r="BT128" t="n">
         <v>0</v>
       </c>
-      <c r="BU128" t="inlineStr"/>
+      <c r="BU128" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV128" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -21332,7 +21606,7 @@
       </c>
       <c r="BN129" t="inlineStr"/>
       <c r="BO129" t="n">
-        <v>0</v>
+        <v>1619890</v>
       </c>
       <c r="BP129" t="n">
         <v>0</v>
@@ -21343,10 +21617,14 @@
       <c r="BT129" t="n">
         <v>0</v>
       </c>
-      <c r="BU129" t="inlineStr"/>
+      <c r="BU129" t="inlineStr">
+        <is>
+          <t>台新</t>
+        </is>
+      </c>
       <c r="BV129" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -22502,21 +22780,27 @@
       </c>
       <c r="BN138" t="inlineStr"/>
       <c r="BO138" t="n">
-        <v>0</v>
+        <v>5329420</v>
       </c>
       <c r="BP138" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ138" t="inlineStr"/>
+        <v>1175500</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>4.53</v>
+      </c>
       <c r="BR138" t="inlineStr"/>
       <c r="BS138" t="inlineStr"/>
       <c r="BT138" t="n">
         <v>0</v>
       </c>
-      <c r="BU138" t="inlineStr"/>
+      <c r="BU138" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="BV138" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -22770,21 +23054,27 @@
       </c>
       <c r="BN140" t="inlineStr"/>
       <c r="BO140" t="n">
-        <v>0</v>
+        <v>17038820</v>
       </c>
       <c r="BP140" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ140" t="inlineStr"/>
+        <v>208540</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>81.70999999999999</v>
+      </c>
       <c r="BR140" t="inlineStr"/>
       <c r="BS140" t="inlineStr"/>
       <c r="BT140" t="n">
         <v>0</v>
       </c>
-      <c r="BU140" t="inlineStr"/>
+      <c r="BU140" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV140" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -22912,21 +23202,27 @@
       </c>
       <c r="BN141" t="inlineStr"/>
       <c r="BO141" t="n">
-        <v>0</v>
+        <v>71088200</v>
       </c>
       <c r="BP141" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ141" t="inlineStr"/>
+        <v>3300080</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>21.54</v>
+      </c>
       <c r="BR141" t="inlineStr"/>
       <c r="BS141" t="inlineStr"/>
       <c r="BT141" t="n">
         <v>0</v>
       </c>
-      <c r="BU141" t="inlineStr"/>
+      <c r="BU141" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV141" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23476,7 @@
       </c>
       <c r="BN143" t="inlineStr"/>
       <c r="BO143" t="n">
-        <v>0</v>
+        <v>431870</v>
       </c>
       <c r="BP143" t="n">
         <v>0</v>
@@ -23191,10 +23487,14 @@
       <c r="BT143" t="n">
         <v>0</v>
       </c>
-      <c r="BU143" t="inlineStr"/>
+      <c r="BU143" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
       <c r="BV143" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -23448,7 +23748,7 @@
       </c>
       <c r="BN145" t="inlineStr"/>
       <c r="BO145" t="n">
-        <v>0</v>
+        <v>2746590</v>
       </c>
       <c r="BP145" t="n">
         <v>0</v>
@@ -23459,10 +23759,14 @@
       <c r="BT145" t="n">
         <v>0</v>
       </c>
-      <c r="BU145" t="inlineStr"/>
+      <c r="BU145" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV145" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -23590,7 +23894,7 @@
       </c>
       <c r="BN146" t="inlineStr"/>
       <c r="BO146" t="n">
-        <v>0</v>
+        <v>1490940</v>
       </c>
       <c r="BP146" t="n">
         <v>0</v>
@@ -23601,10 +23905,14 @@
       <c r="BT146" t="n">
         <v>0</v>
       </c>
-      <c r="BU146" t="inlineStr"/>
+      <c r="BU146" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV146" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -24614,21 +24922,27 @@
       </c>
       <c r="BN154" t="inlineStr"/>
       <c r="BO154" t="n">
-        <v>0</v>
+        <v>86240710</v>
       </c>
       <c r="BP154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ154" t="inlineStr"/>
+        <v>1975260</v>
+      </c>
+      <c r="BQ154" t="n">
+        <v>43.66</v>
+      </c>
       <c r="BR154" t="inlineStr"/>
       <c r="BS154" t="inlineStr"/>
       <c r="BT154" t="n">
         <v>0</v>
       </c>
-      <c r="BU154" t="inlineStr"/>
+      <c r="BU154" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV154" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -24756,7 +25070,7 @@
       </c>
       <c r="BN155" t="inlineStr"/>
       <c r="BO155" t="n">
-        <v>0</v>
+        <v>2429280</v>
       </c>
       <c r="BP155" t="n">
         <v>0</v>
@@ -24774,7 +25088,7 @@
       </c>
       <c r="BV155" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -24902,21 +25216,27 @@
       </c>
       <c r="BN156" t="inlineStr"/>
       <c r="BO156" t="n">
-        <v>0</v>
+        <v>23537930</v>
       </c>
       <c r="BP156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ156" t="inlineStr"/>
+        <v>22850</v>
+      </c>
+      <c r="BQ156" t="n">
+        <v>1030.11</v>
+      </c>
       <c r="BR156" t="inlineStr"/>
       <c r="BS156" t="inlineStr"/>
       <c r="BT156" t="n">
         <v>0</v>
       </c>
-      <c r="BU156" t="inlineStr"/>
+      <c r="BU156" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV156" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -25044,7 +25364,7 @@
       </c>
       <c r="BN157" t="inlineStr"/>
       <c r="BO157" t="n">
-        <v>0</v>
+        <v>167640</v>
       </c>
       <c r="BP157" t="n">
         <v>0</v>
@@ -25057,12 +25377,12 @@
       </c>
       <c r="BU157" t="inlineStr">
         <is>
-          <t>永豐</t>
+          <t>富邦</t>
         </is>
       </c>
       <c r="BV157" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -25190,7 +25510,7 @@
       </c>
       <c r="BN158" t="inlineStr"/>
       <c r="BO158" t="n">
-        <v>0</v>
+        <v>5976880</v>
       </c>
       <c r="BP158" t="n">
         <v>0</v>
@@ -25208,7 +25528,7 @@
       </c>
       <c r="BV158" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -25336,12 +25656,14 @@
       </c>
       <c r="BN159" t="inlineStr"/>
       <c r="BO159" t="n">
-        <v>0</v>
+        <v>3043900</v>
       </c>
       <c r="BP159" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ159" t="inlineStr"/>
+        <v>500</v>
+      </c>
+      <c r="BQ159" t="n">
+        <v>6087.8</v>
+      </c>
       <c r="BR159" t="inlineStr"/>
       <c r="BS159" t="inlineStr"/>
       <c r="BT159" t="n">
@@ -25349,12 +25671,12 @@
       </c>
       <c r="BU159" t="inlineStr">
         <is>
-          <t>國泰</t>
+          <t>富邦</t>
         </is>
       </c>
       <c r="BV159" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -25482,7 +25804,7 @@
       </c>
       <c r="BN160" t="inlineStr"/>
       <c r="BO160" t="n">
-        <v>0</v>
+        <v>2182560</v>
       </c>
       <c r="BP160" t="n">
         <v>0</v>
@@ -25500,7 +25822,7 @@
       </c>
       <c r="BV160" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25950,7 @@
       </c>
       <c r="BN161" t="inlineStr"/>
       <c r="BO161" t="n">
-        <v>0</v>
+        <v>20066610</v>
       </c>
       <c r="BP161" t="n">
         <v>0</v>
@@ -25639,10 +25961,14 @@
       <c r="BT161" t="n">
         <v>0</v>
       </c>
-      <c r="BU161" t="inlineStr"/>
+      <c r="BU161" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV161" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -25770,21 +26096,27 @@
       </c>
       <c r="BN162" t="inlineStr"/>
       <c r="BO162" t="n">
-        <v>0</v>
+        <v>13728580</v>
       </c>
       <c r="BP162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ162" t="inlineStr"/>
+        <v>456310</v>
+      </c>
+      <c r="BQ162" t="n">
+        <v>30.09</v>
+      </c>
       <c r="BR162" t="inlineStr"/>
       <c r="BS162" t="inlineStr"/>
       <c r="BT162" t="n">
         <v>0</v>
       </c>
-      <c r="BU162" t="inlineStr"/>
+      <c r="BU162" t="inlineStr">
+        <is>
+          <t>群益</t>
+        </is>
+      </c>
       <c r="BV162" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -26038,7 +26370,7 @@
       </c>
       <c r="BN164" t="inlineStr"/>
       <c r="BO164" t="n">
-        <v>0</v>
+        <v>122480</v>
       </c>
       <c r="BP164" t="n">
         <v>0</v>
@@ -26049,10 +26381,14 @@
       <c r="BT164" t="n">
         <v>0</v>
       </c>
-      <c r="BU164" t="inlineStr"/>
+      <c r="BU164" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV164" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -26180,7 +26516,7 @@
       </c>
       <c r="BN165" t="inlineStr"/>
       <c r="BO165" t="n">
-        <v>0</v>
+        <v>3984800</v>
       </c>
       <c r="BP165" t="n">
         <v>0</v>
@@ -26191,10 +26527,14 @@
       <c r="BT165" t="n">
         <v>0</v>
       </c>
-      <c r="BU165" t="inlineStr"/>
+      <c r="BU165" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV165" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -26322,21 +26662,27 @@
       </c>
       <c r="BN166" t="inlineStr"/>
       <c r="BO166" t="n">
-        <v>0</v>
+        <v>39452220</v>
       </c>
       <c r="BP166" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ166" t="inlineStr"/>
+        <v>28450</v>
+      </c>
+      <c r="BQ166" t="n">
+        <v>1386.72</v>
+      </c>
       <c r="BR166" t="inlineStr"/>
       <c r="BS166" t="inlineStr"/>
       <c r="BT166" t="n">
         <v>0</v>
       </c>
-      <c r="BU166" t="inlineStr"/>
+      <c r="BU166" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV166" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -26464,7 +26810,7 @@
       </c>
       <c r="BN167" t="inlineStr"/>
       <c r="BO167" t="n">
-        <v>0</v>
+        <v>5953770</v>
       </c>
       <c r="BP167" t="n">
         <v>0</v>
@@ -26475,10 +26821,14 @@
       <c r="BT167" t="n">
         <v>0</v>
       </c>
-      <c r="BU167" t="inlineStr"/>
+      <c r="BU167" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV167" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -26606,7 +26956,7 @@
       </c>
       <c r="BN168" t="inlineStr"/>
       <c r="BO168" t="n">
-        <v>0</v>
+        <v>822090</v>
       </c>
       <c r="BP168" t="n">
         <v>0</v>
@@ -26617,10 +26967,14 @@
       <c r="BT168" t="n">
         <v>0</v>
       </c>
-      <c r="BU168" t="inlineStr"/>
+      <c r="BU168" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV168" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -26748,21 +27102,27 @@
       </c>
       <c r="BN169" t="inlineStr"/>
       <c r="BO169" t="n">
-        <v>0</v>
+        <v>67969770</v>
       </c>
       <c r="BP169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ169" t="inlineStr"/>
+        <v>84510</v>
+      </c>
+      <c r="BQ169" t="n">
+        <v>804.28</v>
+      </c>
       <c r="BR169" t="inlineStr"/>
       <c r="BS169" t="inlineStr"/>
       <c r="BT169" t="n">
         <v>0</v>
       </c>
-      <c r="BU169" t="inlineStr"/>
+      <c r="BU169" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV169" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -26890,21 +27250,27 @@
       </c>
       <c r="BN170" t="inlineStr"/>
       <c r="BO170" t="n">
-        <v>0</v>
+        <v>6760120</v>
       </c>
       <c r="BP170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ170" t="inlineStr"/>
+        <v>1050</v>
+      </c>
+      <c r="BQ170" t="n">
+        <v>6438.21</v>
+      </c>
       <c r="BR170" t="inlineStr"/>
       <c r="BS170" t="inlineStr"/>
       <c r="BT170" t="n">
         <v>0</v>
       </c>
-      <c r="BU170" t="inlineStr"/>
+      <c r="BU170" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV170" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -27032,21 +27398,27 @@
       </c>
       <c r="BN171" t="inlineStr"/>
       <c r="BO171" t="n">
-        <v>0</v>
+        <v>16730930</v>
       </c>
       <c r="BP171" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ171" t="inlineStr"/>
+        <v>227300</v>
+      </c>
+      <c r="BQ171" t="n">
+        <v>73.61</v>
+      </c>
       <c r="BR171" t="inlineStr"/>
       <c r="BS171" t="inlineStr"/>
       <c r="BT171" t="n">
         <v>0</v>
       </c>
-      <c r="BU171" t="inlineStr"/>
+      <c r="BU171" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV171" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -27552,7 +27924,7 @@
       </c>
       <c r="BN175" t="inlineStr"/>
       <c r="BO175" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="BP175" t="n">
         <v>0</v>
@@ -27563,10 +27935,14 @@
       <c r="BT175" t="n">
         <v>0</v>
       </c>
-      <c r="BU175" t="inlineStr"/>
+      <c r="BU175" t="inlineStr">
+        <is>
+          <t>元富</t>
+        </is>
+      </c>
       <c r="BV175" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -27694,7 +28070,7 @@
       </c>
       <c r="BN176" t="inlineStr"/>
       <c r="BO176" t="n">
-        <v>0</v>
+        <v>8047800</v>
       </c>
       <c r="BP176" t="n">
         <v>0</v>
@@ -27705,10 +28081,14 @@
       <c r="BT176" t="n">
         <v>0</v>
       </c>
-      <c r="BU176" t="inlineStr"/>
+      <c r="BU176" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV176" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -27962,7 +28342,7 @@
       </c>
       <c r="BN178" t="inlineStr"/>
       <c r="BO178" t="n">
-        <v>0</v>
+        <v>2990060</v>
       </c>
       <c r="BP178" t="n">
         <v>0</v>
@@ -27973,10 +28353,14 @@
       <c r="BT178" t="n">
         <v>0</v>
       </c>
-      <c r="BU178" t="inlineStr"/>
+      <c r="BU178" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV178" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -28104,7 +28488,7 @@
       </c>
       <c r="BN179" t="inlineStr"/>
       <c r="BO179" t="n">
-        <v>0</v>
+        <v>28530</v>
       </c>
       <c r="BP179" t="n">
         <v>0</v>
@@ -28115,10 +28499,14 @@
       <c r="BT179" t="n">
         <v>0</v>
       </c>
-      <c r="BU179" t="inlineStr"/>
+      <c r="BU179" t="inlineStr">
+        <is>
+          <t>國泰</t>
+        </is>
+      </c>
       <c r="BV179" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -28372,7 +28760,7 @@
       </c>
       <c r="BN181" t="inlineStr"/>
       <c r="BO181" t="n">
-        <v>0</v>
+        <v>6944990</v>
       </c>
       <c r="BP181" t="n">
         <v>0</v>
@@ -28383,10 +28771,14 @@
       <c r="BT181" t="n">
         <v>0</v>
       </c>
-      <c r="BU181" t="inlineStr"/>
+      <c r="BU181" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV181" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28919,7 @@
       </c>
       <c r="BU182" t="inlineStr">
         <is>
-          <t>國票</t>
+          <t>中信</t>
         </is>
       </c>
       <c r="BV182" t="inlineStr">
@@ -28912,7 +29304,7 @@
       </c>
       <c r="BN185" t="inlineStr"/>
       <c r="BO185" t="n">
-        <v>0</v>
+        <v>102470</v>
       </c>
       <c r="BP185" t="n">
         <v>0</v>
@@ -28923,10 +29315,14 @@
       <c r="BT185" t="n">
         <v>0</v>
       </c>
-      <c r="BU185" t="inlineStr"/>
+      <c r="BU185" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV185" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -29054,21 +29450,27 @@
       </c>
       <c r="BN186" t="inlineStr"/>
       <c r="BO186" t="n">
-        <v>0</v>
+        <v>11247950</v>
       </c>
       <c r="BP186" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ186" t="inlineStr"/>
+        <v>49320</v>
+      </c>
+      <c r="BQ186" t="n">
+        <v>228.06</v>
+      </c>
       <c r="BR186" t="inlineStr"/>
       <c r="BS186" t="inlineStr"/>
       <c r="BT186" t="n">
         <v>0</v>
       </c>
-      <c r="BU186" t="inlineStr"/>
+      <c r="BU186" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV186" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -29322,21 +29724,27 @@
       </c>
       <c r="BN188" t="inlineStr"/>
       <c r="BO188" t="n">
-        <v>0</v>
+        <v>3982860</v>
       </c>
       <c r="BP188" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ188" t="inlineStr"/>
+        <v>109700</v>
+      </c>
+      <c r="BQ188" t="n">
+        <v>36.31</v>
+      </c>
       <c r="BR188" t="inlineStr"/>
       <c r="BS188" t="inlineStr"/>
       <c r="BT188" t="n">
         <v>0</v>
       </c>
-      <c r="BU188" t="inlineStr"/>
+      <c r="BU188" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV188" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -29590,7 +29998,7 @@
       </c>
       <c r="BN190" t="inlineStr"/>
       <c r="BO190" t="n">
-        <v>0</v>
+        <v>690200</v>
       </c>
       <c r="BP190" t="n">
         <v>0</v>
@@ -29601,10 +30009,14 @@
       <c r="BT190" t="n">
         <v>0</v>
       </c>
-      <c r="BU190" t="inlineStr"/>
+      <c r="BU190" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV190" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -29732,7 +30144,7 @@
       </c>
       <c r="BN191" t="inlineStr"/>
       <c r="BO191" t="n">
-        <v>0</v>
+        <v>895210</v>
       </c>
       <c r="BP191" t="n">
         <v>0</v>
@@ -29743,10 +30155,14 @@
       <c r="BT191" t="n">
         <v>0</v>
       </c>
-      <c r="BU191" t="inlineStr"/>
+      <c r="BU191" t="inlineStr">
+        <is>
+          <t>群益</t>
+        </is>
+      </c>
       <c r="BV191" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -29874,21 +30290,27 @@
       </c>
       <c r="BN192" t="inlineStr"/>
       <c r="BO192" t="n">
-        <v>0</v>
+        <v>5519010</v>
       </c>
       <c r="BP192" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ192" t="inlineStr"/>
+        <v>18950</v>
+      </c>
+      <c r="BQ192" t="n">
+        <v>291.24</v>
+      </c>
       <c r="BR192" t="inlineStr"/>
       <c r="BS192" t="inlineStr"/>
       <c r="BT192" t="n">
         <v>0</v>
       </c>
-      <c r="BU192" t="inlineStr"/>
+      <c r="BU192" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV192" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -30394,21 +30816,27 @@
       </c>
       <c r="BN196" t="inlineStr"/>
       <c r="BO196" t="n">
-        <v>0</v>
+        <v>35451090</v>
       </c>
       <c r="BP196" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ196" t="inlineStr"/>
+        <v>808740</v>
+      </c>
+      <c r="BQ196" t="n">
+        <v>43.83</v>
+      </c>
       <c r="BR196" t="inlineStr"/>
       <c r="BS196" t="inlineStr"/>
       <c r="BT196" t="n">
         <v>0</v>
       </c>
-      <c r="BU196" t="inlineStr"/>
+      <c r="BU196" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV196" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -30788,21 +31216,27 @@
       </c>
       <c r="BN199" t="inlineStr"/>
       <c r="BO199" t="n">
-        <v>0</v>
+        <v>34408480</v>
       </c>
       <c r="BP199" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ199" t="inlineStr"/>
+        <v>1238330</v>
+      </c>
+      <c r="BQ199" t="n">
+        <v>27.79</v>
+      </c>
       <c r="BR199" t="inlineStr"/>
       <c r="BS199" t="inlineStr"/>
       <c r="BT199" t="n">
         <v>0</v>
       </c>
-      <c r="BU199" t="inlineStr"/>
+      <c r="BU199" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV199" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -30930,7 +31364,7 @@
       </c>
       <c r="BN200" t="inlineStr"/>
       <c r="BO200" t="n">
-        <v>0</v>
+        <v>12822110</v>
       </c>
       <c r="BP200" t="n">
         <v>0</v>
@@ -30943,12 +31377,12 @@
       </c>
       <c r="BU200" t="inlineStr">
         <is>
-          <t>中信</t>
+          <t>富邦</t>
         </is>
       </c>
       <c r="BV200" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -31076,7 +31510,7 @@
       </c>
       <c r="BN201" t="inlineStr"/>
       <c r="BO201" t="n">
-        <v>0</v>
+        <v>647590</v>
       </c>
       <c r="BP201" t="n">
         <v>0</v>
@@ -31089,12 +31523,12 @@
       </c>
       <c r="BU201" t="inlineStr">
         <is>
-          <t>兆豐</t>
+          <t>富邦</t>
         </is>
       </c>
       <c r="BV201" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -31233,7 +31667,11 @@
       <c r="BT202" t="n">
         <v>0</v>
       </c>
-      <c r="BU202" t="inlineStr"/>
+      <c r="BU202" t="inlineStr">
+        <is>
+          <t>元展</t>
+        </is>
+      </c>
       <c r="BV202" t="inlineStr">
         <is>
           <t>今日無可用權證成交金額</t>
@@ -31364,7 +31802,7 @@
       </c>
       <c r="BN203" t="inlineStr"/>
       <c r="BO203" t="n">
-        <v>0</v>
+        <v>4361860</v>
       </c>
       <c r="BP203" t="n">
         <v>0</v>
@@ -31375,10 +31813,14 @@
       <c r="BT203" t="n">
         <v>0</v>
       </c>
-      <c r="BU203" t="inlineStr"/>
+      <c r="BU203" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV203" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -31632,7 +32074,7 @@
       </c>
       <c r="BN205" t="inlineStr"/>
       <c r="BO205" t="n">
-        <v>0</v>
+        <v>606990</v>
       </c>
       <c r="BP205" t="n">
         <v>0</v>
@@ -31643,10 +32085,14 @@
       <c r="BT205" t="n">
         <v>0</v>
       </c>
-      <c r="BU205" t="inlineStr"/>
+      <c r="BU205" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
       <c r="BV205" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -31774,21 +32220,27 @@
       </c>
       <c r="BN206" t="inlineStr"/>
       <c r="BO206" t="n">
-        <v>0</v>
+        <v>11232390</v>
       </c>
       <c r="BP206" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ206" t="inlineStr"/>
+        <v>45000</v>
+      </c>
+      <c r="BQ206" t="n">
+        <v>249.61</v>
+      </c>
       <c r="BR206" t="inlineStr"/>
       <c r="BS206" t="inlineStr"/>
       <c r="BT206" t="n">
         <v>0</v>
       </c>
-      <c r="BU206" t="inlineStr"/>
+      <c r="BU206" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="BV206" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -32168,7 +32620,7 @@
       </c>
       <c r="BN209" t="inlineStr"/>
       <c r="BO209" t="n">
-        <v>0</v>
+        <v>8504380</v>
       </c>
       <c r="BP209" t="n">
         <v>0</v>
@@ -32179,10 +32631,14 @@
       <c r="BT209" t="n">
         <v>0</v>
       </c>
-      <c r="BU209" t="inlineStr"/>
+      <c r="BU209" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV209" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -32436,7 +32892,7 @@
       </c>
       <c r="BN211" t="inlineStr"/>
       <c r="BO211" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="BP211" t="n">
         <v>0</v>
@@ -32447,10 +32903,14 @@
       <c r="BT211" t="n">
         <v>0</v>
       </c>
-      <c r="BU211" t="inlineStr"/>
+      <c r="BU211" t="inlineStr">
+        <is>
+          <t>兆豐</t>
+        </is>
+      </c>
       <c r="BV211" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -33082,21 +33542,27 @@
       </c>
       <c r="BN216" t="inlineStr"/>
       <c r="BO216" t="n">
-        <v>0</v>
+        <v>4615210</v>
       </c>
       <c r="BP216" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ216" t="inlineStr"/>
+        <v>27320</v>
+      </c>
+      <c r="BQ216" t="n">
+        <v>168.93</v>
+      </c>
       <c r="BR216" t="inlineStr"/>
       <c r="BS216" t="inlineStr"/>
       <c r="BT216" t="n">
         <v>0</v>
       </c>
-      <c r="BU216" t="inlineStr"/>
+      <c r="BU216" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV216" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -33224,21 +33690,27 @@
       </c>
       <c r="BN217" t="inlineStr"/>
       <c r="BO217" t="n">
-        <v>0</v>
+        <v>6699310</v>
       </c>
       <c r="BP217" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ217" t="inlineStr"/>
+        <v>208820</v>
+      </c>
+      <c r="BQ217" t="n">
+        <v>32.08</v>
+      </c>
       <c r="BR217" t="inlineStr"/>
       <c r="BS217" t="inlineStr"/>
       <c r="BT217" t="n">
         <v>0</v>
       </c>
-      <c r="BU217" t="inlineStr"/>
+      <c r="BU217" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV217" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -33366,21 +33838,27 @@
       </c>
       <c r="BN218" t="inlineStr"/>
       <c r="BO218" t="n">
-        <v>0</v>
+        <v>39784560</v>
       </c>
       <c r="BP218" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ218" t="inlineStr"/>
+        <v>484040</v>
+      </c>
+      <c r="BQ218" t="n">
+        <v>82.19</v>
+      </c>
       <c r="BR218" t="inlineStr"/>
       <c r="BS218" t="inlineStr"/>
       <c r="BT218" t="n">
         <v>0</v>
       </c>
-      <c r="BU218" t="inlineStr"/>
+      <c r="BU218" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV218" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -33634,7 +34112,7 @@
       </c>
       <c r="BN220" t="inlineStr"/>
       <c r="BO220" t="n">
-        <v>0</v>
+        <v>99810</v>
       </c>
       <c r="BP220" t="n">
         <v>0</v>
@@ -33645,10 +34123,14 @@
       <c r="BT220" t="n">
         <v>0</v>
       </c>
-      <c r="BU220" t="inlineStr"/>
+      <c r="BU220" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV220" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -33776,7 +34258,7 @@
       </c>
       <c r="BN221" t="inlineStr"/>
       <c r="BO221" t="n">
-        <v>0</v>
+        <v>4169330</v>
       </c>
       <c r="BP221" t="n">
         <v>0</v>
@@ -33787,10 +34269,14 @@
       <c r="BT221" t="n">
         <v>0</v>
       </c>
-      <c r="BU221" t="inlineStr"/>
+      <c r="BU221" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV221" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -34044,7 +34530,7 @@
       </c>
       <c r="BN223" t="inlineStr"/>
       <c r="BO223" t="n">
-        <v>0</v>
+        <v>8243810</v>
       </c>
       <c r="BP223" t="n">
         <v>0</v>
@@ -34055,10 +34541,14 @@
       <c r="BT223" t="n">
         <v>0</v>
       </c>
-      <c r="BU223" t="inlineStr"/>
+      <c r="BU223" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV223" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -34186,7 +34676,7 @@
       </c>
       <c r="BN224" t="inlineStr"/>
       <c r="BO224" t="n">
-        <v>0</v>
+        <v>5607680</v>
       </c>
       <c r="BP224" t="n">
         <v>0</v>
@@ -34197,10 +34687,14 @@
       <c r="BT224" t="n">
         <v>0</v>
       </c>
-      <c r="BU224" t="inlineStr"/>
+      <c r="BU224" t="inlineStr">
+        <is>
+          <t>富邦</t>
+        </is>
+      </c>
       <c r="BV224" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -34706,7 +35200,7 @@
       </c>
       <c r="BN228" t="inlineStr"/>
       <c r="BO228" t="n">
-        <v>0</v>
+        <v>755410</v>
       </c>
       <c r="BP228" t="n">
         <v>0</v>
@@ -34717,10 +35211,14 @@
       <c r="BT228" t="n">
         <v>0</v>
       </c>
-      <c r="BU228" t="inlineStr"/>
+      <c r="BU228" t="inlineStr">
+        <is>
+          <t>群益</t>
+        </is>
+      </c>
       <c r="BV228" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -34848,21 +35346,27 @@
       </c>
       <c r="BN229" t="inlineStr"/>
       <c r="BO229" t="n">
-        <v>0</v>
+        <v>48046350</v>
       </c>
       <c r="BP229" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ229" t="inlineStr"/>
+        <v>1397880</v>
+      </c>
+      <c r="BQ229" t="n">
+        <v>34.37</v>
+      </c>
       <c r="BR229" t="inlineStr"/>
       <c r="BS229" t="inlineStr"/>
       <c r="BT229" t="n">
         <v>0</v>
       </c>
-      <c r="BU229" t="inlineStr"/>
+      <c r="BU229" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV229" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -34990,7 +35494,7 @@
       </c>
       <c r="BN230" t="inlineStr"/>
       <c r="BO230" t="n">
-        <v>0</v>
+        <v>3471640</v>
       </c>
       <c r="BP230" t="n">
         <v>0</v>
@@ -35001,10 +35505,14 @@
       <c r="BT230" t="n">
         <v>0</v>
       </c>
-      <c r="BU230" t="inlineStr"/>
+      <c r="BU230" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV230" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -35258,7 +35766,7 @@
       </c>
       <c r="BN232" t="inlineStr"/>
       <c r="BO232" t="n">
-        <v>0</v>
+        <v>19180</v>
       </c>
       <c r="BP232" t="n">
         <v>0</v>
@@ -35269,10 +35777,14 @@
       <c r="BT232" t="n">
         <v>0</v>
       </c>
-      <c r="BU232" t="inlineStr"/>
+      <c r="BU232" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
       <c r="BV232" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -35400,21 +35912,27 @@
       </c>
       <c r="BN233" t="inlineStr"/>
       <c r="BO233" t="n">
-        <v>0</v>
+        <v>12247650</v>
       </c>
       <c r="BP233" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ233" t="inlineStr"/>
+        <v>33810</v>
+      </c>
+      <c r="BQ233" t="n">
+        <v>362.25</v>
+      </c>
       <c r="BR233" t="inlineStr"/>
       <c r="BS233" t="inlineStr"/>
       <c r="BT233" t="n">
         <v>0</v>
       </c>
-      <c r="BU233" t="inlineStr"/>
+      <c r="BU233" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV233" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -35542,7 +36060,7 @@
       </c>
       <c r="BN234" t="inlineStr"/>
       <c r="BO234" t="n">
-        <v>0</v>
+        <v>3381580</v>
       </c>
       <c r="BP234" t="n">
         <v>0</v>
@@ -35553,10 +36071,14 @@
       <c r="BT234" t="n">
         <v>0</v>
       </c>
-      <c r="BU234" t="inlineStr"/>
+      <c r="BU234" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV234" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -35684,21 +36206,27 @@
       </c>
       <c r="BN235" t="inlineStr"/>
       <c r="BO235" t="n">
-        <v>0</v>
+        <v>1641030</v>
       </c>
       <c r="BP235" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ235" t="inlineStr"/>
+        <v>19500</v>
+      </c>
+      <c r="BQ235" t="n">
+        <v>84.16</v>
+      </c>
       <c r="BR235" t="inlineStr"/>
       <c r="BS235" t="inlineStr"/>
       <c r="BT235" t="n">
         <v>0</v>
       </c>
-      <c r="BU235" t="inlineStr"/>
+      <c r="BU235" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV235" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -35826,21 +36354,27 @@
       </c>
       <c r="BN236" t="inlineStr"/>
       <c r="BO236" t="n">
-        <v>0</v>
+        <v>17931910</v>
       </c>
       <c r="BP236" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ236" t="inlineStr"/>
+        <v>162130</v>
+      </c>
+      <c r="BQ236" t="n">
+        <v>110.6</v>
+      </c>
       <c r="BR236" t="inlineStr"/>
       <c r="BS236" t="inlineStr"/>
       <c r="BT236" t="n">
         <v>0</v>
       </c>
-      <c r="BU236" t="inlineStr"/>
+      <c r="BU236" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV236" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -35968,7 +36502,7 @@
       </c>
       <c r="BN237" t="inlineStr"/>
       <c r="BO237" t="n">
-        <v>0</v>
+        <v>758780</v>
       </c>
       <c r="BP237" t="n">
         <v>0</v>
@@ -35981,12 +36515,12 @@
       </c>
       <c r="BU237" t="inlineStr">
         <is>
-          <t>第一</t>
+          <t>群益</t>
         </is>
       </c>
       <c r="BV237" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -36114,21 +36648,27 @@
       </c>
       <c r="BN238" t="inlineStr"/>
       <c r="BO238" t="n">
-        <v>0</v>
+        <v>18727980</v>
       </c>
       <c r="BP238" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ238" t="inlineStr"/>
+        <v>1244270</v>
+      </c>
+      <c r="BQ238" t="n">
+        <v>15.05</v>
+      </c>
       <c r="BR238" t="inlineStr"/>
       <c r="BS238" t="inlineStr"/>
       <c r="BT238" t="n">
         <v>0</v>
       </c>
-      <c r="BU238" t="inlineStr"/>
+      <c r="BU238" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV238" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -36256,21 +36796,27 @@
       </c>
       <c r="BN239" t="inlineStr"/>
       <c r="BO239" t="n">
-        <v>0</v>
+        <v>59325140</v>
       </c>
       <c r="BP239" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ239" t="inlineStr"/>
+        <v>2835870</v>
+      </c>
+      <c r="BQ239" t="n">
+        <v>20.92</v>
+      </c>
       <c r="BR239" t="inlineStr"/>
       <c r="BS239" t="inlineStr"/>
       <c r="BT239" t="n">
         <v>0</v>
       </c>
-      <c r="BU239" t="inlineStr"/>
+      <c r="BU239" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV239" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -36398,21 +36944,27 @@
       </c>
       <c r="BN240" t="inlineStr"/>
       <c r="BO240" t="n">
-        <v>0</v>
+        <v>31007840</v>
       </c>
       <c r="BP240" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ240" t="inlineStr"/>
+        <v>1408320</v>
+      </c>
+      <c r="BQ240" t="n">
+        <v>22.02</v>
+      </c>
       <c r="BR240" t="inlineStr"/>
       <c r="BS240" t="inlineStr"/>
       <c r="BT240" t="n">
         <v>0</v>
       </c>
-      <c r="BU240" t="inlineStr"/>
+      <c r="BU240" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV240" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -36540,21 +37092,27 @@
       </c>
       <c r="BN241" t="inlineStr"/>
       <c r="BO241" t="n">
-        <v>0</v>
+        <v>57315210</v>
       </c>
       <c r="BP241" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ241" t="inlineStr"/>
+        <v>1156870</v>
+      </c>
+      <c r="BQ241" t="n">
+        <v>49.54</v>
+      </c>
       <c r="BR241" t="inlineStr"/>
       <c r="BS241" t="inlineStr"/>
       <c r="BT241" t="n">
         <v>0</v>
       </c>
-      <c r="BU241" t="inlineStr"/>
+      <c r="BU241" t="inlineStr">
+        <is>
+          <t>富邦</t>
+        </is>
+      </c>
       <c r="BV241" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -36682,7 +37240,7 @@
       </c>
       <c r="BN242" t="inlineStr"/>
       <c r="BO242" t="n">
-        <v>0</v>
+        <v>142050</v>
       </c>
       <c r="BP242" t="n">
         <v>0</v>
@@ -36695,12 +37253,12 @@
       </c>
       <c r="BU242" t="inlineStr">
         <is>
-          <t>玉山</t>
+          <t>富邦</t>
         </is>
       </c>
       <c r="BV242" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -36828,21 +37386,27 @@
       </c>
       <c r="BN243" t="inlineStr"/>
       <c r="BO243" t="n">
-        <v>0</v>
+        <v>9711960</v>
       </c>
       <c r="BP243" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ243" t="inlineStr"/>
+        <v>323710</v>
+      </c>
+      <c r="BQ243" t="n">
+        <v>30</v>
+      </c>
       <c r="BR243" t="inlineStr"/>
       <c r="BS243" t="inlineStr"/>
       <c r="BT243" t="n">
         <v>0</v>
       </c>
-      <c r="BU243" t="inlineStr"/>
+      <c r="BU243" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
       <c r="BV243" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -36970,21 +37534,27 @@
       </c>
       <c r="BN244" t="inlineStr"/>
       <c r="BO244" t="n">
-        <v>0</v>
+        <v>14703320</v>
       </c>
       <c r="BP244" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ244" t="inlineStr"/>
+        <v>9800</v>
+      </c>
+      <c r="BQ244" t="n">
+        <v>1500.34</v>
+      </c>
       <c r="BR244" t="inlineStr"/>
       <c r="BS244" t="inlineStr"/>
       <c r="BT244" t="n">
         <v>0</v>
       </c>
-      <c r="BU244" t="inlineStr"/>
+      <c r="BU244" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV244" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -37112,21 +37682,27 @@
       </c>
       <c r="BN245" t="inlineStr"/>
       <c r="BO245" t="n">
-        <v>0</v>
+        <v>14002820</v>
       </c>
       <c r="BP245" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ245" t="inlineStr"/>
+        <v>114600</v>
+      </c>
+      <c r="BQ245" t="n">
+        <v>122.19</v>
+      </c>
       <c r="BR245" t="inlineStr"/>
       <c r="BS245" t="inlineStr"/>
       <c r="BT245" t="n">
         <v>0</v>
       </c>
-      <c r="BU245" t="inlineStr"/>
+      <c r="BU245" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV245" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -37517,7 +38093,11 @@
       <c r="BT248" t="n">
         <v>0</v>
       </c>
-      <c r="BU248" t="inlineStr"/>
+      <c r="BU248" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV248" t="inlineStr">
         <is>
           <t>今日無可用權證成交金額</t>
@@ -37900,7 +38480,7 @@
       </c>
       <c r="BN251" t="inlineStr"/>
       <c r="BO251" t="n">
-        <v>0</v>
+        <v>2364590</v>
       </c>
       <c r="BP251" t="n">
         <v>0</v>
@@ -37911,10 +38491,14 @@
       <c r="BT251" t="n">
         <v>0</v>
       </c>
-      <c r="BU251" t="inlineStr"/>
+      <c r="BU251" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV251" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -38294,7 +38878,7 @@
       </c>
       <c r="BN254" t="inlineStr"/>
       <c r="BO254" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="BP254" t="n">
         <v>0</v>
@@ -38305,10 +38889,14 @@
       <c r="BT254" t="n">
         <v>0</v>
       </c>
-      <c r="BU254" t="inlineStr"/>
+      <c r="BU254" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
       <c r="BV254" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -38436,7 +39024,7 @@
       </c>
       <c r="BN255" t="inlineStr"/>
       <c r="BO255" t="n">
-        <v>0</v>
+        <v>1984450</v>
       </c>
       <c r="BP255" t="n">
         <v>0</v>
@@ -38447,10 +39035,14 @@
       <c r="BT255" t="n">
         <v>0</v>
       </c>
-      <c r="BU255" t="inlineStr"/>
+      <c r="BU255" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
       <c r="BV255" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -38704,7 +39296,7 @@
       </c>
       <c r="BN257" t="inlineStr"/>
       <c r="BO257" t="n">
-        <v>0</v>
+        <v>6523450</v>
       </c>
       <c r="BP257" t="n">
         <v>0</v>
@@ -38715,10 +39307,14 @@
       <c r="BT257" t="n">
         <v>0</v>
       </c>
-      <c r="BU257" t="inlineStr"/>
+      <c r="BU257" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="BV257" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -39350,7 +39946,7 @@
       </c>
       <c r="BN262" t="inlineStr"/>
       <c r="BO262" t="n">
-        <v>0</v>
+        <v>624700</v>
       </c>
       <c r="BP262" t="n">
         <v>0</v>
@@ -39361,10 +39957,14 @@
       <c r="BT262" t="n">
         <v>0</v>
       </c>
-      <c r="BU262" t="inlineStr"/>
+      <c r="BU262" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV262" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -39618,21 +40218,27 @@
       </c>
       <c r="BN264" t="inlineStr"/>
       <c r="BO264" t="n">
-        <v>0</v>
+        <v>8731610</v>
       </c>
       <c r="BP264" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ264" t="inlineStr"/>
+        <v>150430</v>
+      </c>
+      <c r="BQ264" t="n">
+        <v>58.04</v>
+      </c>
       <c r="BR264" t="inlineStr"/>
       <c r="BS264" t="inlineStr"/>
       <c r="BT264" t="n">
         <v>0</v>
       </c>
-      <c r="BU264" t="inlineStr"/>
+      <c r="BU264" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV264" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -39886,21 +40492,27 @@
       </c>
       <c r="BN266" t="inlineStr"/>
       <c r="BO266" t="n">
-        <v>0</v>
+        <v>7303830</v>
       </c>
       <c r="BP266" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ266" t="inlineStr"/>
+        <v>37100</v>
+      </c>
+      <c r="BQ266" t="n">
+        <v>196.87</v>
+      </c>
       <c r="BR266" t="inlineStr"/>
       <c r="BS266" t="inlineStr"/>
       <c r="BT266" t="n">
         <v>0</v>
       </c>
-      <c r="BU266" t="inlineStr"/>
+      <c r="BU266" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV266" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -40028,7 +40640,7 @@
       </c>
       <c r="BN267" t="inlineStr"/>
       <c r="BO267" t="n">
-        <v>0</v>
+        <v>1499630</v>
       </c>
       <c r="BP267" t="n">
         <v>0</v>
@@ -40039,10 +40651,14 @@
       <c r="BT267" t="n">
         <v>0</v>
       </c>
-      <c r="BU267" t="inlineStr"/>
+      <c r="BU267" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV267" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -40170,7 +40786,7 @@
       </c>
       <c r="BN268" t="inlineStr"/>
       <c r="BO268" t="n">
-        <v>0</v>
+        <v>1562480</v>
       </c>
       <c r="BP268" t="n">
         <v>0</v>
@@ -40181,10 +40797,14 @@
       <c r="BT268" t="n">
         <v>0</v>
       </c>
-      <c r="BU268" t="inlineStr"/>
+      <c r="BU268" t="inlineStr">
+        <is>
+          <t>元富</t>
+        </is>
+      </c>
       <c r="BV268" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -40564,7 +41184,7 @@
       </c>
       <c r="BN271" t="inlineStr"/>
       <c r="BO271" t="n">
-        <v>0</v>
+        <v>2548350</v>
       </c>
       <c r="BP271" t="n">
         <v>0</v>
@@ -40575,10 +41195,14 @@
       <c r="BT271" t="n">
         <v>0</v>
       </c>
-      <c r="BU271" t="inlineStr"/>
+      <c r="BU271" t="inlineStr">
+        <is>
+          <t>國泰</t>
+        </is>
+      </c>
       <c r="BV271" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -40968,21 +41592,27 @@
       </c>
       <c r="BN274" t="inlineStr"/>
       <c r="BO274" t="n">
-        <v>0</v>
+        <v>9478170</v>
       </c>
       <c r="BP274" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ274" t="inlineStr"/>
+        <v>20140</v>
+      </c>
+      <c r="BQ274" t="n">
+        <v>470.61</v>
+      </c>
       <c r="BR274" t="inlineStr"/>
       <c r="BS274" t="inlineStr"/>
       <c r="BT274" t="n">
         <v>0</v>
       </c>
-      <c r="BU274" t="inlineStr"/>
+      <c r="BU274" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="BV274" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -41120,7 +41750,7 @@
       </c>
       <c r="BN275" t="inlineStr"/>
       <c r="BO275" t="n">
-        <v>0</v>
+        <v>6944990</v>
       </c>
       <c r="BP275" t="n">
         <v>0</v>
@@ -41131,10 +41761,14 @@
       <c r="BT275" t="n">
         <v>0</v>
       </c>
-      <c r="BU275" t="inlineStr"/>
+      <c r="BU275" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV275" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -41272,7 +41906,7 @@
       </c>
       <c r="BN276" t="inlineStr"/>
       <c r="BO276" t="n">
-        <v>0</v>
+        <v>822090</v>
       </c>
       <c r="BP276" t="n">
         <v>0</v>
@@ -41283,10 +41917,14 @@
       <c r="BT276" t="n">
         <v>0</v>
       </c>
-      <c r="BU276" t="inlineStr"/>
+      <c r="BU276" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV276" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -41424,7 +42062,7 @@
       </c>
       <c r="BN277" t="inlineStr"/>
       <c r="BO277" t="n">
-        <v>0</v>
+        <v>12822110</v>
       </c>
       <c r="BP277" t="n">
         <v>0</v>
@@ -41437,12 +42075,12 @@
       </c>
       <c r="BU277" t="inlineStr">
         <is>
-          <t>中信</t>
+          <t>富邦</t>
         </is>
       </c>
       <c r="BV277" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -41716,7 +42354,7 @@
       </c>
       <c r="BN279" t="inlineStr"/>
       <c r="BO279" t="n">
-        <v>0</v>
+        <v>99810</v>
       </c>
       <c r="BP279" t="n">
         <v>0</v>
@@ -41727,10 +42365,14 @@
       <c r="BT279" t="n">
         <v>0</v>
       </c>
-      <c r="BU279" t="inlineStr"/>
+      <c r="BU279" t="inlineStr">
+        <is>
+          <t>凱基</t>
+        </is>
+      </c>
       <c r="BV279" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -42004,21 +42646,27 @@
       </c>
       <c r="BN281" t="inlineStr"/>
       <c r="BO281" t="n">
-        <v>0</v>
+        <v>17931910</v>
       </c>
       <c r="BP281" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ281" t="inlineStr"/>
+        <v>162130</v>
+      </c>
+      <c r="BQ281" t="n">
+        <v>110.6</v>
+      </c>
       <c r="BR281" t="inlineStr"/>
       <c r="BS281" t="inlineStr"/>
       <c r="BT281" t="n">
         <v>0</v>
       </c>
-      <c r="BU281" t="inlineStr"/>
+      <c r="BU281" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV281" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -42272,21 +42920,27 @@
       </c>
       <c r="BN283" t="inlineStr"/>
       <c r="BO283" t="n">
-        <v>0</v>
+        <v>695420</v>
       </c>
       <c r="BP283" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ283" t="inlineStr"/>
+        <v>40600</v>
+      </c>
+      <c r="BQ283" t="n">
+        <v>17.13</v>
+      </c>
       <c r="BR283" t="inlineStr"/>
       <c r="BS283" t="inlineStr"/>
       <c r="BT283" t="n">
         <v>0</v>
       </c>
-      <c r="BU283" t="inlineStr"/>
+      <c r="BU283" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV283" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -42414,21 +43068,27 @@
       </c>
       <c r="BN284" t="inlineStr"/>
       <c r="BO284" t="n">
-        <v>0</v>
+        <v>6259170</v>
       </c>
       <c r="BP284" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ284" t="inlineStr"/>
+        <v>145780</v>
+      </c>
+      <c r="BQ284" t="n">
+        <v>42.94</v>
+      </c>
       <c r="BR284" t="inlineStr"/>
       <c r="BS284" t="inlineStr"/>
       <c r="BT284" t="n">
         <v>0</v>
       </c>
-      <c r="BU284" t="inlineStr"/>
+      <c r="BU284" t="inlineStr">
+        <is>
+          <t>兆豐</t>
+        </is>
+      </c>
       <c r="BV284" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -42556,7 +43216,7 @@
       </c>
       <c r="BN285" t="inlineStr"/>
       <c r="BO285" t="n">
-        <v>0</v>
+        <v>74370</v>
       </c>
       <c r="BP285" t="n">
         <v>0</v>
@@ -42567,10 +43227,14 @@
       <c r="BT285" t="n">
         <v>0</v>
       </c>
-      <c r="BU285" t="inlineStr"/>
+      <c r="BU285" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
       <c r="BV285" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -42698,21 +43362,27 @@
       </c>
       <c r="BN286" t="inlineStr"/>
       <c r="BO286" t="n">
-        <v>0</v>
+        <v>16720700</v>
       </c>
       <c r="BP286" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ286" t="inlineStr"/>
+        <v>106230</v>
+      </c>
+      <c r="BQ286" t="n">
+        <v>157.4</v>
+      </c>
       <c r="BR286" t="inlineStr"/>
       <c r="BS286" t="inlineStr"/>
       <c r="BT286" t="n">
         <v>0</v>
       </c>
-      <c r="BU286" t="inlineStr"/>
+      <c r="BU286" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV286" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -43344,21 +44014,27 @@
       </c>
       <c r="BN291" t="inlineStr"/>
       <c r="BO291" t="n">
-        <v>0</v>
+        <v>14703320</v>
       </c>
       <c r="BP291" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ291" t="inlineStr"/>
+        <v>9800</v>
+      </c>
+      <c r="BQ291" t="n">
+        <v>1500.34</v>
+      </c>
       <c r="BR291" t="inlineStr"/>
       <c r="BS291" t="inlineStr"/>
       <c r="BT291" t="n">
         <v>0</v>
       </c>
-      <c r="BU291" t="inlineStr"/>
+      <c r="BU291" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV291" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -43486,7 +44162,7 @@
       </c>
       <c r="BN292" t="inlineStr"/>
       <c r="BO292" t="n">
-        <v>0</v>
+        <v>1619890</v>
       </c>
       <c r="BP292" t="n">
         <v>0</v>
@@ -43497,10 +44173,14 @@
       <c r="BT292" t="n">
         <v>0</v>
       </c>
-      <c r="BU292" t="inlineStr"/>
+      <c r="BU292" t="inlineStr">
+        <is>
+          <t>台新</t>
+        </is>
+      </c>
       <c r="BV292" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -43754,7 +44434,7 @@
       </c>
       <c r="BN294" t="inlineStr"/>
       <c r="BO294" t="n">
-        <v>0</v>
+        <v>867210</v>
       </c>
       <c r="BP294" t="n">
         <v>0</v>
@@ -43765,10 +44445,14 @@
       <c r="BT294" t="n">
         <v>0</v>
       </c>
-      <c r="BU294" t="inlineStr"/>
+      <c r="BU294" t="inlineStr">
+        <is>
+          <t>永豐</t>
+        </is>
+      </c>
       <c r="BV294" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -43896,21 +44580,27 @@
       </c>
       <c r="BN295" t="inlineStr"/>
       <c r="BO295" t="n">
-        <v>0</v>
+        <v>1458330</v>
       </c>
       <c r="BP295" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ295" t="inlineStr"/>
+        <v>140080</v>
+      </c>
+      <c r="BQ295" t="n">
+        <v>10.41</v>
+      </c>
       <c r="BR295" t="inlineStr"/>
       <c r="BS295" t="inlineStr"/>
       <c r="BT295" t="n">
         <v>0</v>
       </c>
-      <c r="BU295" t="inlineStr"/>
+      <c r="BU295" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV295" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -44038,7 +44728,7 @@
       </c>
       <c r="BN296" t="inlineStr"/>
       <c r="BO296" t="n">
-        <v>0</v>
+        <v>581090</v>
       </c>
       <c r="BP296" t="n">
         <v>0</v>
@@ -44049,10 +44739,14 @@
       <c r="BT296" t="n">
         <v>0</v>
       </c>
-      <c r="BU296" t="inlineStr"/>
+      <c r="BU296" t="inlineStr">
+        <is>
+          <t>元富</t>
+        </is>
+      </c>
       <c r="BV296" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -44306,7 +45000,7 @@
       </c>
       <c r="BN298" t="inlineStr"/>
       <c r="BO298" t="n">
-        <v>0</v>
+        <v>159520</v>
       </c>
       <c r="BP298" t="n">
         <v>0</v>
@@ -44317,10 +45011,14 @@
       <c r="BT298" t="n">
         <v>0</v>
       </c>
-      <c r="BU298" t="inlineStr"/>
+      <c r="BU298" t="inlineStr">
+        <is>
+          <t>國票</t>
+        </is>
+      </c>
       <c r="BV298" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -44448,7 +45146,7 @@
       </c>
       <c r="BN299" t="inlineStr"/>
       <c r="BO299" t="n">
-        <v>0</v>
+        <v>210620</v>
       </c>
       <c r="BP299" t="n">
         <v>0</v>
@@ -44459,10 +45157,14 @@
       <c r="BT299" t="n">
         <v>0</v>
       </c>
-      <c r="BU299" t="inlineStr"/>
+      <c r="BU299" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="BV299" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -44842,7 +45544,7 @@
       </c>
       <c r="BN302" t="inlineStr"/>
       <c r="BO302" t="n">
-        <v>0</v>
+        <v>3808110</v>
       </c>
       <c r="BP302" t="n">
         <v>0</v>
@@ -44853,10 +45555,14 @@
       <c r="BT302" t="n">
         <v>0</v>
       </c>
-      <c r="BU302" t="inlineStr"/>
+      <c r="BU302" t="inlineStr">
+        <is>
+          <t>台新</t>
+        </is>
+      </c>
       <c r="BV302" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -44984,21 +45690,27 @@
       </c>
       <c r="BN303" t="inlineStr"/>
       <c r="BO303" t="n">
-        <v>0</v>
+        <v>1784860</v>
       </c>
       <c r="BP303" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ303" t="inlineStr"/>
+        <v>50050</v>
+      </c>
+      <c r="BQ303" t="n">
+        <v>35.66</v>
+      </c>
       <c r="BR303" t="inlineStr"/>
       <c r="BS303" t="inlineStr"/>
       <c r="BT303" t="n">
         <v>0</v>
       </c>
-      <c r="BU303" t="inlineStr"/>
+      <c r="BU303" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV303" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -45126,21 +45838,27 @@
       </c>
       <c r="BN304" t="inlineStr"/>
       <c r="BO304" t="n">
-        <v>0</v>
+        <v>1323200</v>
       </c>
       <c r="BP304" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ304" t="inlineStr"/>
+        <v>141070</v>
+      </c>
+      <c r="BQ304" t="n">
+        <v>9.380000000000001</v>
+      </c>
       <c r="BR304" t="inlineStr"/>
       <c r="BS304" t="inlineStr"/>
       <c r="BT304" t="n">
         <v>0</v>
       </c>
-      <c r="BU304" t="inlineStr"/>
+      <c r="BU304" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="BV304" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -45646,7 +46364,7 @@
       </c>
       <c r="BN308" t="inlineStr"/>
       <c r="BO308" t="n">
-        <v>0</v>
+        <v>13110</v>
       </c>
       <c r="BP308" t="n">
         <v>0</v>
@@ -45657,10 +46375,14 @@
       <c r="BT308" t="n">
         <v>0</v>
       </c>
-      <c r="BU308" t="inlineStr"/>
+      <c r="BU308" t="inlineStr">
+        <is>
+          <t>元富</t>
+        </is>
+      </c>
       <c r="BV308" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -45788,21 +46510,27 @@
       </c>
       <c r="BN309" t="inlineStr"/>
       <c r="BO309" t="n">
-        <v>0</v>
+        <v>24351970</v>
       </c>
       <c r="BP309" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ309" t="inlineStr"/>
+        <v>798830</v>
+      </c>
+      <c r="BQ309" t="n">
+        <v>30.48</v>
+      </c>
       <c r="BR309" t="inlineStr"/>
       <c r="BS309" t="inlineStr"/>
       <c r="BT309" t="n">
         <v>0</v>
       </c>
-      <c r="BU309" t="inlineStr"/>
+      <c r="BU309" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV309" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -45930,7 +46658,7 @@
       </c>
       <c r="BN310" t="inlineStr"/>
       <c r="BO310" t="n">
-        <v>0</v>
+        <v>151230</v>
       </c>
       <c r="BP310" t="n">
         <v>0</v>
@@ -45941,10 +46669,14 @@
       <c r="BT310" t="n">
         <v>0</v>
       </c>
-      <c r="BU310" t="inlineStr"/>
+      <c r="BU310" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV310" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>
@@ -46072,7 +46804,7 @@
       </c>
       <c r="BN311" t="inlineStr"/>
       <c r="BO311" t="n">
-        <v>0</v>
+        <v>1336480</v>
       </c>
       <c r="BP311" t="n">
         <v>0</v>
@@ -46083,10 +46815,14 @@
       <c r="BT311" t="n">
         <v>0</v>
       </c>
-      <c r="BU311" t="inlineStr"/>
+      <c r="BU311" t="inlineStr">
+        <is>
+          <t>元大</t>
+        </is>
+      </c>
       <c r="BV311" t="inlineStr">
         <is>
-          <t>今日無可用權證成交金額</t>
+          <t>無明顯權證資金訊號</t>
         </is>
       </c>
     </row>

--- a/output/latest/all_candidates_latest.xlsx
+++ b/output/latest/all_candidates_latest.xlsx
@@ -1060,7 +1060,7 @@
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM16" t="n">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       <c r="BK20" t="inlineStr"/>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM20" t="n">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       <c r="BK29" t="inlineStr"/>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM29" t="n">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="BV35" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -5934,13 +5934,17 @@
       <c r="BK36" t="inlineStr"/>
       <c r="BL36" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM36" t="n">
         <v>0</v>
       </c>
-      <c r="BN36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr">
+        <is>
+          <t>認購權證成交金額很大且認購/認售比偏高，需檢查標的是否高位追價或獲利結清</t>
+        </is>
+      </c>
       <c r="BO36" t="n">
         <v>111096700</v>
       </c>
@@ -5962,7 +5966,7 @@
       </c>
       <c r="BV36" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6098,7 @@
       <c r="BK37" t="inlineStr"/>
       <c r="BL37" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM37" t="n">
@@ -6120,7 +6124,7 @@
       </c>
       <c r="BV37" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6282,7 @@
       </c>
       <c r="BV38" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6556,7 @@
       <c r="BK40" t="inlineStr"/>
       <c r="BL40" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM40" t="n">
@@ -6578,7 +6582,7 @@
       </c>
       <c r="BV40" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6716,7 @@
       <c r="BK41" t="inlineStr"/>
       <c r="BL41" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM41" t="n">
@@ -6740,7 +6744,7 @@
       </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6878,7 @@
       <c r="BK42" t="inlineStr"/>
       <c r="BL42" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM42" t="n">
@@ -6900,7 +6904,7 @@
       </c>
       <c r="BV42" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7178,7 @@
       <c r="BK44" t="inlineStr"/>
       <c r="BL44" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM44" t="n">
@@ -7202,7 +7206,7 @@
       </c>
       <c r="BV44" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7480,7 @@
       <c r="BK46" t="inlineStr"/>
       <c r="BL46" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM46" t="n">
@@ -7504,7 +7508,7 @@
       </c>
       <c r="BV46" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7668,7 @@
       </c>
       <c r="BV47" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7942,7 @@
       <c r="BK49" t="inlineStr"/>
       <c r="BL49" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM49" t="n">
@@ -7964,7 +7968,7 @@
       </c>
       <c r="BV49" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8242,7 @@
       <c r="BK51" t="inlineStr"/>
       <c r="BL51" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM51" t="n">
@@ -8266,7 +8270,7 @@
       </c>
       <c r="BV51" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8430,7 @@
       </c>
       <c r="BV52" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9290,7 @@
       </c>
       <c r="BV58" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10848,7 @@
       </c>
       <c r="BV69" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -12466,7 +12470,7 @@
       </c>
       <c r="BV80" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12712,7 @@
       </c>
       <c r="BV81" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -12950,7 +12954,7 @@
       </c>
       <c r="BV82" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13170,7 @@
       </c>
       <c r="BL83" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM83" t="n">
@@ -13194,7 +13198,7 @@
       </c>
       <c r="BV83" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13414,7 @@
       </c>
       <c r="BL84" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM84" t="n">
@@ -13436,7 +13440,7 @@
       </c>
       <c r="BV84" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13684,7 @@
       </c>
       <c r="BV85" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -14366,7 +14370,7 @@
       </c>
       <c r="BV88" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -14608,7 +14612,7 @@
       </c>
       <c r="BV89" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15298,7 @@
       </c>
       <c r="BV92" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -15542,7 +15546,7 @@
       </c>
       <c r="BV93" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -15762,13 +15766,17 @@
       </c>
       <c r="BL94" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM94" t="n">
         <v>0</v>
       </c>
-      <c r="BN94" t="inlineStr"/>
+      <c r="BN94" t="inlineStr">
+        <is>
+          <t>認購權證成交量與成交金額同步偏大，短線資金關注度高</t>
+        </is>
+      </c>
       <c r="BO94" t="n">
         <v>67969770</v>
       </c>
@@ -15790,7 +15798,7 @@
       </c>
       <c r="BV94" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -16258,7 +16266,7 @@
       </c>
       <c r="BV96" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16512,7 @@
       </c>
       <c r="BV97" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16958,7 @@
       </c>
       <c r="BL99" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM99" t="n">
@@ -16978,7 +16986,7 @@
       </c>
       <c r="BV99" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -17198,7 +17206,7 @@
       </c>
       <c r="BL100" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM100" t="n">
@@ -17226,7 +17234,7 @@
       </c>
       <c r="BV100" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -17610,7 +17618,7 @@
       </c>
       <c r="BV102" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -17904,7 +17912,7 @@
       </c>
       <c r="BV104" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -18714,7 +18722,7 @@
       <c r="BK110" t="inlineStr"/>
       <c r="BL110" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM110" t="n">
@@ -18742,7 +18750,7 @@
       </c>
       <c r="BV110" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -19144,7 +19152,7 @@
       <c r="BK113" t="inlineStr"/>
       <c r="BL113" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM113" t="n">
@@ -19172,7 +19180,7 @@
       </c>
       <c r="BV113" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19338,7 @@
       </c>
       <c r="BV114" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -19760,7 +19768,7 @@
       </c>
       <c r="BV117" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -19918,7 +19926,7 @@
       </c>
       <c r="BV118" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -20212,7 +20220,7 @@
       </c>
       <c r="BV120" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -20342,7 +20350,7 @@
       <c r="BK121" t="inlineStr"/>
       <c r="BL121" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM121" t="n">
@@ -20370,7 +20378,7 @@
       </c>
       <c r="BV121" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20536,7 @@
       </c>
       <c r="BV122" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -20658,7 +20666,7 @@
       <c r="BK123" t="inlineStr"/>
       <c r="BL123" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM123" t="n">
@@ -20686,7 +20694,7 @@
       </c>
       <c r="BV123" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -20998,7 +21006,7 @@
       </c>
       <c r="BV125" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -21154,7 +21162,7 @@
       </c>
       <c r="BV126" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21318,7 @@
       </c>
       <c r="BV127" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -21440,7 +21448,7 @@
       <c r="BK128" t="inlineStr"/>
       <c r="BL128" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM128" t="n">
@@ -21468,7 +21476,7 @@
       </c>
       <c r="BV128" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -21624,7 +21632,7 @@
       </c>
       <c r="BV129" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -22800,7 +22808,7 @@
       </c>
       <c r="BV138" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -23046,7 +23054,7 @@
       <c r="BK140" t="inlineStr"/>
       <c r="BL140" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM140" t="n">
@@ -23074,7 +23082,7 @@
       </c>
       <c r="BV140" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23202,7 @@
       <c r="BK141" t="inlineStr"/>
       <c r="BL141" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM141" t="n">
@@ -23222,7 +23230,7 @@
       </c>
       <c r="BV141" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -23494,7 +23502,7 @@
       </c>
       <c r="BV143" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -23766,7 +23774,7 @@
       </c>
       <c r="BV145" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -23912,7 +23920,7 @@
       </c>
       <c r="BV146" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -24914,7 +24922,7 @@
       <c r="BK154" t="inlineStr"/>
       <c r="BL154" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM154" t="n">
@@ -24942,7 +24950,7 @@
       </c>
       <c r="BV154" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -25088,7 +25096,7 @@
       </c>
       <c r="BV155" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -25208,7 +25216,7 @@
       <c r="BK156" t="inlineStr"/>
       <c r="BL156" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM156" t="n">
@@ -25236,7 +25244,7 @@
       </c>
       <c r="BV156" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -25382,7 +25390,7 @@
       </c>
       <c r="BV157" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -25528,7 +25536,7 @@
       </c>
       <c r="BV158" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25684,7 @@
       </c>
       <c r="BV159" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -25822,7 +25830,7 @@
       </c>
       <c r="BV160" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -25942,7 +25950,7 @@
       <c r="BK161" t="inlineStr"/>
       <c r="BL161" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM161" t="n">
@@ -25968,7 +25976,7 @@
       </c>
       <c r="BV161" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -26088,7 +26096,7 @@
       <c r="BK162" t="inlineStr"/>
       <c r="BL162" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM162" t="n">
@@ -26116,7 +26124,7 @@
       </c>
       <c r="BV162" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -26388,7 +26396,7 @@
       </c>
       <c r="BV164" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -26534,7 +26542,7 @@
       </c>
       <c r="BV165" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -26654,7 +26662,7 @@
       <c r="BK166" t="inlineStr"/>
       <c r="BL166" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM166" t="n">
@@ -26682,7 +26690,7 @@
       </c>
       <c r="BV166" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -26828,7 +26836,7 @@
       </c>
       <c r="BV167" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -26974,7 +26982,7 @@
       </c>
       <c r="BV168" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -27094,13 +27102,17 @@
       <c r="BK169" t="inlineStr"/>
       <c r="BL169" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM169" t="n">
         <v>0</v>
       </c>
-      <c r="BN169" t="inlineStr"/>
+      <c r="BN169" t="inlineStr">
+        <is>
+          <t>認購權證成交量與成交金額同步偏大，短線資金關注度高</t>
+        </is>
+      </c>
       <c r="BO169" t="n">
         <v>67969770</v>
       </c>
@@ -27122,7 +27134,7 @@
       </c>
       <c r="BV169" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -27270,7 +27282,7 @@
       </c>
       <c r="BV170" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -27390,7 +27402,7 @@
       <c r="BK171" t="inlineStr"/>
       <c r="BL171" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM171" t="n">
@@ -27418,7 +27430,7 @@
       </c>
       <c r="BV171" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -27942,7 +27954,7 @@
       </c>
       <c r="BV175" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -28088,7 +28100,7 @@
       </c>
       <c r="BV176" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -28360,7 +28372,7 @@
       </c>
       <c r="BV178" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -28506,7 +28518,7 @@
       </c>
       <c r="BV179" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -28778,7 +28790,7 @@
       </c>
       <c r="BV181" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -29322,7 +29334,7 @@
       </c>
       <c r="BV185" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -29442,7 +29454,7 @@
       <c r="BK186" t="inlineStr"/>
       <c r="BL186" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM186" t="n">
@@ -29470,7 +29482,7 @@
       </c>
       <c r="BV186" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -29744,7 +29756,7 @@
       </c>
       <c r="BV188" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30028,7 @@
       </c>
       <c r="BV190" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -30162,7 +30174,7 @@
       </c>
       <c r="BV191" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -30310,7 +30322,7 @@
       </c>
       <c r="BV192" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -30808,7 +30820,7 @@
       <c r="BK196" t="inlineStr"/>
       <c r="BL196" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM196" t="n">
@@ -30836,7 +30848,7 @@
       </c>
       <c r="BV196" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -31208,7 +31220,7 @@
       <c r="BK199" t="inlineStr"/>
       <c r="BL199" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM199" t="n">
@@ -31236,7 +31248,7 @@
       </c>
       <c r="BV199" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -31356,7 +31368,7 @@
       <c r="BK200" t="inlineStr"/>
       <c r="BL200" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM200" t="n">
@@ -31382,7 +31394,7 @@
       </c>
       <c r="BV200" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -31528,7 +31540,7 @@
       </c>
       <c r="BV201" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -31820,7 +31832,7 @@
       </c>
       <c r="BV203" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -32092,7 +32104,7 @@
       </c>
       <c r="BV205" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -32212,7 +32224,7 @@
       <c r="BK206" t="inlineStr"/>
       <c r="BL206" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM206" t="n">
@@ -32240,7 +32252,7 @@
       </c>
       <c r="BV206" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -32638,7 +32650,7 @@
       </c>
       <c r="BV209" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -32910,7 +32922,7 @@
       </c>
       <c r="BV211" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -33562,7 +33574,7 @@
       </c>
       <c r="BV216" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -33710,7 +33722,7 @@
       </c>
       <c r="BV217" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -33830,7 +33842,7 @@
       <c r="BK218" t="inlineStr"/>
       <c r="BL218" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM218" t="n">
@@ -33858,7 +33870,7 @@
       </c>
       <c r="BV218" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -34130,7 +34142,7 @@
       </c>
       <c r="BV220" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -34276,7 +34288,7 @@
       </c>
       <c r="BV221" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -34548,7 +34560,7 @@
       </c>
       <c r="BV223" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -34694,7 +34706,7 @@
       </c>
       <c r="BV224" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -35218,7 +35230,7 @@
       </c>
       <c r="BV228" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -35338,7 +35350,7 @@
       <c r="BK229" t="inlineStr"/>
       <c r="BL229" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM229" t="n">
@@ -35366,7 +35378,7 @@
       </c>
       <c r="BV229" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -35512,7 +35524,7 @@
       </c>
       <c r="BV230" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -35784,7 +35796,7 @@
       </c>
       <c r="BV232" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -35904,7 +35916,7 @@
       <c r="BK233" t="inlineStr"/>
       <c r="BL233" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM233" t="n">
@@ -35932,7 +35944,7 @@
       </c>
       <c r="BV233" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -36078,7 +36090,7 @@
       </c>
       <c r="BV234" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -36226,7 +36238,7 @@
       </c>
       <c r="BV235" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -36346,7 +36358,7 @@
       <c r="BK236" t="inlineStr"/>
       <c r="BL236" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM236" t="n">
@@ -36374,7 +36386,7 @@
       </c>
       <c r="BV236" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -36520,7 +36532,7 @@
       </c>
       <c r="BV237" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -36640,7 +36652,7 @@
       <c r="BK238" t="inlineStr"/>
       <c r="BL238" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM238" t="n">
@@ -36668,7 +36680,7 @@
       </c>
       <c r="BV238" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -36788,13 +36800,17 @@
       <c r="BK239" t="inlineStr"/>
       <c r="BL239" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM239" t="n">
         <v>0</v>
       </c>
-      <c r="BN239" t="inlineStr"/>
+      <c r="BN239" t="inlineStr">
+        <is>
+          <t>認購權證成交量與成交金額同步偏大，短線資金關注度高</t>
+        </is>
+      </c>
       <c r="BO239" t="n">
         <v>59325140</v>
       </c>
@@ -36816,7 +36832,7 @@
       </c>
       <c r="BV239" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -36936,7 +36952,7 @@
       <c r="BK240" t="inlineStr"/>
       <c r="BL240" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM240" t="n">
@@ -36964,7 +36980,7 @@
       </c>
       <c r="BV240" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -37084,7 +37100,7 @@
       <c r="BK241" t="inlineStr"/>
       <c r="BL241" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM241" t="n">
@@ -37112,7 +37128,7 @@
       </c>
       <c r="BV241" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額偏高，先列觀察</t>
         </is>
       </c>
     </row>
@@ -37258,7 +37274,7 @@
       </c>
       <c r="BV242" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -37406,7 +37422,7 @@
       </c>
       <c r="BV243" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -37526,7 +37542,7 @@
       <c r="BK244" t="inlineStr"/>
       <c r="BL244" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM244" t="n">
@@ -37554,7 +37570,7 @@
       </c>
       <c r="BV244" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -37674,7 +37690,7 @@
       <c r="BK245" t="inlineStr"/>
       <c r="BL245" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM245" t="n">
@@ -37702,7 +37718,7 @@
       </c>
       <c r="BV245" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -38498,7 +38514,7 @@
       </c>
       <c r="BV251" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -38896,7 +38912,7 @@
       </c>
       <c r="BV254" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -39042,7 +39058,7 @@
       </c>
       <c r="BV255" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -39314,7 +39330,7 @@
       </c>
       <c r="BV257" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -39964,7 +39980,7 @@
       </c>
       <c r="BV262" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -40238,7 +40254,7 @@
       </c>
       <c r="BV264" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -40512,7 +40528,7 @@
       </c>
       <c r="BV266" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -40658,7 +40674,7 @@
       </c>
       <c r="BV267" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -40804,7 +40820,7 @@
       </c>
       <c r="BV268" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -41202,7 +41218,7 @@
       </c>
       <c r="BV271" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -41612,7 +41628,7 @@
       </c>
       <c r="BV274" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -41768,7 +41784,7 @@
       </c>
       <c r="BV275" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -41924,7 +41940,7 @@
       </c>
       <c r="BV276" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -42054,7 +42070,7 @@
       <c r="BK277" t="inlineStr"/>
       <c r="BL277" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM277" t="n">
@@ -42080,7 +42096,7 @@
       </c>
       <c r="BV277" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -42372,7 +42388,7 @@
       </c>
       <c r="BV279" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -42638,7 +42654,7 @@
       <c r="BK281" t="inlineStr"/>
       <c r="BL281" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM281" t="n">
@@ -42666,7 +42682,7 @@
       </c>
       <c r="BV281" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -42940,7 +42956,7 @@
       </c>
       <c r="BV283" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -43088,7 +43104,7 @@
       </c>
       <c r="BV284" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -43234,7 +43250,7 @@
       </c>
       <c r="BV285" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -43354,7 +43370,7 @@
       </c>
       <c r="BL286" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM286" t="n">
@@ -43382,7 +43398,7 @@
       </c>
       <c r="BV286" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -44006,7 +44022,7 @@
       </c>
       <c r="BL291" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM291" t="n">
@@ -44034,7 +44050,7 @@
       </c>
       <c r="BV291" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -44180,7 +44196,7 @@
       </c>
       <c r="BV292" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -44452,7 +44468,7 @@
       </c>
       <c r="BV294" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -44600,7 +44616,7 @@
       </c>
       <c r="BV295" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -44746,7 +44762,7 @@
       </c>
       <c r="BV296" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -45018,7 +45034,7 @@
       </c>
       <c r="BV298" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -45164,7 +45180,7 @@
       </c>
       <c r="BV299" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -45562,7 +45578,7 @@
       </c>
       <c r="BV302" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -45710,7 +45726,7 @@
       </c>
       <c r="BV303" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -45858,7 +45874,7 @@
       </c>
       <c r="BV304" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -46382,7 +46398,7 @@
       </c>
       <c r="BV308" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -46502,7 +46518,7 @@
       </c>
       <c r="BL309" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="BM309" t="n">
@@ -46530,7 +46546,7 @@
       </c>
       <c r="BV309" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，認購權證成交金額有一定水準，先列觀察</t>
         </is>
       </c>
     </row>
@@ -46676,7 +46692,7 @@
       </c>
       <c r="BV310" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -46822,7 +46838,7 @@
       </c>
       <c r="BV311" t="inlineStr">
         <is>
-          <t>無明顯權證資金訊號</t>
+          <t>首日缺少歷史比較，權證成交金額未達觀察門檻</t>
         </is>
       </c>
     </row>
@@ -46923,7 +46939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46941,16 +46957,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>no_signal</t>
+          <t>call_activity_observation</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>163</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>no_signal</t>
+        </is>
+      </c>
       <c r="B3" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="n">
         <v>147</v>
       </c>
     </row>

--- a/output/latest/all_candidates_latest.xlsx
+++ b/output/latest/all_candidates_latest.xlsx
@@ -32382,17 +32382,17 @@
       </c>
       <c r="BN200" t="inlineStr"/>
       <c r="BO200" t="n">
-        <v>3520410</v>
+        <v>2992510</v>
       </c>
       <c r="BP200" t="n">
         <v>0</v>
       </c>
       <c r="BQ200" t="inlineStr"/>
       <c r="BR200" t="n">
-        <v>15.65</v>
+        <v>-1.69</v>
       </c>
       <c r="BS200" t="n">
-        <v>15.65</v>
+        <v>-1.69</v>
       </c>
       <c r="BT200" t="n">
         <v>0</v>
@@ -32532,17 +32532,17 @@
       </c>
       <c r="BN201" t="inlineStr"/>
       <c r="BO201" t="n">
-        <v>3045640</v>
+        <v>2705640</v>
       </c>
       <c r="BP201" t="n">
         <v>0</v>
       </c>
       <c r="BQ201" t="inlineStr"/>
       <c r="BR201" t="n">
-        <v>-49.04</v>
+        <v>-54.73</v>
       </c>
       <c r="BS201" t="n">
-        <v>-49.04</v>
+        <v>-54.73</v>
       </c>
       <c r="BT201" t="n">
         <v>0</v>
@@ -40034,37 +40034,17 @@
       <c r="BI255" t="inlineStr"/>
       <c r="BJ255" t="inlineStr"/>
       <c r="BK255" t="inlineStr"/>
-      <c r="BL255" t="inlineStr">
-        <is>
-          <t>no_signal</t>
-        </is>
-      </c>
-      <c r="BM255" t="n">
-        <v>0</v>
-      </c>
+      <c r="BL255" t="inlineStr"/>
+      <c r="BM255" t="inlineStr"/>
       <c r="BN255" t="inlineStr"/>
-      <c r="BO255" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP255" t="n">
-        <v>0</v>
-      </c>
+      <c r="BO255" t="inlineStr"/>
+      <c r="BP255" t="inlineStr"/>
       <c r="BQ255" t="inlineStr"/>
       <c r="BR255" t="inlineStr"/>
       <c r="BS255" t="inlineStr"/>
-      <c r="BT255" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU255" t="inlineStr">
-        <is>
-          <t>元展</t>
-        </is>
-      </c>
-      <c r="BV255" t="inlineStr">
-        <is>
-          <t>今日無可用權證成交金額</t>
-        </is>
-      </c>
+      <c r="BT255" t="inlineStr"/>
+      <c r="BU255" t="inlineStr"/>
+      <c r="BV255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -50930,17 +50910,17 @@
       </c>
       <c r="BN333" t="inlineStr"/>
       <c r="BO333" t="n">
-        <v>3520410</v>
+        <v>2992510</v>
       </c>
       <c r="BP333" t="n">
         <v>0</v>
       </c>
       <c r="BQ333" t="inlineStr"/>
       <c r="BR333" t="n">
-        <v>15.65</v>
+        <v>-1.69</v>
       </c>
       <c r="BS333" t="n">
-        <v>15.65</v>
+        <v>-1.69</v>
       </c>
       <c r="BT333" t="n">
         <v>0</v>
@@ -56711,13 +56691,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
